--- a/reports/TKPL_Registered_Players.xlsx
+++ b/reports/TKPL_Registered_Players.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Summary Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Approved &amp; Verified (84)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Payment Pending (12)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="All Registrations (96)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Approved &amp; Verified (89)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Payment Pending (10)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All Registrations (99)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Approved &amp; Verified (84)'!$A$1:$Q$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Payment Pending (12)'!$A$1:$Q$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Registrations (96)'!$A$1:$Q$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Approved &amp; Verified (89)'!$A$1:$Q$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Payment Pending (10)'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Registrations (99)'!$A$1:$Q$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Live Roster Report — Generated on 30 Oct 2026, 04:18 PM IST</t>
+          <t>Live Roster Report — Generated on 30 Oct 2026, 04:45 PM IST</t>
         </is>
       </c>
     </row>
@@ -697,25 +697,25 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>99</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>₹33,516</t>
+          <t>₹35,511</t>
         </is>
       </c>
     </row>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -835,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:Q90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2019,27 +2019,27 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0116</t>
+          <t>TKPL-2026-0115</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>Vonk Krishna Naik</t>
+          <t>ASHOK ROYAL</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>9502128368</t>
+          <t>8121314001</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>1998-05-04</t>
+          <t>1996-06-28</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
-          <t>Guvvalacheruvu, Rayachoty dst</t>
+          <t>RAJAMPET</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -2057,7 +2057,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J15" s="21" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>MRNS 11s</t>
+        </is>
+      </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -2070,7 +2074,7 @@
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0014</t>
+          <t>TKPL-RCPT-2026-0085</t>
         </is>
       </c>
       <c r="N15" s="22" t="inlineStr">
@@ -2080,12 +2084,12 @@
       </c>
       <c r="O15" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:18 PM</t>
+          <t>30-10-2026 04:27 PM</t>
         </is>
       </c>
       <c r="P15" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:15 PM</t>
+          <t>30-10-2026 12:14 PM</t>
         </is>
       </c>
       <c r="Q15" s="21" t="inlineStr">
@@ -2100,27 +2104,27 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0117</t>
+          <t>TKPL-2026-0116</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>SYED SHAMEER</t>
+          <t>Vonk Krishna Naik</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>7993308648</t>
+          <t>9502128368</t>
         </is>
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>2005-08-19</t>
+          <t>1998-05-04</t>
         </is>
       </c>
       <c r="F16" s="18" t="inlineStr">
         <is>
-          <t>Pullampet</t>
+          <t>Guvvalacheruvu, Rayachoty dst</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
@@ -2138,11 +2142,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
+      <c r="J16" s="18" t="inlineStr"/>
       <c r="K16" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="M16" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0047</t>
+          <t>TKPL-RCPT-2026-0014</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="O16" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:44 PM</t>
+          <t>30-10-2026 12:18 PM</t>
         </is>
       </c>
       <c r="P16" s="17" t="inlineStr">
@@ -2185,27 +2185,27 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0118</t>
+          <t>TKPL-2026-0117</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>Samith</t>
+          <t>SYED SHAMEER</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>6281866816</t>
+          <t>7993308648</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>2006-05-07</t>
+          <t>2005-08-19</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Pullampet</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t>Apl premier league champions</t>
+          <t>Excellent</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0072</t>
+          <t>TKPL-RCPT-2026-0047</t>
         </is>
       </c>
       <c r="N17" s="22" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="O17" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:28 PM</t>
+          <t>30-10-2026 01:44 PM</t>
         </is>
       </c>
       <c r="P17" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:16 PM</t>
+          <t>30-10-2026 12:15 PM</t>
         </is>
       </c>
       <c r="Q17" s="21" t="inlineStr">
@@ -2270,27 +2270,27 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0119</t>
+          <t>TKPL-2026-0118</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>Kaif (Ramamohan)</t>
+          <t>Samith</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>7799646472</t>
+          <t>6281866816</t>
         </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>1993-10-06</t>
+          <t>2006-05-07</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
         <is>
-          <t>Raychoty</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G18" s="17" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
-          <t>Local tournaments and countys</t>
+          <t>Apl premier league champions</t>
         </is>
       </c>
       <c r="K18" s="17" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="M18" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0016</t>
+          <t>TKPL-RCPT-2026-0072</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O18" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:22 PM</t>
+          <t>30-10-2026 03:28 PM</t>
         </is>
       </c>
       <c r="P18" s="17" t="inlineStr">
@@ -2355,27 +2355,27 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0120</t>
+          <t>TKPL-2026-0119</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>Nageshwar Reddy N</t>
+          <t>Kaif (Ramamohan)</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>9398142273</t>
+          <t>7799646472</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>1998-07-14</t>
+          <t>1993-10-06</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Raychoty</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="J19" s="21" t="inlineStr">
         <is>
-          <t>Played professional cricket and many local , out side state tournaments</t>
+          <t>Local tournaments and countys</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0059</t>
+          <t>TKPL-RCPT-2026-0016</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -2420,17 +2420,17 @@
       </c>
       <c r="O19" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:47 PM</t>
+          <t>30-10-2026 12:22 PM</t>
         </is>
       </c>
       <c r="P19" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:17 PM</t>
+          <t>30-10-2026 12:16 PM</t>
         </is>
       </c>
       <c r="Q19" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -2440,32 +2440,32 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0121</t>
+          <t>TKPL-2026-0120</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>Indra Sena Reddy</t>
+          <t>Nageshwar Reddy N</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>6300027464</t>
+          <t>9398142273</t>
         </is>
       </c>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>2002-06-10</t>
+          <t>1998-07-14</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
         <is>
-          <t>Pendlimarri</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G20" s="17" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="J20" s="18" t="inlineStr">
         <is>
-          <t>5 years experience</t>
+          <t>Played professional cricket and many local , out side state tournaments</t>
         </is>
       </c>
       <c r="K20" s="17" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="M20" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0012</t>
+          <t>TKPL-RCPT-2026-0059</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="O20" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:18 PM</t>
+          <t>30-10-2026 02:47 PM</t>
         </is>
       </c>
       <c r="P20" s="17" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="Q20" s="18" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -2525,27 +2525,27 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0123</t>
+          <t>TKPL-2026-0121</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
         <is>
-          <t>Goddindla Ashok kumar</t>
+          <t>Indra Sena Reddy</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>6301929492</t>
+          <t>6300027464</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>1999-09-16</t>
+          <t>2002-06-10</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>Rayachoty</t>
+          <t>Pendlimarri</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
@@ -2565,8 +2565,7 @@
       </c>
       <c r="J21" s="21" t="inlineStr">
         <is>
-          <t>Rayachoty premier league 2026/
-Karanataka institute of cricket</t>
+          <t>5 years experience</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
@@ -2581,7 +2580,7 @@
       </c>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0013</t>
+          <t>TKPL-RCPT-2026-0012</t>
         </is>
       </c>
       <c r="N21" s="22" t="inlineStr">
@@ -2611,32 +2610,32 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0124</t>
+          <t>TKPL-2026-0123</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>Charan Kumar</t>
+          <t>Goddindla Ashok kumar</t>
         </is>
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>9951035846</t>
+          <t>6301929492</t>
         </is>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>1997-08-28</t>
+          <t>1999-09-16</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
         <is>
-          <t>Proddatur</t>
+          <t>Rayachoty</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
@@ -2649,7 +2648,12 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J22" s="18" t="inlineStr"/>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>Rayachoty premier league 2026/
+Karanataka institute of cricket</t>
+        </is>
+      </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -2662,7 +2666,7 @@
       </c>
       <c r="M22" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0015</t>
+          <t>TKPL-RCPT-2026-0013</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -2677,7 +2681,7 @@
       </c>
       <c r="P22" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:18 PM</t>
+          <t>30-10-2026 12:17 PM</t>
         </is>
       </c>
       <c r="Q22" s="18" t="inlineStr">
@@ -2692,27 +2696,27 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0126</t>
+          <t>TKPL-2026-0124</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>E.Anjaneyulu</t>
+          <t>Charan Kumar</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>9347481541</t>
+          <t>9951035846</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>1994-03-10</t>
+          <t>1997-08-28</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>Chakram PETA</t>
+          <t>Proddatur</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
@@ -2730,11 +2734,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J23" s="21" t="inlineStr">
-        <is>
-          <t>Local tournaments</t>
-        </is>
-      </c>
+      <c r="J23" s="21" t="inlineStr"/>
       <c r="K23" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0017</t>
+          <t>TKPL-RCPT-2026-0015</t>
         </is>
       </c>
       <c r="N23" s="22" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="O23" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:24 PM</t>
+          <t>30-10-2026 12:18 PM</t>
         </is>
       </c>
       <c r="P23" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:22 PM</t>
+          <t>30-10-2026 12:18 PM</t>
         </is>
       </c>
       <c r="Q23" s="21" t="inlineStr">
@@ -2777,27 +2777,27 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0127</t>
+          <t>TKPL-2026-0126</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>G. Gurivireddy</t>
+          <t>E.Anjaneyulu</t>
         </is>
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>8099296433</t>
+          <t>9347481541</t>
         </is>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>1999-07-05</t>
+          <t>1994-03-10</t>
         </is>
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
-          <t>Yerraguntla</t>
+          <t>Chakram PETA</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
@@ -2815,7 +2815,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr"/>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>Local tournaments</t>
+        </is>
+      </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -2828,7 +2832,7 @@
       </c>
       <c r="M24" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0019</t>
+          <t>TKPL-RCPT-2026-0017</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -2838,12 +2842,12 @@
       </c>
       <c r="O24" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:26 PM</t>
+          <t>30-10-2026 12:24 PM</t>
         </is>
       </c>
       <c r="P24" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:24 PM</t>
+          <t>30-10-2026 12:22 PM</t>
         </is>
       </c>
       <c r="Q24" s="18" t="inlineStr">
@@ -2858,27 +2862,27 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0128</t>
+          <t>TKPL-2026-0127</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>Gandham babu akahil</t>
+          <t>G. Gurivireddy</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>8500036244</t>
+          <t>8099296433</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>1995-05-10</t>
+          <t>1999-07-05</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t>Pulivendula</t>
+          <t>Yerraguntla</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
@@ -2896,11 +2900,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>Crick heroes</t>
-        </is>
-      </c>
+      <c r="J25" s="21" t="inlineStr"/>
       <c r="K25" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M25" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0018</t>
+          <t>TKPL-RCPT-2026-0019</t>
         </is>
       </c>
       <c r="N25" s="22" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="P25" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:25 PM</t>
+          <t>30-10-2026 12:24 PM</t>
         </is>
       </c>
       <c r="Q25" s="21" t="inlineStr">
@@ -2943,27 +2943,27 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0129</t>
+          <t>TKPL-2026-0128</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>AVULA BINDU reddy</t>
+          <t>Gandham babu akahil</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>9177166167</t>
+          <t>8500036244</t>
         </is>
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>1997-06-07</t>
+          <t>1995-05-10</t>
         </is>
       </c>
       <c r="F26" s="18" t="inlineStr">
         <is>
-          <t>Rayachoty</t>
+          <t>Pulivendula</t>
         </is>
       </c>
       <c r="G26" s="17" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
-          <t>Local tournaments winning captain</t>
+          <t>Crick heroes</t>
         </is>
       </c>
       <c r="K26" s="17" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="M26" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0020</t>
+          <t>TKPL-RCPT-2026-0018</t>
         </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
@@ -3028,22 +3028,22 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0131</t>
+          <t>TKPL-2026-0129</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>Kiran kumar reddy Avula</t>
+          <t>AVULA BINDU reddy</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7448726536</t>
+          <t>9177166167</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>1994-10-21</t>
+          <t>1997-06-07</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -3066,7 +3066,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J27" s="21" t="inlineStr"/>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>Local tournaments winning captain</t>
+        </is>
+      </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -3079,7 +3083,7 @@
       </c>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0021</t>
+          <t>TKPL-RCPT-2026-0020</t>
         </is>
       </c>
       <c r="N27" s="22" t="inlineStr">
@@ -3089,12 +3093,12 @@
       </c>
       <c r="O27" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:29 PM</t>
+          <t>30-10-2026 12:26 PM</t>
         </is>
       </c>
       <c r="P27" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:28 PM</t>
+          <t>30-10-2026 12:25 PM</t>
         </is>
       </c>
       <c r="Q27" s="21" t="inlineStr">
@@ -3109,27 +3113,27 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0132</t>
+          <t>TKPL-2026-0131</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>SUDHEER KUMAR NASYAM</t>
+          <t>Kiran kumar reddy Avula</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>9440271935</t>
+          <t>7448726536</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>1995-04-08</t>
+          <t>1994-10-21</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>PRODDATUR</t>
+          <t>Rayachoty</t>
         </is>
       </c>
       <c r="G28" s="17" t="inlineStr">
@@ -3160,7 +3164,7 @@
       </c>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0022</t>
+          <t>TKPL-RCPT-2026-0021</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -3170,12 +3174,12 @@
       </c>
       <c r="O28" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:30 PM</t>
+          <t>30-10-2026 12:29 PM</t>
         </is>
       </c>
       <c r="P28" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:29 PM</t>
+          <t>30-10-2026 12:28 PM</t>
         </is>
       </c>
       <c r="Q28" s="18" t="inlineStr">
@@ -3190,45 +3194,126 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
+          <t>TKPL-2026-0132</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>SUDHEER KUMAR NASYAM</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>9440271935</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>1995-04-08</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>PRODDATUR</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr"/>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L29" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0022</t>
+        </is>
+      </c>
+      <c r="N29" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O29" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 12:29 PM</t>
+        </is>
+      </c>
+      <c r="Q29" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
           <t>TKPL-2026-0133</t>
         </is>
       </c>
-      <c r="C29" s="21" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>L.SUNEEL</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>9392550479</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>2003-05-10</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
         <is>
           <t>V.N palli</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>Bowler</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
         <is>
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J29" s="21" t="inlineStr">
+      <c r="J30" s="18" t="inlineStr">
         <is>
           <t>1.PRAKASH NAGAR PREMIER LEAGUE (PPL)
 2.(YSR KADAPA) U.RAJUPALEM PREMIERE LEAGUE-2
@@ -3245,124 +3330,39 @@
 13.kodur premier league</t>
         </is>
       </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L29" s="19" t="inlineStr">
+      <c r="K30" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L30" s="19" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="M29" s="13" t="inlineStr">
+      <c r="M30" s="17" t="inlineStr">
         <is>
           <t>TKPL-RCPT-2026-0060</t>
         </is>
       </c>
-      <c r="N29" s="22" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O29" s="13" t="inlineStr">
+      <c r="N30" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O30" s="17" t="inlineStr">
         <is>
           <t>30-10-2026 02:47 PM</t>
         </is>
       </c>
-      <c r="P29" s="13" t="inlineStr">
+      <c r="P30" s="17" t="inlineStr">
         <is>
           <t>30-10-2026 12:32 PM</t>
         </is>
       </c>
-      <c r="Q29" s="21" t="inlineStr">
+      <c r="Q30" s="18" t="inlineStr">
         <is>
           <t>Registration confirmed upon verified Razorpay payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>TKPL-2026-0134</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Ambavaram Jayasimha Reddy</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>9989280089</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>1992-07-10</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>Middela</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>All-Rounder</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J30" s="18" t="inlineStr">
-        <is>
-          <t>15 years experience</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L30" s="19" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>TKPL-RCPT-2026-0023</t>
-        </is>
-      </c>
-      <c r="N30" s="20" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O30" s="17" t="inlineStr">
-        <is>
-          <t>30-10-2026 12:33 PM</t>
-        </is>
-      </c>
-      <c r="P30" s="17" t="inlineStr">
-        <is>
-          <t>30-10-2026 12:32 PM</t>
-        </is>
-      </c>
-      <c r="Q30" s="18" t="inlineStr">
-        <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -3372,27 +3372,27 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0135</t>
+          <t>TKPL-2026-0134</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>Dhana</t>
+          <t>Ambavaram Jayasimha Reddy</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>9014382907</t>
+          <t>9989280089</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>2005-05-07</t>
+          <t>1992-07-10</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Middela</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="J31" s="21" t="inlineStr">
         <is>
-          <t>U_19 district matches, state jons matches</t>
+          <t>15 years experience</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0024</t>
+          <t>TKPL-RCPT-2026-0023</t>
         </is>
       </c>
       <c r="N31" s="22" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="O31" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:35 PM</t>
+          <t>30-10-2026 12:33 PM</t>
         </is>
       </c>
       <c r="P31" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:34 PM</t>
+          <t>30-10-2026 12:32 PM</t>
         </is>
       </c>
       <c r="Q31" s="21" t="inlineStr">
@@ -3457,32 +3457,32 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0136</t>
+          <t>TKPL-2026-0135</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>YUVARAJU M</t>
+          <t>Dhana</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>9148135125</t>
+          <t>9014382907</t>
         </is>
       </c>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>1994-07-15</t>
+          <t>2005-05-07</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
         <is>
-          <t>Ambavaram</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="J32" s="18" t="inlineStr">
         <is>
-          <t>Playing local tournament s</t>
+          <t>U_19 district matches, state jons matches</t>
         </is>
       </c>
       <c r="K32" s="17" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0025</t>
+          <t>TKPL-RCPT-2026-0024</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="O32" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:36 PM</t>
+          <t>30-10-2026 12:35 PM</t>
         </is>
       </c>
       <c r="P32" s="17" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0137</t>
+          <t>TKPL-2026-0136</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>Gona Mojesh</t>
+          <t>YUVARAJU M</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>9381962853</t>
+          <t>9148135125</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>1994-06-05</t>
+          <t>1994-07-15</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
         <is>
-          <t>Daddanala village proddatur</t>
+          <t>Ambavaram</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="J33" s="21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Playing local tournament s</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0026</t>
+          <t>TKPL-RCPT-2026-0025</t>
         </is>
       </c>
       <c r="N33" s="22" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="O33" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:40 PM</t>
+          <t>30-10-2026 12:36 PM</t>
         </is>
       </c>
       <c r="P33" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:38 PM</t>
+          <t>30-10-2026 12:34 PM</t>
         </is>
       </c>
       <c r="Q33" s="21" t="inlineStr">
@@ -3627,27 +3627,27 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0138</t>
+          <t>TKPL-2026-0137</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>G.karthik</t>
+          <t>Gona Mojesh</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>9059629062</t>
+          <t>9381962853</t>
         </is>
       </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>1994-06-05</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>R.s kondapuram</t>
+          <t>Daddanala village proddatur</t>
         </is>
       </c>
       <c r="G34" s="17" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="J34" s="18" t="inlineStr">
         <is>
-          <t>Yas</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K34" s="17" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="M34" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0037</t>
+          <t>TKPL-RCPT-2026-0026</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="O34" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:06 PM</t>
+          <t>30-10-2026 12:40 PM</t>
         </is>
       </c>
       <c r="P34" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:40 PM</t>
+          <t>30-10-2026 12:38 PM</t>
         </is>
       </c>
       <c r="Q34" s="18" t="inlineStr">
@@ -3712,27 +3712,27 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0139</t>
+          <t>TKPL-2026-0138</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>Ashok Kumar Reddy Gadikota</t>
+          <t>G.karthik</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>6302087695</t>
+          <t>9059629062</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>1995-05-10</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
         <is>
-          <t>Kamalapuram</t>
+          <t>R.s kondapuram</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
@@ -3742,17 +3742,17 @@
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
-          <t>Left-arm Pace</t>
+          <t>Right-arm Pace</t>
         </is>
       </c>
       <c r="J35" s="21" t="inlineStr">
         <is>
-          <t>Lot of tournaments</t>
+          <t>Yas</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0027</t>
+          <t>TKPL-RCPT-2026-0037</t>
         </is>
       </c>
       <c r="N35" s="22" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="O35" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:41 PM</t>
+          <t>30-10-2026 01:06 PM</t>
         </is>
       </c>
       <c r="P35" s="13" t="inlineStr">
@@ -3797,27 +3797,27 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0140</t>
+          <t>TKPL-2026-0139</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>G NAGESWARA</t>
+          <t>Ashok Kumar Reddy Gadikota</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t>9177765054</t>
+          <t>6302087695</t>
         </is>
       </c>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>1993-01-01</t>
+          <t>1995-05-10</t>
         </is>
       </c>
       <c r="F36" s="18" t="inlineStr">
         <is>
-          <t>MAHADEVAPALLI</t>
+          <t>Kamalapuram</t>
         </is>
       </c>
       <c r="G36" s="17" t="inlineStr">
@@ -3827,15 +3827,19 @@
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Spin</t>
-        </is>
-      </c>
-      <c r="J36" s="18" t="inlineStr"/>
+          <t>Left-arm Pace</t>
+        </is>
+      </c>
+      <c r="J36" s="18" t="inlineStr">
+        <is>
+          <t>Lot of tournaments</t>
+        </is>
+      </c>
       <c r="K36" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -3848,7 +3852,7 @@
       </c>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0028</t>
+          <t>TKPL-RCPT-2026-0027</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
@@ -3878,27 +3882,27 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0141</t>
+          <t>TKPL-2026-0140</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>Mukkamalla srinivasula reddy</t>
+          <t>G NAGESWARA</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>6302796593</t>
+          <t>9177765054</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>2001-09-17</t>
+          <t>1993-01-01</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
         <is>
-          <t>Jammalamadugu</t>
+          <t>MAHADEVAPALLI</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
@@ -3913,7 +3917,7 @@
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>Right-arm Spin</t>
         </is>
       </c>
       <c r="J37" s="21" t="inlineStr"/>
@@ -3929,7 +3933,7 @@
       </c>
       <c r="M37" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0073</t>
+          <t>TKPL-RCPT-2026-0028</t>
         </is>
       </c>
       <c r="N37" s="22" t="inlineStr">
@@ -3939,12 +3943,12 @@
       </c>
       <c r="O37" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:30 PM</t>
+          <t>30-10-2026 12:41 PM</t>
         </is>
       </c>
       <c r="P37" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:42 PM</t>
+          <t>30-10-2026 12:40 PM</t>
         </is>
       </c>
       <c r="Q37" s="21" t="inlineStr">
@@ -3959,32 +3963,32 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0142</t>
+          <t>TKPL-2026-0141</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>SHAIK BASHA</t>
+          <t>Mukkamalla srinivasula reddy</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>8886151191</t>
+          <t>6302796593</t>
         </is>
       </c>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>1996-08-15</t>
+          <t>2001-09-17</t>
         </is>
       </c>
       <c r="F38" s="18" t="inlineStr">
         <is>
-          <t>Pandilla Palli (V) LAKKIREDDY PALLI</t>
+          <t>Jammalamadugu</t>
         </is>
       </c>
       <c r="G38" s="17" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
@@ -4010,7 +4014,7 @@
       </c>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0029</t>
+          <t>TKPL-RCPT-2026-0073</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
@@ -4020,12 +4024,12 @@
       </c>
       <c r="O38" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:44 PM</t>
+          <t>30-10-2026 03:30 PM</t>
         </is>
       </c>
       <c r="P38" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:43 PM</t>
+          <t>30-10-2026 12:42 PM</t>
         </is>
       </c>
       <c r="Q38" s="18" t="inlineStr">
@@ -4040,32 +4044,32 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0143</t>
+          <t>TKPL-2026-0142</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>Kondamori Mallikarjuna</t>
+          <t>SHAIK BASHA</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>8919443170</t>
+          <t>8886151191</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>1995-05-15</t>
+          <t>1996-08-15</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
         <is>
-          <t>Surabhi,Nagulaguttapalle</t>
+          <t>Pandilla Palli (V) LAKKIREDDY PALLI</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -4078,11 +4082,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J39" s="21" t="inlineStr">
-        <is>
-          <t>South zone player</t>
-        </is>
-      </c>
+      <c r="J39" s="21" t="inlineStr"/>
       <c r="K39" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M39" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0030</t>
+          <t>TKPL-RCPT-2026-0029</t>
         </is>
       </c>
       <c r="N39" s="22" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O39" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:46 PM</t>
+          <t>30-10-2026 12:44 PM</t>
         </is>
       </c>
       <c r="P39" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:45 PM</t>
+          <t>30-10-2026 12:43 PM</t>
         </is>
       </c>
       <c r="Q39" s="21" t="inlineStr">
@@ -4125,32 +4125,32 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0144</t>
+          <t>TKPL-2026-0143</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Shaik abbas</t>
+          <t>Kondamori Mallikarjuna</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>7569102219</t>
+          <t>8919443170</t>
         </is>
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>2002-01-15</t>
+          <t>1995-05-15</t>
         </is>
       </c>
       <c r="F40" s="18" t="inlineStr">
         <is>
-          <t>Rayachoty</t>
+          <t>Surabhi,Nagulaguttapalle</t>
         </is>
       </c>
       <c r="G40" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="J40" s="18" t="inlineStr">
         <is>
-          <t>Local tournaments</t>
+          <t>South zone player</t>
         </is>
       </c>
       <c r="K40" s="17" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0031</t>
+          <t>TKPL-RCPT-2026-0030</t>
         </is>
       </c>
       <c r="N40" s="20" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O40" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:51 PM</t>
+          <t>30-10-2026 12:46 PM</t>
         </is>
       </c>
       <c r="P40" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:50 PM</t>
+          <t>30-10-2026 12:45 PM</t>
         </is>
       </c>
       <c r="Q40" s="18" t="inlineStr">
@@ -4210,32 +4210,32 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0145</t>
+          <t>TKPL-2026-0144</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>Cheppali Ravi</t>
+          <t>Shaik abbas</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>9703707403</t>
+          <t>7569102219</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>1999-06-14</t>
+          <t>2002-01-15</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
         <is>
-          <t>Porumamilla</t>
+          <t>Rayachoty</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t>10 years experience</t>
+          <t>Local tournaments</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="M41" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0032</t>
+          <t>TKPL-RCPT-2026-0031</t>
         </is>
       </c>
       <c r="N41" s="22" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="O41" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:52 PM</t>
+          <t>30-10-2026 12:51 PM</t>
         </is>
       </c>
       <c r="P41" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:51 PM</t>
+          <t>30-10-2026 12:50 PM</t>
         </is>
       </c>
       <c r="Q41" s="21" t="inlineStr">
@@ -4295,32 +4295,32 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0146</t>
+          <t>TKPL-2026-0145</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>RAJESH KUMAR REDDY KALLURU</t>
+          <t>Cheppali Ravi</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t>9010553383</t>
+          <t>9703707403</t>
         </is>
       </c>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t>1993-05-08</t>
+          <t>1999-06-14</t>
         </is>
       </c>
       <c r="F42" s="18" t="inlineStr">
         <is>
-          <t>YERRAGUNTLA</t>
+          <t>Porumamilla</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="J42" s="18" t="inlineStr">
         <is>
-          <t>Nil</t>
+          <t>10 years experience</t>
         </is>
       </c>
       <c r="K42" s="17" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0033</t>
+          <t>TKPL-RCPT-2026-0032</t>
         </is>
       </c>
       <c r="N42" s="20" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="P42" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:52 PM</t>
+          <t>30-10-2026 12:51 PM</t>
         </is>
       </c>
       <c r="Q42" s="18" t="inlineStr">
@@ -4380,27 +4380,27 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0147</t>
+          <t>TKPL-2026-0146</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
         <is>
-          <t>Vinod Royal PIDEM</t>
+          <t>RAJESH KUMAR REDDY KALLURU</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>9701069113</t>
+          <t>9010553383</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>1998-04-10</t>
+          <t>1993-05-08</t>
         </is>
       </c>
       <c r="F43" s="21" t="inlineStr">
         <is>
-          <t>Guvvalacheruvu</t>
+          <t>YERRAGUNTLA</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="J43" s="21" t="inlineStr">
         <is>
-          <t>I have played many tournaments in Bangalore and Guvvalacheruvu locality</t>
+          <t>Nil</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0042</t>
+          <t>TKPL-RCPT-2026-0033</t>
         </is>
       </c>
       <c r="N43" s="22" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O43" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:21 PM</t>
+          <t>30-10-2026 12:52 PM</t>
         </is>
       </c>
       <c r="P43" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:54 PM</t>
+          <t>30-10-2026 12:52 PM</t>
         </is>
       </c>
       <c r="Q43" s="21" t="inlineStr">
@@ -4465,27 +4465,27 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0148</t>
+          <t>TKPL-2026-0147</t>
         </is>
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>Mola Rama subba reddy</t>
+          <t>Vinod Royal PIDEM</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>8919616379</t>
+          <t>9701069113</t>
         </is>
       </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>2001-09-13</t>
+          <t>1998-04-10</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
         <is>
-          <t>Pendlimarri,ayyavaripalli</t>
+          <t>Guvvalacheruvu</t>
         </is>
       </c>
       <c r="G44" s="17" t="inlineStr">
@@ -4503,7 +4503,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J44" s="18" t="inlineStr"/>
+      <c r="J44" s="18" t="inlineStr">
+        <is>
+          <t>I have played many tournaments in Bangalore and Guvvalacheruvu locality</t>
+        </is>
+      </c>
       <c r="K44" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -4516,7 +4520,7 @@
       </c>
       <c r="M44" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0035</t>
+          <t>TKPL-RCPT-2026-0042</t>
         </is>
       </c>
       <c r="N44" s="20" t="inlineStr">
@@ -4526,12 +4530,12 @@
       </c>
       <c r="O44" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:05 PM</t>
+          <t>30-10-2026 01:21 PM</t>
         </is>
       </c>
       <c r="P44" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:00 PM</t>
+          <t>30-10-2026 12:54 PM</t>
         </is>
       </c>
       <c r="Q44" s="18" t="inlineStr">
@@ -4546,32 +4550,32 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0149</t>
+          <t>TKPL-2026-0148</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>SHAIK shaheed basha</t>
+          <t>Mola Rama subba reddy</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>6300135203</t>
+          <t>8919616379</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>1996-08-12</t>
+          <t>2001-09-13</t>
         </is>
       </c>
       <c r="F45" s="21" t="inlineStr">
         <is>
-          <t>Kamalapuram</t>
+          <t>Pendlimarri,ayyavaripalli</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -4584,11 +4588,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J45" s="21" t="inlineStr">
-        <is>
-          <t>Eenadu tournament 2015-16</t>
-        </is>
-      </c>
+      <c r="J45" s="21" t="inlineStr"/>
       <c r="K45" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="M45" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0034</t>
+          <t>TKPL-RCPT-2026-0035</t>
         </is>
       </c>
       <c r="N45" s="22" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="O45" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:02 PM</t>
+          <t>30-10-2026 01:05 PM</t>
         </is>
       </c>
       <c r="P45" s="13" t="inlineStr">
@@ -4631,47 +4631,47 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0150</t>
+          <t>TKPL-2026-0149</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>GOGULA NAVEEN</t>
+          <t>SHAIK shaheed basha</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>8374450713</t>
+          <t>6300135203</t>
         </is>
       </c>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>2005-06-01</t>
+          <t>1996-08-12</t>
         </is>
       </c>
       <c r="F46" s="18" t="inlineStr">
         <is>
-          <t>Badvel</t>
+          <t>Kamalapuram</t>
         </is>
       </c>
       <c r="G46" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>Left-arm Pace</t>
+          <t>Right-arm Pace</t>
         </is>
       </c>
       <c r="J46" s="18" t="inlineStr">
         <is>
-          <t>Intercollegiate south zone match’s</t>
+          <t>Eenadu tournament 2015-16</t>
         </is>
       </c>
       <c r="K46" s="17" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0038</t>
+          <t>TKPL-RCPT-2026-0034</t>
         </is>
       </c>
       <c r="N46" s="20" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="O46" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:10 PM</t>
+          <t>30-10-2026 01:02 PM</t>
         </is>
       </c>
       <c r="P46" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:04 PM</t>
+          <t>30-10-2026 01:00 PM</t>
         </is>
       </c>
       <c r="Q46" s="18" t="inlineStr">
@@ -4716,45 +4716,49 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0151</t>
+          <t>TKPL-2026-0150</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
         <is>
-          <t>Bovilla govardhan Reddy</t>
+          <t>GOGULA NAVEEN</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>7013387821</t>
+          <t>8374450713</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>1990-09-30</t>
+          <t>2005-06-01</t>
         </is>
       </c>
       <c r="F47" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Badvel</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J47" s="21" t="inlineStr"/>
+          <t>Left-arm Pace</t>
+        </is>
+      </c>
+      <c r="J47" s="21" t="inlineStr">
+        <is>
+          <t>Intercollegiate south zone match’s</t>
+        </is>
+      </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -4767,7 +4771,7 @@
       </c>
       <c r="M47" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0036</t>
+          <t>TKPL-RCPT-2026-0038</t>
         </is>
       </c>
       <c r="N47" s="22" t="inlineStr">
@@ -4777,7 +4781,7 @@
       </c>
       <c r="O47" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:05 PM</t>
+          <t>30-10-2026 01:10 PM</t>
         </is>
       </c>
       <c r="P47" s="13" t="inlineStr">
@@ -4797,32 +4801,32 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0153</t>
+          <t>TKPL-2026-0151</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>Gajaguduru mahammad nurulla</t>
+          <t>Bovilla govardhan Reddy</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t>8328130920</t>
+          <t>7013387821</t>
         </is>
       </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>2005-06-22</t>
+          <t>1990-09-30</t>
         </is>
       </c>
       <c r="F48" s="18" t="inlineStr">
         <is>
-          <t>Narasapuram</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
@@ -4835,11 +4839,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J48" s="18" t="inlineStr">
-        <is>
-          <t>6 years</t>
-        </is>
-      </c>
+      <c r="J48" s="18" t="inlineStr"/>
       <c r="K48" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0039</t>
+          <t>TKPL-RCPT-2026-0036</t>
         </is>
       </c>
       <c r="N48" s="20" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="O48" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:10 PM</t>
+          <t>30-10-2026 01:05 PM</t>
         </is>
       </c>
       <c r="P48" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:09 PM</t>
+          <t>30-10-2026 01:04 PM</t>
         </is>
       </c>
       <c r="Q48" s="18" t="inlineStr">
@@ -4882,32 +4882,32 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0155</t>
+          <t>TKPL-2026-0153</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>K SHIVA</t>
+          <t>Gajaguduru mahammad nurulla</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>9951549753</t>
+          <t>8328130920</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>1995-01-15</t>
+          <t>2005-06-22</t>
         </is>
       </c>
       <c r="F49" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Narasapuram</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -4917,10 +4917,14 @@
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J49" s="21" t="inlineStr"/>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J49" s="21" t="inlineStr">
+        <is>
+          <t>6 years</t>
+        </is>
+      </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -4933,7 +4937,7 @@
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0040</t>
+          <t>TKPL-RCPT-2026-0039</t>
         </is>
       </c>
       <c r="N49" s="22" t="inlineStr">
@@ -4943,12 +4947,12 @@
       </c>
       <c r="O49" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:13 PM</t>
+          <t>30-10-2026 01:10 PM</t>
         </is>
       </c>
       <c r="P49" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:12 PM</t>
+          <t>30-10-2026 01:09 PM</t>
         </is>
       </c>
       <c r="Q49" s="21" t="inlineStr">
@@ -4963,32 +4967,32 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0156</t>
+          <t>TKPL-2026-0155</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>G jaya prakash reddy</t>
+          <t>K SHIVA</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t>8309293988</t>
+          <t>9951549753</t>
         </is>
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>2002-07-25</t>
+          <t>1995-01-15</t>
         </is>
       </c>
       <c r="F50" s="18" t="inlineStr">
         <is>
-          <t>Rajempet</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
@@ -4998,14 +5002,10 @@
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J50" s="18" t="inlineStr">
-        <is>
-          <t>Atbpl</t>
-        </is>
-      </c>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J50" s="18" t="inlineStr"/>
       <c r="K50" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0041</t>
+          <t>TKPL-RCPT-2026-0040</t>
         </is>
       </c>
       <c r="N50" s="20" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="O50" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:15 PM</t>
+          <t>30-10-2026 01:13 PM</t>
         </is>
       </c>
       <c r="P50" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:15 PM</t>
+          <t>30-10-2026 01:12 PM</t>
         </is>
       </c>
       <c r="Q50" s="18" t="inlineStr">
@@ -5048,27 +5048,27 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0157</t>
+          <t>TKPL-2026-0156</t>
         </is>
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>Shaik Rizwan</t>
+          <t>G jaya prakash reddy</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>9703546013</t>
+          <t>8309293988</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>1989-05-08</t>
+          <t>2002-07-25</t>
         </is>
       </c>
       <c r="F51" s="21" t="inlineStr">
         <is>
-          <t>Rayachoty</t>
+          <t>Rajempet</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
@@ -5083,10 +5083,14 @@
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Spin</t>
-        </is>
-      </c>
-      <c r="J51" s="21" t="inlineStr"/>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J51" s="21" t="inlineStr">
+        <is>
+          <t>Atbpl</t>
+        </is>
+      </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5099,7 +5103,7 @@
       </c>
       <c r="M51" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0061</t>
+          <t>TKPL-RCPT-2026-0041</t>
         </is>
       </c>
       <c r="N51" s="22" t="inlineStr">
@@ -5109,17 +5113,17 @@
       </c>
       <c r="O51" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:47 PM</t>
+          <t>30-10-2026 01:15 PM</t>
         </is>
       </c>
       <c r="P51" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:17 PM</t>
+          <t>30-10-2026 01:15 PM</t>
         </is>
       </c>
       <c r="Q51" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -5129,27 +5133,27 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0159</t>
+          <t>TKPL-2026-0157</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>shaik Mynuddin</t>
+          <t>Shaik Rizwan</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t>8885266722</t>
+          <t>9703546013</t>
         </is>
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>1998-06-06</t>
+          <t>1989-05-08</t>
         </is>
       </c>
       <c r="F52" s="18" t="inlineStr">
         <is>
-          <t>Lakkireddy palli (m) ,Rayachoty</t>
+          <t>Rayachoty</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
@@ -5164,14 +5168,10 @@
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J52" s="18" t="inlineStr">
-        <is>
-          <t>MNR cricket tournament, Vijay primier League, friends cricket league etc...</t>
-        </is>
-      </c>
+          <t>Right-arm Spin</t>
+        </is>
+      </c>
+      <c r="J52" s="18" t="inlineStr"/>
       <c r="K52" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0043</t>
+          <t>TKPL-RCPT-2026-0061</t>
         </is>
       </c>
       <c r="N52" s="20" t="inlineStr">
@@ -5194,17 +5194,17 @@
       </c>
       <c r="O52" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:22 PM</t>
+          <t>30-10-2026 02:47 PM</t>
         </is>
       </c>
       <c r="P52" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:22 PM</t>
+          <t>30-10-2026 01:17 PM</t>
         </is>
       </c>
       <c r="Q52" s="18" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -5214,27 +5214,27 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0160</t>
+          <t>TKPL-2026-0159</t>
         </is>
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>Shaik Saddam Hussain</t>
+          <t>shaik Mynuddin</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>8374530338</t>
+          <t>8885266722</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>1995-06-05</t>
+          <t>1998-06-06</t>
         </is>
       </c>
       <c r="F53" s="21" t="inlineStr">
         <is>
-          <t>6-6, Thurakapalli, Gurrappagari Palli(Post), Veeraballi(M),YSR KADAPA (Dt))</t>
+          <t>Lakkireddy palli (m) ,Rayachoty</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
@@ -5252,7 +5252,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J53" s="21" t="inlineStr"/>
+      <c r="J53" s="21" t="inlineStr">
+        <is>
+          <t>MNR cricket tournament, Vijay primier League, friends cricket league etc...</t>
+        </is>
+      </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5265,7 +5269,7 @@
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0044</t>
+          <t>TKPL-RCPT-2026-0043</t>
         </is>
       </c>
       <c r="N53" s="22" t="inlineStr">
@@ -5275,7 +5279,7 @@
       </c>
       <c r="O53" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:23 PM</t>
+          <t>30-10-2026 01:22 PM</t>
         </is>
       </c>
       <c r="P53" s="13" t="inlineStr">
@@ -5295,32 +5299,32 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0161</t>
+          <t>TKPL-2026-0160</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>Jaffar khan phatan</t>
+          <t>Shaik Saddam Hussain</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>9160616545</t>
+          <t>8374530338</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>2001-11-15</t>
+          <t>1995-06-05</t>
         </is>
       </c>
       <c r="F54" s="18" t="inlineStr">
         <is>
-          <t>Nandalur mandal kadapa district</t>
+          <t>6-6, Thurakapalli, Gurrappagari Palli(Post), Veeraballi(M),YSR KADAPA (Dt))</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
@@ -5346,7 +5350,7 @@
       </c>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0045</t>
+          <t>TKPL-RCPT-2026-0044</t>
         </is>
       </c>
       <c r="N54" s="20" t="inlineStr">
@@ -5356,12 +5360,12 @@
       </c>
       <c r="O54" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:27 PM</t>
+          <t>30-10-2026 01:23 PM</t>
         </is>
       </c>
       <c r="P54" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:26 PM</t>
+          <t>30-10-2026 01:22 PM</t>
         </is>
       </c>
       <c r="Q54" s="18" t="inlineStr">
@@ -5376,45 +5380,126 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
+          <t>TKPL-2026-0161</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t>Jaffar khan phatan</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>9160616545</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>2001-11-15</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t>Nandalur mandal kadapa district</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H55" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J55" s="21" t="inlineStr"/>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L55" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M55" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0045</t>
+        </is>
+      </c>
+      <c r="N55" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O55" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 01:27 PM</t>
+        </is>
+      </c>
+      <c r="P55" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 01:26 PM</t>
+        </is>
+      </c>
+      <c r="Q55" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
           <t>TKPL-2026-0162</t>
         </is>
       </c>
-      <c r="C55" s="21" t="inlineStr">
+      <c r="C56" s="18" t="inlineStr">
         <is>
           <t>Mude Shankar naik</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>9502271805</t>
         </is>
       </c>
-      <c r="E55" s="13" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>2008-06-26</t>
         </is>
       </c>
-      <c r="F55" s="21" t="inlineStr">
+      <c r="F56" s="18" t="inlineStr">
         <is>
           <t>Galiveedu</t>
         </is>
       </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="G56" s="17" t="inlineStr">
         <is>
           <t>Batter</t>
         </is>
       </c>
-      <c r="H55" s="13" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J55" s="21" t="inlineStr">
+      <c r="J56" s="18" t="inlineStr">
         <is>
           <t>51(21) 4s-5 6s-3
 50 runs in a limited over match. Super!. See on CricHeroes. https://cricheroes.in/scorecard/26220470/until-unity-club-/peruru-11-vs-ashok-11s
@@ -5424,119 +5509,34 @@
 https://crhero.link/campaign/apps</t>
         </is>
       </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L55" s="19" t="inlineStr">
+      <c r="K56" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L56" s="19" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="M55" s="13" t="inlineStr">
+      <c r="M56" s="17" t="inlineStr">
         <is>
           <t>TKPL-RCPT-2026-0048</t>
         </is>
       </c>
-      <c r="N55" s="22" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O55" s="13" t="inlineStr">
+      <c r="N56" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O56" s="17" t="inlineStr">
         <is>
           <t>30-10-2026 01:45 PM</t>
         </is>
       </c>
-      <c r="P55" s="13" t="inlineStr">
+      <c r="P56" s="17" t="inlineStr">
         <is>
           <t>30-10-2026 01:31 PM</t>
-        </is>
-      </c>
-      <c r="Q55" s="21" t="inlineStr">
-        <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="17" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>TKPL-2026-0163</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
-        <is>
-          <t>Dasari palli Abhishek</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>9390757461</t>
-        </is>
-      </c>
-      <c r="E56" s="17" t="inlineStr">
-        <is>
-          <t>2005-07-19</t>
-        </is>
-      </c>
-      <c r="F56" s="18" t="inlineStr">
-        <is>
-          <t>Porumamilla</t>
-        </is>
-      </c>
-      <c r="G56" s="17" t="inlineStr">
-        <is>
-          <t>Batter</t>
-        </is>
-      </c>
-      <c r="H56" s="17" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
-        <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J56" s="18" t="inlineStr">
-        <is>
-          <t>6years experience</t>
-        </is>
-      </c>
-      <c r="K56" s="17" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L56" s="19" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="M56" s="17" t="inlineStr">
-        <is>
-          <t>TKPL-RCPT-2026-0046</t>
-        </is>
-      </c>
-      <c r="N56" s="20" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O56" s="17" t="inlineStr">
-        <is>
-          <t>30-10-2026 01:43 PM</t>
-        </is>
-      </c>
-      <c r="P56" s="17" t="inlineStr">
-        <is>
-          <t>30-10-2026 01:42 PM</t>
         </is>
       </c>
       <c r="Q56" s="18" t="inlineStr">
@@ -5551,32 +5551,32 @@
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0165</t>
+          <t>TKPL-2026-0163</t>
         </is>
       </c>
       <c r="C57" s="21" t="inlineStr">
         <is>
-          <t>samuel chakravarthy</t>
+          <t>Dasari palli Abhishek</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>9962511777</t>
+          <t>9390757461</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>1983-07-11</t>
+          <t>2005-07-19</t>
         </is>
       </c>
       <c r="F57" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Porumamilla</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
@@ -5589,7 +5589,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J57" s="21" t="inlineStr"/>
+      <c r="J57" s="21" t="inlineStr">
+        <is>
+          <t>6years experience</t>
+        </is>
+      </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5602,7 +5606,7 @@
       </c>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0050</t>
+          <t>TKPL-RCPT-2026-0046</t>
         </is>
       </c>
       <c r="N57" s="22" t="inlineStr">
@@ -5612,12 +5616,12 @@
       </c>
       <c r="O57" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:03 PM</t>
+          <t>30-10-2026 01:43 PM</t>
         </is>
       </c>
       <c r="P57" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:56 PM</t>
+          <t>30-10-2026 01:42 PM</t>
         </is>
       </c>
       <c r="Q57" s="21" t="inlineStr">
@@ -5632,27 +5636,27 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0166</t>
+          <t>TKPL-2026-0165</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>M SYED NASRUDDIN</t>
+          <t>samuel chakravarthy</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t>9494040272</t>
+          <t>9962511777</t>
         </is>
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>1997-08-08</t>
+          <t>1983-07-11</t>
         </is>
       </c>
       <c r="F58" s="18" t="inlineStr">
         <is>
-          <t>PRODDATUR</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G58" s="17" t="inlineStr">
@@ -5670,11 +5674,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J58" s="18" t="inlineStr">
-        <is>
-          <t>I played lot's of tournament all over andhra pradesh</t>
-        </is>
-      </c>
+      <c r="J58" s="18" t="inlineStr"/>
       <c r="K58" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="M58" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0049</t>
+          <t>TKPL-RCPT-2026-0050</t>
         </is>
       </c>
       <c r="N58" s="20" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="O58" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:01 PM</t>
+          <t>30-10-2026 02:03 PM</t>
         </is>
       </c>
       <c r="P58" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:59 PM</t>
+          <t>30-10-2026 01:56 PM</t>
         </is>
       </c>
       <c r="Q58" s="18" t="inlineStr">
@@ -5717,37 +5717,37 @@
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0167</t>
+          <t>TKPL-2026-0166</t>
         </is>
       </c>
       <c r="C59" s="21" t="inlineStr">
         <is>
-          <t>Syed yaseen</t>
+          <t>M SYED NASRUDDIN</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>9542075835</t>
+          <t>9494040272</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>1994-07-24</t>
+          <t>1997-08-08</t>
         </is>
       </c>
       <c r="F59" s="21" t="inlineStr">
         <is>
-          <t>Rajampeta</t>
+          <t>PRODDATUR</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I59" s="13" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="J59" s="21" t="inlineStr">
         <is>
-          <t>RMCL TOURNAMENT 5 TIMES WINNER HAS A CAPTAIN AND MANY TOURNAMENT WINNER IN RAJAMPETA</t>
+          <t>I played lot's of tournament all over andhra pradesh</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0051</t>
+          <t>TKPL-RCPT-2026-0049</t>
         </is>
       </c>
       <c r="N59" s="22" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O59" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:03 PM</t>
+          <t>30-10-2026 02:01 PM</t>
         </is>
       </c>
       <c r="P59" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:02 PM</t>
+          <t>30-10-2026 01:59 PM</t>
         </is>
       </c>
       <c r="Q59" s="21" t="inlineStr">
@@ -5802,37 +5802,37 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0168</t>
+          <t>TKPL-2026-0167</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>Pallapu sai</t>
+          <t>Syed yaseen</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>9014830335</t>
+          <t>9542075835</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>2002-06-14</t>
+          <t>1994-07-24</t>
         </is>
       </c>
       <c r="F60" s="18" t="inlineStr">
         <is>
-          <t>Chinnanandem</t>
+          <t>Rajampeta</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
@@ -5840,7 +5840,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J60" s="18" t="inlineStr"/>
+      <c r="J60" s="18" t="inlineStr">
+        <is>
+          <t>RMCL TOURNAMENT 5 TIMES WINNER HAS A CAPTAIN AND MANY TOURNAMENT WINNER IN RAJAMPETA</t>
+        </is>
+      </c>
       <c r="K60" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5853,7 +5857,7 @@
       </c>
       <c r="M60" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0052</t>
+          <t>TKPL-RCPT-2026-0051</t>
         </is>
       </c>
       <c r="N60" s="20" t="inlineStr">
@@ -5863,12 +5867,12 @@
       </c>
       <c r="O60" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:27 PM</t>
+          <t>30-10-2026 02:03 PM</t>
         </is>
       </c>
       <c r="P60" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:26 PM</t>
+          <t>30-10-2026 02:02 PM</t>
         </is>
       </c>
       <c r="Q60" s="18" t="inlineStr">
@@ -5883,27 +5887,27 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0169</t>
+          <t>TKPL-2026-0168</t>
         </is>
       </c>
       <c r="C61" s="21" t="inlineStr">
         <is>
-          <t>Lavakumar gandikota</t>
+          <t>Pallapu sai</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>9603837873</t>
+          <t>9014830335</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>1995-06-08</t>
+          <t>2002-06-14</t>
         </is>
       </c>
       <c r="F61" s="21" t="inlineStr">
         <is>
-          <t>Rayachoty</t>
+          <t>Chinnanandem</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
@@ -5934,7 +5938,7 @@
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0053</t>
+          <t>TKPL-RCPT-2026-0052</t>
         </is>
       </c>
       <c r="N61" s="22" t="inlineStr">
@@ -5944,12 +5948,12 @@
       </c>
       <c r="O61" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:31 PM</t>
+          <t>30-10-2026 02:27 PM</t>
         </is>
       </c>
       <c r="P61" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:30 PM</t>
+          <t>30-10-2026 02:26 PM</t>
         </is>
       </c>
       <c r="Q61" s="21" t="inlineStr">
@@ -5964,27 +5968,27 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0170</t>
+          <t>TKPL-2026-0169</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>Bhaskar Thirumalakonda</t>
+          <t>Lavakumar gandikota</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>7794902066</t>
+          <t>9603837873</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>2000-10-22</t>
+          <t>1995-06-08</t>
         </is>
       </c>
       <c r="F62" s="18" t="inlineStr">
         <is>
-          <t>Galiveedu</t>
+          <t>Rayachoty</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
@@ -6015,7 +6019,7 @@
       </c>
       <c r="M62" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0054</t>
+          <t>TKPL-RCPT-2026-0053</t>
         </is>
       </c>
       <c r="N62" s="20" t="inlineStr">
@@ -6025,12 +6029,12 @@
       </c>
       <c r="O62" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:32 PM</t>
+          <t>30-10-2026 02:31 PM</t>
         </is>
       </c>
       <c r="P62" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:31 PM</t>
+          <t>30-10-2026 02:30 PM</t>
         </is>
       </c>
       <c r="Q62" s="18" t="inlineStr">
@@ -6045,27 +6049,27 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0171</t>
+          <t>TKPL-2026-0170</t>
         </is>
       </c>
       <c r="C63" s="21" t="inlineStr">
         <is>
-          <t>THALLU IMRAN</t>
+          <t>Bhaskar Thirumalakonda</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>9182994104</t>
+          <t>7794902066</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>1997-07-10</t>
+          <t>2000-10-22</t>
         </is>
       </c>
       <c r="F63" s="21" t="inlineStr">
         <is>
-          <t>Rayachoti</t>
+          <t>Galiveedu</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
@@ -6083,11 +6087,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J63" s="21" t="inlineStr">
-        <is>
-          <t>RPL and local tournaments</t>
-        </is>
-      </c>
+      <c r="J63" s="21" t="inlineStr"/>
       <c r="K63" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0055</t>
+          <t>TKPL-RCPT-2026-0054</t>
         </is>
       </c>
       <c r="N63" s="22" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="O63" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:38 PM</t>
+          <t>30-10-2026 02:32 PM</t>
         </is>
       </c>
       <c r="P63" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:37 PM</t>
+          <t>30-10-2026 02:31 PM</t>
         </is>
       </c>
       <c r="Q63" s="21" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0172</t>
+          <t>TKPL-2026-0171</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>P.munidhra</t>
+          <t>THALLU IMRAN</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>6304924346</t>
+          <t>9182994104</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>2006-05-05</t>
+          <t>1997-07-10</t>
         </is>
       </c>
       <c r="F64" s="18" t="inlineStr">
         <is>
-          <t>Khajipet /pulluru</t>
+          <t>Rayachoti</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Right-arm Pace</t>
         </is>
       </c>
       <c r="J64" s="18" t="inlineStr">
         <is>
-          <t>Playing local Tournaments</t>
+          <t>RPL and local tournaments</t>
         </is>
       </c>
       <c r="K64" s="17" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="M64" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0056</t>
+          <t>TKPL-RCPT-2026-0055</t>
         </is>
       </c>
       <c r="N64" s="20" t="inlineStr">
@@ -6195,12 +6195,12 @@
       </c>
       <c r="O64" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:39 PM</t>
+          <t>30-10-2026 02:38 PM</t>
         </is>
       </c>
       <c r="P64" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:38 PM</t>
+          <t>30-10-2026 02:37 PM</t>
         </is>
       </c>
       <c r="Q64" s="18" t="inlineStr">
@@ -6215,32 +6215,32 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0174</t>
+          <t>TKPL-2026-0172</t>
         </is>
       </c>
       <c r="C65" s="21" t="inlineStr">
         <is>
-          <t>Bandla Nagaraj</t>
+          <t>P.munidhra</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>8639151288</t>
+          <t>6304924346</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>1988-09-24</t>
+          <t>2006-05-05</t>
         </is>
       </c>
       <c r="F65" s="21" t="inlineStr">
         <is>
-          <t>Rajampeta,bhuvagiripalli</t>
+          <t>Khajipet /pulluru</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J65" s="21" t="inlineStr">
         <is>
-          <t>TPL and KPL</t>
+          <t>Playing local Tournaments</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0062</t>
+          <t>TKPL-RCPT-2026-0056</t>
         </is>
       </c>
       <c r="N65" s="22" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="O65" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:49 PM</t>
+          <t>30-10-2026 02:39 PM</t>
         </is>
       </c>
       <c r="P65" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:49 PM</t>
+          <t>30-10-2026 02:38 PM</t>
         </is>
       </c>
       <c r="Q65" s="21" t="inlineStr">
@@ -6300,27 +6300,27 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0175</t>
+          <t>TKPL-2026-0174</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>Kammineni pavan Kumar yadav</t>
+          <t>Bandla Nagaraj</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>7995878278</t>
+          <t>8639151288</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>1998-06-16</t>
+          <t>1988-09-24</t>
         </is>
       </c>
       <c r="F66" s="18" t="inlineStr">
         <is>
-          <t>Rayachoti</t>
+          <t>Rajampeta,bhuvagiripalli</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
@@ -6338,7 +6338,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J66" s="18" t="inlineStr"/>
+      <c r="J66" s="18" t="inlineStr">
+        <is>
+          <t>TPL and KPL</t>
+        </is>
+      </c>
       <c r="K66" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6351,7 +6355,7 @@
       </c>
       <c r="M66" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0063</t>
+          <t>TKPL-RCPT-2026-0062</t>
         </is>
       </c>
       <c r="N66" s="20" t="inlineStr">
@@ -6361,12 +6365,12 @@
       </c>
       <c r="O66" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:00 PM</t>
+          <t>30-10-2026 02:49 PM</t>
         </is>
       </c>
       <c r="P66" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:52 PM</t>
+          <t>30-10-2026 02:49 PM</t>
         </is>
       </c>
       <c r="Q66" s="18" t="inlineStr">
@@ -6381,27 +6385,27 @@
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0176</t>
+          <t>TKPL-2026-0175</t>
         </is>
       </c>
       <c r="C67" s="21" t="inlineStr">
         <is>
-          <t>Mekala Chandravasulu Reddy</t>
+          <t>Kammineni pavan Kumar yadav</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>9493353988</t>
+          <t>7995878278</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>1992-06-08</t>
+          <t>1998-06-16</t>
         </is>
       </c>
       <c r="F67" s="21" t="inlineStr">
         <is>
-          <t>Yerraguntla</t>
+          <t>Rayachoti</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
@@ -6419,11 +6423,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J67" s="21" t="inlineStr">
-        <is>
-          <t>I have played 450 matches on cricheros profile</t>
-        </is>
-      </c>
+      <c r="J67" s="21" t="inlineStr"/>
       <c r="K67" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="M67" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0064</t>
+          <t>TKPL-RCPT-2026-0063</t>
         </is>
       </c>
       <c r="N67" s="22" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="O67" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:11 PM</t>
+          <t>30-10-2026 03:00 PM</t>
         </is>
       </c>
       <c r="P67" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:04 PM</t>
+          <t>30-10-2026 02:52 PM</t>
         </is>
       </c>
       <c r="Q67" s="21" t="inlineStr">
@@ -6466,32 +6466,32 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0178</t>
+          <t>TKPL-2026-0176</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>Shaik Ghouse mohiddin  ( mohid)</t>
+          <t>Mekala Chandravasulu Reddy</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>7997116597</t>
+          <t>9493353988</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>1993-12-27</t>
+          <t>1992-06-08</t>
         </is>
       </c>
       <c r="F68" s="18" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Yerraguntla</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
@@ -6504,7 +6504,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J68" s="18" t="inlineStr"/>
+      <c r="J68" s="18" t="inlineStr">
+        <is>
+          <t>I have played 450 matches on cricheros profile</t>
+        </is>
+      </c>
       <c r="K68" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6517,7 +6521,7 @@
       </c>
       <c r="M68" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0065</t>
+          <t>TKPL-RCPT-2026-0064</t>
         </is>
       </c>
       <c r="N68" s="20" t="inlineStr">
@@ -6527,12 +6531,12 @@
       </c>
       <c r="O68" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:13 PM</t>
+          <t>30-10-2026 03:11 PM</t>
         </is>
       </c>
       <c r="P68" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:12 PM</t>
+          <t>30-10-2026 03:04 PM</t>
         </is>
       </c>
       <c r="Q68" s="18" t="inlineStr">
@@ -6547,22 +6551,22 @@
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0179</t>
+          <t>TKPL-2026-0178</t>
         </is>
       </c>
       <c r="C69" s="21" t="inlineStr">
         <is>
-          <t>Shaik saif..@PINTU</t>
+          <t>Shaik Ghouse mohiddin  ( mohid)</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>8919628160</t>
+          <t>7997116597</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>2000-09-09</t>
+          <t>1993-12-27</t>
         </is>
       </c>
       <c r="F69" s="21" t="inlineStr">
@@ -6572,7 +6576,7 @@
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -6582,14 +6586,10 @@
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J69" s="21" t="inlineStr">
-        <is>
-          <t>KKR..MPL LEAGUES</t>
-        </is>
-      </c>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J69" s="21" t="inlineStr"/>
       <c r="K69" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="M69" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0066</t>
+          <t>TKPL-RCPT-2026-0065</t>
         </is>
       </c>
       <c r="N69" s="22" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="O69" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:14 PM</t>
+          <t>30-10-2026 03:13 PM</t>
         </is>
       </c>
       <c r="P69" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:13 PM</t>
+          <t>30-10-2026 03:12 PM</t>
         </is>
       </c>
       <c r="Q69" s="21" t="inlineStr">
@@ -6632,32 +6632,32 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0180</t>
+          <t>TKPL-2026-0179</t>
         </is>
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>SURENDRA KUMAR YADAV</t>
+          <t>Shaik saif..@PINTU</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>9000555438</t>
+          <t>8919628160</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>1989-06-08</t>
+          <t>2000-09-09</t>
         </is>
       </c>
       <c r="F70" s="18" t="inlineStr">
         <is>
-          <t>KADAPA</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
@@ -6667,12 +6667,12 @@
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J70" s="18" t="inlineStr">
         <is>
-          <t>JOURNALIST TOURNAMENTS</t>
+          <t>KKR..MPL LEAGUES</t>
         </is>
       </c>
       <c r="K70" s="17" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="M70" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0067</t>
+          <t>TKPL-RCPT-2026-0066</t>
         </is>
       </c>
       <c r="N70" s="20" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O70" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:18 PM</t>
+          <t>30-10-2026 03:14 PM</t>
         </is>
       </c>
       <c r="P70" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:17 PM</t>
+          <t>30-10-2026 03:13 PM</t>
         </is>
       </c>
       <c r="Q70" s="18" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0181</t>
+          <t>TKPL-2026-0180</t>
         </is>
       </c>
       <c r="C71" s="21" t="inlineStr">
         <is>
-          <t>BANDELA PRAVEEN KUMAR</t>
+          <t>SURENDRA KUMAR YADAV</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>9493832807</t>
+          <t>9000555438</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>1992-02-29</t>
+          <t>1989-06-08</t>
         </is>
       </c>
       <c r="F71" s="21" t="inlineStr">
         <is>
-          <t>Nandimandalam</t>
+          <t>KADAPA</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="J71" s="21" t="inlineStr">
         <is>
-          <t>I participate in state-wide revenue tournaments as part of the district team representing the Revenue Department.</t>
+          <t>JOURNALIST TOURNAMENTS</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="M71" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0068</t>
+          <t>TKPL-RCPT-2026-0067</t>
         </is>
       </c>
       <c r="N71" s="22" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="P71" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:18 PM</t>
+          <t>30-10-2026 03:17 PM</t>
         </is>
       </c>
       <c r="Q71" s="21" t="inlineStr">
@@ -6802,32 +6802,32 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0182</t>
+          <t>TKPL-2026-0181</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>Bharath Kumar reddy</t>
+          <t>BANDELA PRAVEEN KUMAR</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>7981122958</t>
+          <t>9493832807</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>1992-02-29</t>
         </is>
       </c>
       <c r="F72" s="18" t="inlineStr">
         <is>
-          <t>Chinnamandem</t>
+          <t>Nandimandalam</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H72" s="17" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Right-arm Pace</t>
         </is>
       </c>
       <c r="J72" s="18" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>I participate in state-wide revenue tournaments as part of the district team representing the Revenue Department.</t>
         </is>
       </c>
       <c r="K72" s="17" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="M72" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0069</t>
+          <t>TKPL-RCPT-2026-0068</t>
         </is>
       </c>
       <c r="N72" s="20" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="O72" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:22 PM</t>
+          <t>30-10-2026 03:18 PM</t>
         </is>
       </c>
       <c r="P72" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:21 PM</t>
+          <t>30-10-2026 03:18 PM</t>
         </is>
       </c>
       <c r="Q72" s="18" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0183</t>
+          <t>TKPL-2026-0182</t>
         </is>
       </c>
       <c r="C73" s="21" t="inlineStr">
         <is>
-          <t>Gantenapalli mahesh</t>
+          <t>Bharath Kumar reddy</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>6281951630</t>
+          <t>7981122958</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>1996-06-05</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="F73" s="21" t="inlineStr">
         <is>
-          <t>kadapa</t>
+          <t>Chinnamandem</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
@@ -6922,10 +6922,14 @@
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J73" s="21" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J73" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
       <c r="K73" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6938,7 +6942,7 @@
       </c>
       <c r="M73" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0070</t>
+          <t>TKPL-RCPT-2026-0069</t>
         </is>
       </c>
       <c r="N73" s="22" t="inlineStr">
@@ -6948,12 +6952,12 @@
       </c>
       <c r="O73" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:27 PM</t>
+          <t>30-10-2026 03:22 PM</t>
         </is>
       </c>
       <c r="P73" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:26 PM</t>
+          <t>30-10-2026 03:21 PM</t>
         </is>
       </c>
       <c r="Q73" s="21" t="inlineStr">
@@ -6968,27 +6972,27 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0184</t>
+          <t>TKPL-2026-0183</t>
         </is>
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>CHARU NAGARAJU</t>
+          <t>Gantenapalli mahesh</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>9160446640</t>
+          <t>6281951630</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>1992-04-03</t>
+          <t>1996-06-05</t>
         </is>
       </c>
       <c r="F74" s="18" t="inlineStr">
         <is>
-          <t>KADAPA</t>
+          <t>kadapa</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
@@ -7006,11 +7010,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J74" s="18" t="inlineStr">
-        <is>
-          <t>LOCAL TOURNAMNETS</t>
-        </is>
-      </c>
+      <c r="J74" s="18" t="inlineStr"/>
       <c r="K74" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="M74" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0071</t>
+          <t>TKPL-RCPT-2026-0070</t>
         </is>
       </c>
       <c r="N74" s="20" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="P74" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:27 PM</t>
+          <t>30-10-2026 03:26 PM</t>
         </is>
       </c>
       <c r="Q74" s="18" t="inlineStr">
@@ -7053,32 +7053,32 @@
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0185</t>
+          <t>TKPL-2026-0184</t>
         </is>
       </c>
       <c r="C75" s="21" t="inlineStr">
         <is>
-          <t>U.OBULESU</t>
+          <t>CHARU NAGARAJU</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>9398778303</t>
+          <t>9160446640</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>1997-05-16</t>
+          <t>1992-04-03</t>
         </is>
       </c>
       <c r="F75" s="21" t="inlineStr">
         <is>
-          <t>Lakkireddipalli</t>
+          <t>KADAPA</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H75" s="13" t="inlineStr">
@@ -7091,7 +7091,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J75" s="21" t="inlineStr"/>
+      <c r="J75" s="21" t="inlineStr">
+        <is>
+          <t>LOCAL TOURNAMNETS</t>
+        </is>
+      </c>
       <c r="K75" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7104,7 +7108,7 @@
       </c>
       <c r="M75" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0077</t>
+          <t>TKPL-RCPT-2026-0071</t>
         </is>
       </c>
       <c r="N75" s="22" t="inlineStr">
@@ -7114,17 +7118,17 @@
       </c>
       <c r="O75" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:50 PM</t>
+          <t>30-10-2026 03:27 PM</t>
         </is>
       </c>
       <c r="P75" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:29 PM</t>
+          <t>30-10-2026 03:27 PM</t>
         </is>
       </c>
       <c r="Q75" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7134,32 +7138,32 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0186</t>
+          <t>TKPL-2026-0185</t>
         </is>
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>Dinesh Don Don</t>
+          <t>U.OBULESU</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t>7386474099</t>
+          <t>9398778303</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>2000-11-25</t>
+          <t>1997-05-16</t>
         </is>
       </c>
       <c r="F76" s="18" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Lakkireddipalli</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
@@ -7172,11 +7176,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J76" s="18" t="inlineStr">
-        <is>
-          <t>Played Big Tournaments</t>
-        </is>
-      </c>
+      <c r="J76" s="18" t="inlineStr"/>
       <c r="K76" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0078</t>
+          <t>TKPL-RCPT-2026-0077</t>
         </is>
       </c>
       <c r="N76" s="20" t="inlineStr">
@@ -7219,22 +7219,22 @@
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0187</t>
+          <t>TKPL-2026-0186</t>
         </is>
       </c>
       <c r="C77" s="21" t="inlineStr">
         <is>
-          <t>Danger Man Ravi</t>
+          <t>Dinesh Don Don</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>9052561634</t>
+          <t>7386474099</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>2000-01-13</t>
+          <t>2000-11-25</t>
         </is>
       </c>
       <c r="F77" s="21" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="J77" s="21" t="inlineStr">
         <is>
-          <t>Tournament experience 15 years</t>
+          <t>Played Big Tournaments</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="M77" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0074</t>
+          <t>TKPL-RCPT-2026-0078</t>
         </is>
       </c>
       <c r="N77" s="22" t="inlineStr">
@@ -7284,17 +7284,17 @@
       </c>
       <c r="O77" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:32 PM</t>
+          <t>30-10-2026 03:50 PM</t>
         </is>
       </c>
       <c r="P77" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:31 PM</t>
+          <t>30-10-2026 03:29 PM</t>
         </is>
       </c>
       <c r="Q77" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7304,22 +7304,22 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0188</t>
+          <t>TKPL-2026-0187</t>
         </is>
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>Crazy boy mp</t>
+          <t>Danger Man Ravi</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>9000814023</t>
+          <t>9052561634</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>1995-08-22</t>
+          <t>2000-01-13</t>
         </is>
       </c>
       <c r="F78" s="18" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
@@ -7342,7 +7342,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J78" s="18" t="inlineStr"/>
+      <c r="J78" s="18" t="inlineStr">
+        <is>
+          <t>Tournament experience 15 years</t>
+        </is>
+      </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7355,7 +7359,7 @@
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0076</t>
+          <t>TKPL-RCPT-2026-0074</t>
         </is>
       </c>
       <c r="N78" s="20" t="inlineStr">
@@ -7365,7 +7369,7 @@
       </c>
       <c r="O78" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:50 PM</t>
+          <t>30-10-2026 03:32 PM</t>
         </is>
       </c>
       <c r="P78" s="17" t="inlineStr">
@@ -7375,7 +7379,7 @@
       </c>
       <c r="Q78" s="18" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7385,22 +7389,22 @@
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0189</t>
+          <t>TKPL-2026-0188</t>
         </is>
       </c>
       <c r="C79" s="21" t="inlineStr">
         <is>
-          <t>RAJA</t>
+          <t>Crazy boy mp</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>9398317906</t>
+          <t>9000814023</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>1999-09-15</t>
+          <t>1995-08-22</t>
         </is>
       </c>
       <c r="F79" s="21" t="inlineStr">
@@ -7410,7 +7414,7 @@
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H79" s="13" t="inlineStr">
@@ -7436,7 +7440,7 @@
       </c>
       <c r="M79" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0075</t>
+          <t>TKPL-RCPT-2026-0076</t>
         </is>
       </c>
       <c r="N79" s="22" t="inlineStr">
@@ -7446,17 +7450,17 @@
       </c>
       <c r="O79" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:47 PM</t>
+          <t>30-10-2026 03:50 PM</t>
         </is>
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:46 PM</t>
+          <t>30-10-2026 03:31 PM</t>
         </is>
       </c>
       <c r="Q79" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7466,32 +7470,32 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0190</t>
+          <t>TKPL-2026-0189</t>
         </is>
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>Nachu.vinodkumar</t>
+          <t>RAJA</t>
         </is>
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t>8499806339</t>
+          <t>9398317906</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>1995-07-10</t>
+          <t>1999-09-15</t>
         </is>
       </c>
       <c r="F80" s="18" t="inlineStr">
         <is>
-          <t>Annamayya district.galiveedu.</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G80" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H80" s="17" t="inlineStr">
@@ -7501,14 +7505,10 @@
       </c>
       <c r="I80" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Spin</t>
-        </is>
-      </c>
-      <c r="J80" s="18" t="inlineStr">
-        <is>
-          <t>ATPBL Kadapa king team. south zone Mumbai club. International matches Nepal premier leag</t>
-        </is>
-      </c>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J80" s="18" t="inlineStr"/>
       <c r="K80" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0079</t>
+          <t>TKPL-RCPT-2026-0075</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="O80" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:54 PM</t>
+          <t>30-10-2026 03:47 PM</t>
         </is>
       </c>
       <c r="P80" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:54 PM</t>
+          <t>30-10-2026 03:46 PM</t>
         </is>
       </c>
       <c r="Q80" s="18" t="inlineStr">
@@ -7551,32 +7551,32 @@
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0192</t>
+          <t>TKPL-2026-0190</t>
         </is>
       </c>
       <c r="C81" s="21" t="inlineStr">
         <is>
-          <t>D  Nagarjuna Reddy</t>
+          <t>Nachu.vinodkumar</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>7396440670</t>
+          <t>8499806339</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>2008-06-16</t>
+          <t>1995-07-10</t>
         </is>
       </c>
       <c r="F81" s="21" t="inlineStr">
         <is>
-          <t>Chakrayapeta town</t>
+          <t>Annamayya district.galiveedu.</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>Right-arm Spin</t>
         </is>
       </c>
       <c r="J81" s="21" t="inlineStr">
         <is>
-          <t>Chakrayapeta  youth tournament</t>
+          <t>ATPBL Kadapa king team. south zone Mumbai club. International matches Nepal premier leag</t>
         </is>
       </c>
       <c r="K81" s="13" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="M81" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0080</t>
+          <t>TKPL-RCPT-2026-0079</t>
         </is>
       </c>
       <c r="N81" s="22" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O81" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:06 PM</t>
+          <t>30-10-2026 03:54 PM</t>
         </is>
       </c>
       <c r="P81" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:04 PM</t>
+          <t>30-10-2026 03:54 PM</t>
         </is>
       </c>
       <c r="Q81" s="21" t="inlineStr">
@@ -7636,27 +7636,27 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0193</t>
+          <t>TKPL-2026-0191</t>
         </is>
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>MOTAPOTHULA VAMSI (PANT)</t>
+          <t>Giri</t>
         </is>
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t>8309585550</t>
+          <t>7989571634</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>2002-04-06</t>
+          <t>1997-06-02</t>
         </is>
       </c>
       <c r="F82" s="18" t="inlineStr">
         <is>
-          <t>SAVISETTIPALLI</t>
+          <t>Vempalli</t>
         </is>
       </c>
       <c r="G82" s="17" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>Left-arm Pace</t>
         </is>
       </c>
       <c r="J82" s="18" t="inlineStr">
         <is>
-          <t>6years experience many trophies win</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="K82" s="17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0081</t>
+          <t>TKPL-RCPT-2026-0088</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="O82" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:06 PM</t>
+          <t>30-10-2026 04:30 PM</t>
         </is>
       </c>
       <c r="P82" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:05 PM</t>
+          <t>30-10-2026 03:56 PM</t>
         </is>
       </c>
       <c r="Q82" s="18" t="inlineStr">
@@ -7721,32 +7721,32 @@
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0194</t>
+          <t>TKPL-2026-0192</t>
         </is>
       </c>
       <c r="C83" s="21" t="inlineStr">
         <is>
-          <t>ARSHAD PATAN</t>
+          <t>D  Nagarjuna Reddy</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>8309771127</t>
+          <t>7396440670</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>2007-07-09</t>
+          <t>2008-06-16</t>
         </is>
       </c>
       <c r="F83" s="21" t="inlineStr">
         <is>
-          <t>Kadapa: ayesha shool near pedda darga</t>
+          <t>Chakrayapeta town</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
@@ -7761,8 +7761,7 @@
       </c>
       <c r="J83" s="21" t="inlineStr">
         <is>
-          <t>ATBPL-1
-ANDHRA TENNIS BALL PERMIER LEAUGE</t>
+          <t>Chakrayapeta  youth tournament</t>
         </is>
       </c>
       <c r="K83" s="13" t="inlineStr">
@@ -7777,7 +7776,7 @@
       </c>
       <c r="M83" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0082</t>
+          <t>TKPL-RCPT-2026-0080</t>
         </is>
       </c>
       <c r="N83" s="22" t="inlineStr">
@@ -7787,12 +7786,12 @@
       </c>
       <c r="O83" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:11 PM</t>
+          <t>30-10-2026 04:06 PM</t>
         </is>
       </c>
       <c r="P83" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:09 PM</t>
+          <t>30-10-2026 04:04 PM</t>
         </is>
       </c>
       <c r="Q83" s="21" t="inlineStr">
@@ -7807,27 +7806,27 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0195</t>
+          <t>TKPL-2026-0193</t>
         </is>
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>M SUBBA REDDY</t>
+          <t>MOTAPOTHULA VAMSI (PANT)</t>
         </is>
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t>9052632763</t>
+          <t>8309585550</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>1987-06-06</t>
+          <t>2002-04-06</t>
         </is>
       </c>
       <c r="F84" s="18" t="inlineStr">
         <is>
-          <t>Khajipet</t>
+          <t>SAVISETTIPALLI</t>
         </is>
       </c>
       <c r="G84" s="17" t="inlineStr">
@@ -7837,7 +7836,7 @@
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I84" s="17" t="inlineStr">
@@ -7847,7 +7846,7 @@
       </c>
       <c r="J84" s="18" t="inlineStr">
         <is>
-          <t>Nill</t>
+          <t>6years experience many trophies win</t>
         </is>
       </c>
       <c r="K84" s="17" t="inlineStr">
@@ -7862,7 +7861,7 @@
       </c>
       <c r="M84" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0083</t>
+          <t>TKPL-RCPT-2026-0081</t>
         </is>
       </c>
       <c r="N84" s="20" t="inlineStr">
@@ -7872,12 +7871,12 @@
       </c>
       <c r="O84" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:15 PM</t>
+          <t>30-10-2026 04:06 PM</t>
         </is>
       </c>
       <c r="P84" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:14 PM</t>
+          <t>30-10-2026 04:05 PM</t>
         </is>
       </c>
       <c r="Q84" s="18" t="inlineStr">
@@ -7892,83 +7891,505 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
+          <t>TKPL-2026-0194</t>
+        </is>
+      </c>
+      <c r="C85" s="21" t="inlineStr">
+        <is>
+          <t>ARSHAD PATAN</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>8309771127</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>2007-07-09</t>
+        </is>
+      </c>
+      <c r="F85" s="21" t="inlineStr">
+        <is>
+          <t>Kadapa: ayesha shool near pedda darga</t>
+        </is>
+      </c>
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J85" s="21" t="inlineStr">
+        <is>
+          <t>ATBPL-1
+ANDHRA TENNIS BALL PERMIER LEAUGE</t>
+        </is>
+      </c>
+      <c r="K85" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L85" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M85" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0082</t>
+        </is>
+      </c>
+      <c r="N85" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O85" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:11 PM</t>
+        </is>
+      </c>
+      <c r="P85" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:09 PM</t>
+        </is>
+      </c>
+      <c r="Q85" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0195</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>M SUBBA REDDY</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>9052632763</t>
+        </is>
+      </c>
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>1987-06-06</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="inlineStr">
+        <is>
+          <t>Khajipet</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I86" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J86" s="18" t="inlineStr">
+        <is>
+          <t>Nill</t>
+        </is>
+      </c>
+      <c r="K86" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L86" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M86" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0083</t>
+        </is>
+      </c>
+      <c r="N86" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O86" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:15 PM</t>
+        </is>
+      </c>
+      <c r="P86" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:14 PM</t>
+        </is>
+      </c>
+      <c r="Q86" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="13" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
           <t>TKPL-2026-0196</t>
         </is>
       </c>
-      <c r="C85" s="21" t="inlineStr">
+      <c r="C87" s="21" t="inlineStr">
         <is>
           <t>Eswar Beema</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr">
+      <c r="D87" s="13" t="inlineStr">
         <is>
           <t>7337007666</t>
         </is>
       </c>
-      <c r="E85" s="13" t="inlineStr">
+      <c r="E87" s="13" t="inlineStr">
         <is>
           <t>1993-04-04</t>
         </is>
       </c>
-      <c r="F85" s="21" t="inlineStr">
+      <c r="F87" s="21" t="inlineStr">
         <is>
           <t>Kamalapuram</t>
         </is>
       </c>
-      <c r="G85" s="13" t="inlineStr">
+      <c r="G87" s="13" t="inlineStr">
         <is>
           <t>All-Rounder</t>
         </is>
       </c>
-      <c r="H85" s="13" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
+      <c r="H87" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
         <is>
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J85" s="21" t="inlineStr"/>
-      <c r="K85" s="13" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L85" s="19" t="inlineStr">
+      <c r="J87" s="21" t="inlineStr"/>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L87" s="19" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="M85" s="13" t="inlineStr">
+      <c r="M87" s="13" t="inlineStr">
         <is>
           <t>TKPL-RCPT-2026-0084</t>
         </is>
       </c>
-      <c r="N85" s="22" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O85" s="13" t="inlineStr">
+      <c r="N87" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O87" s="13" t="inlineStr">
         <is>
           <t>30-10-2026 04:17 PM</t>
         </is>
       </c>
-      <c r="P85" s="13" t="inlineStr">
+      <c r="P87" s="13" t="inlineStr">
         <is>
           <t>30-10-2026 04:16 PM</t>
         </is>
       </c>
-      <c r="Q85" s="21" t="inlineStr">
+      <c r="Q87" s="21" t="inlineStr">
         <is>
           <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="17" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0197</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>Sameer</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>7013094749</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>2002-10-08</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>Yerraguntla</t>
+        </is>
+      </c>
+      <c r="G88" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>Left Hand</t>
+        </is>
+      </c>
+      <c r="I88" s="17" t="inlineStr">
+        <is>
+          <t>Left-arm Spin</t>
+        </is>
+      </c>
+      <c r="J88" s="18" t="inlineStr">
+        <is>
+          <t>I played lots of tournaments I’m a player of the 7s x1 team</t>
+        </is>
+      </c>
+      <c r="K88" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L88" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M88" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0087</t>
+        </is>
+      </c>
+      <c r="N88" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O88" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:29 PM</t>
+        </is>
+      </c>
+      <c r="P88" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:26 PM</t>
+        </is>
+      </c>
+      <c r="Q88" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="13" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0198</t>
+        </is>
+      </c>
+      <c r="C89" s="21" t="inlineStr">
+        <is>
+          <t>Barigela Suvarthaiah</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>8125231723</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>1989-06-25</t>
+        </is>
+      </c>
+      <c r="F89" s="21" t="inlineStr">
+        <is>
+          <t>RTPP</t>
+        </is>
+      </c>
+      <c r="G89" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H89" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J89" s="21" t="inlineStr"/>
+      <c r="K89" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L89" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M89" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0086</t>
+        </is>
+      </c>
+      <c r="N89" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O89" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:28 PM</t>
+        </is>
+      </c>
+      <c r="P89" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:27 PM</t>
+        </is>
+      </c>
+      <c r="Q89" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="17" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0199</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>krishnareddy sirigireddy</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>9177757989</t>
+        </is>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>1985-05-30</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J90" s="18" t="inlineStr">
+        <is>
+          <t>Rayalasima cricket  tournament winner</t>
+        </is>
+      </c>
+      <c r="K90" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L90" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M90" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0089</t>
+        </is>
+      </c>
+      <c r="N90" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O90" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:40 PM</t>
+        </is>
+      </c>
+      <c r="P90" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:29 PM</t>
+        </is>
+      </c>
+      <c r="Q90" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q85"/>
+  <autoFilter ref="A1:Q90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7979,7 +8400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8175,27 +8596,27 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0115</t>
+          <t>TKPL-2026-0122</t>
         </is>
       </c>
       <c r="C3" s="21" t="inlineStr">
         <is>
-          <t>ASHOK ROYAL</t>
+          <t>B VINOD KUMAR REDDY</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>8121314001</t>
+          <t>8500849901</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>1996-06-28</t>
+          <t>1993-04-10</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t>RAJAMPET</t>
+          <t>Pulivendula</t>
         </is>
       </c>
       <c r="G3" s="13" t="inlineStr">
@@ -8213,11 +8634,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t>MRNS 11s</t>
-        </is>
-      </c>
+      <c r="J3" s="21" t="inlineStr"/>
       <c r="K3" s="13" t="inlineStr">
         <is>
           <t>Submitted</t>
@@ -8245,7 +8662,7 @@
       </c>
       <c r="P3" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:14 PM</t>
+          <t>30-10-2026 12:17 PM</t>
         </is>
       </c>
       <c r="Q3" s="21" t="inlineStr">
@@ -8260,32 +8677,32 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0122</t>
+          <t>TKPL-2026-0125</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>B VINOD KUMAR REDDY</t>
+          <t>M SYED NASRUDDIN</t>
         </is>
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>8500849901</t>
+          <t>9949486154</t>
         </is>
       </c>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>1993-04-10</t>
+          <t>1997-08-08</t>
         </is>
       </c>
       <c r="F4" s="18" t="inlineStr">
         <is>
-          <t>Pulivendula</t>
+          <t>Proddatur</t>
         </is>
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
@@ -8298,7 +8715,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr"/>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>All indian level tournament,  State level tournament, rayalaseema level tournament, district level tournament lot's of experience in all type of tournament and pravite matches alhamdulillah</t>
+        </is>
+      </c>
       <c r="K4" s="17" t="inlineStr">
         <is>
           <t>Submitted</t>
@@ -8326,7 +8747,7 @@
       </c>
       <c r="P4" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:17 PM</t>
+          <t>30-10-2026 12:18 PM</t>
         </is>
       </c>
       <c r="Q4" s="18" t="inlineStr">
@@ -8341,32 +8762,32 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0125</t>
+          <t>TKPL-2026-0130</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>M SYED NASRUDDIN</t>
+          <t>Vulasala Bharath</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>9949486154</t>
+          <t>7995250457</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>1997-08-08</t>
+          <t>2008-05-25</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t>Proddatur</t>
+          <t>GALIVEEDU</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -8381,7 +8802,7 @@
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t>All indian level tournament,  State level tournament, rayalaseema level tournament, district level tournament lot's of experience in all type of tournament and pravite matches alhamdulillah</t>
+          <t>Galiveedu tournament</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -8411,7 +8832,7 @@
       </c>
       <c r="P5" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 12:18 PM</t>
+          <t>30-10-2026 12:28 PM</t>
         </is>
       </c>
       <c r="Q5" s="21" t="inlineStr">
@@ -8426,27 +8847,27 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0130</t>
+          <t>TKPL-2026-0152</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>Vulasala Bharath</t>
+          <t>Niranjan Kumar</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>7995250457</t>
+          <t>7032538123</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>2008-05-25</t>
+          <t>2001-05-05</t>
         </is>
       </c>
       <c r="F6" s="18" t="inlineStr">
         <is>
-          <t>GALIVEEDU</t>
+          <t>T sundupalli</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -8461,14 +8882,10 @@
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>Galiveedu tournament</t>
-        </is>
-      </c>
+          <t>Left-arm Pace</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr"/>
       <c r="K6" s="17" t="inlineStr">
         <is>
           <t>Submitted</t>
@@ -8496,7 +8913,7 @@
       </c>
       <c r="P6" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 12:28 PM</t>
+          <t>30-10-2026 01:06 PM</t>
         </is>
       </c>
       <c r="Q6" s="18" t="inlineStr">
@@ -8511,27 +8928,27 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0152</t>
+          <t>TKPL-2026-0154</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>Niranjan Kumar</t>
+          <t>Venkatakumar S</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7032538123</t>
+          <t>9390667626</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>2001-05-05</t>
+          <t>2002-02-04</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t>T sundupalli</t>
+          <t>Rayachoty  vemaplli   road B T palli</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -8577,7 +8994,7 @@
       </c>
       <c r="P7" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:06 PM</t>
+          <t>30-10-2026 01:11 PM</t>
         </is>
       </c>
       <c r="Q7" s="21" t="inlineStr">
@@ -8592,32 +9009,32 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0154</t>
+          <t>TKPL-2026-0158</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>Venkatakumar S</t>
+          <t>Shaikbabaji</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>9390667626</t>
+          <t>9885626641</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>2002-02-04</t>
+          <t>1996-01-17</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">
         <is>
-          <t>Rayachoty  vemaplli   road B T palli</t>
+          <t>Nagulaguttapalli</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
@@ -8627,10 +9044,14 @@
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>Left-arm Pace</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr"/>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>I have  local tournaments  experience</t>
+        </is>
+      </c>
       <c r="K8" s="17" t="inlineStr">
         <is>
           <t>Submitted</t>
@@ -8658,7 +9079,7 @@
       </c>
       <c r="P8" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:11 PM</t>
+          <t>30-10-2026 01:19 PM</t>
         </is>
       </c>
       <c r="Q8" s="18" t="inlineStr">
@@ -8673,32 +9094,32 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0158</t>
+          <t>TKPL-2026-0164</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>Shaikbabaji</t>
+          <t>Bhanu prakash</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>9885626641</t>
+          <t>9100859612</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>1996-01-17</t>
+          <t>2008-09-21</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t>Nagulaguttapalli</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -8713,7 +9134,7 @@
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t>I have  local tournaments  experience</t>
+          <t>Renadu titians and pai viecory tirupati</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -8743,7 +9164,7 @@
       </c>
       <c r="P9" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:19 PM</t>
+          <t>30-10-2026 01:49 PM</t>
         </is>
       </c>
       <c r="Q9" s="21" t="inlineStr">
@@ -8758,49 +9179,45 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0164</t>
+          <t>TKPL-2026-0173</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>Bhanu prakash</t>
+          <t>Yellutla ravikumar naidu</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>9100859612</t>
+          <t>9705490252</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>2008-09-21</t>
+          <t>2005-03-16</t>
         </is>
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Chinamandam</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t>Renadu titians and pai viecory tirupati</t>
-        </is>
-      </c>
+          <t>Left-arm Spin</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="inlineStr"/>
       <c r="K10" s="17" t="inlineStr">
         <is>
           <t>Submitted</t>
@@ -8828,7 +9245,7 @@
       </c>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:49 PM</t>
+          <t>30-10-2026 02:48 PM</t>
         </is>
       </c>
       <c r="Q10" s="18" t="inlineStr">
@@ -8843,22 +9260,22 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0173</t>
+          <t>TKPL-2026-0177</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>Yellutla ravikumar naidu</t>
+          <t>Yellutla Sree hari naidu</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>9705490252</t>
+          <t>6281999214</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>2005-03-16</t>
+          <t>2009-04-10</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -8873,12 +9290,12 @@
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>Left-arm Spin</t>
+          <t>Right-arm Pace</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr"/>
@@ -8909,7 +9326,7 @@
       </c>
       <c r="P11" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:48 PM</t>
+          <t>30-10-2026 03:06 PM</t>
         </is>
       </c>
       <c r="Q11" s="21" t="inlineStr">
@@ -8918,174 +9335,8 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>TKPL-2026-0177</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>Yellutla Sree hari naidu</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>6281999214</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>2009-04-10</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>Chinamandam</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>All-Rounder</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J12" s="18" t="inlineStr"/>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L12" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P12" s="17" t="inlineStr">
-        <is>
-          <t>30-10-2026 03:06 PM</t>
-        </is>
-      </c>
-      <c r="Q12" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>TKPL-2026-0191</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>Giri</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>7989571634</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>1997-06-02</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>Vempalli</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>All-Rounder</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>Left Hand</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>Left-arm Pace</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t>5 years</t>
-        </is>
-      </c>
-      <c r="K13" s="13" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L13" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="M13" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N13" s="22" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O13" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P13" s="13" t="inlineStr">
-        <is>
-          <t>30-10-2026 03:56 PM</t>
-        </is>
-      </c>
-      <c r="Q13" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q13"/>
+  <autoFilter ref="A1:Q11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9096,7 +9347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q97"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10406,17 +10657,17 @@
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L16" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L16" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M16" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TKPL-RCPT-2026-0085</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -10426,7 +10677,7 @@
       </c>
       <c r="O16" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30-10-2026 04:27 PM</t>
         </is>
       </c>
       <c r="P16" s="17" t="inlineStr">
@@ -10436,7 +10687,7 @@
       </c>
       <c r="Q16" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -16768,17 +17019,17 @@
       </c>
       <c r="K92" s="17" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L92" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L92" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M92" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TKPL-RCPT-2026-0088</t>
         </is>
       </c>
       <c r="N92" s="20" t="inlineStr">
@@ -16788,7 +17039,7 @@
       </c>
       <c r="O92" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30-10-2026 04:30 PM</t>
         </is>
       </c>
       <c r="P92" s="17" t="inlineStr">
@@ -16798,7 +17049,7 @@
       </c>
       <c r="Q92" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -17224,8 +17475,259 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="17" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0197</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>Sameer</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>7013094749</t>
+        </is>
+      </c>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>2002-10-08</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>Yerraguntla</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H98" s="17" t="inlineStr">
+        <is>
+          <t>Left Hand</t>
+        </is>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>Left-arm Spin</t>
+        </is>
+      </c>
+      <c r="J98" s="18" t="inlineStr">
+        <is>
+          <t>I played lots of tournaments I’m a player of the 7s x1 team</t>
+        </is>
+      </c>
+      <c r="K98" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L98" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M98" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0087</t>
+        </is>
+      </c>
+      <c r="N98" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O98" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:29 PM</t>
+        </is>
+      </c>
+      <c r="P98" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:26 PM</t>
+        </is>
+      </c>
+      <c r="Q98" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="13" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0198</t>
+        </is>
+      </c>
+      <c r="C99" s="21" t="inlineStr">
+        <is>
+          <t>Barigela Suvarthaiah</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>8125231723</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="inlineStr">
+        <is>
+          <t>1989-06-25</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="inlineStr">
+        <is>
+          <t>RTPP</t>
+        </is>
+      </c>
+      <c r="G99" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H99" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J99" s="21" t="inlineStr"/>
+      <c r="K99" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L99" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M99" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0086</t>
+        </is>
+      </c>
+      <c r="N99" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O99" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:28 PM</t>
+        </is>
+      </c>
+      <c r="P99" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:27 PM</t>
+        </is>
+      </c>
+      <c r="Q99" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0199</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>krishnareddy sirigireddy</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="inlineStr">
+        <is>
+          <t>9177757989</t>
+        </is>
+      </c>
+      <c r="E100" s="17" t="inlineStr">
+        <is>
+          <t>1985-05-30</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H100" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J100" s="18" t="inlineStr">
+        <is>
+          <t>Rayalasima cricket  tournament winner</t>
+        </is>
+      </c>
+      <c r="K100" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L100" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M100" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0089</t>
+        </is>
+      </c>
+      <c r="N100" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O100" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:40 PM</t>
+        </is>
+      </c>
+      <c r="P100" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:29 PM</t>
+        </is>
+      </c>
+      <c r="Q100" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q97"/>
+  <autoFilter ref="A1:Q100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/TKPL_Registered_Players.xlsx
+++ b/reports/TKPL_Registered_Players.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Summary Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Approved &amp; Verified (89)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Payment Pending (10)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="All Registrations (99)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Approved &amp; Verified (109)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Payment Pending (8)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All Registrations (117)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Approved &amp; Verified (89)'!$A$1:$Q$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Payment Pending (10)'!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Registrations (99)'!$A$1:$Q$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Approved &amp; Verified (109)'!$A$1:$Q$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Payment Pending (8)'!$A$1:$Q$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Registrations (117)'!$A$1:$Q$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Live Roster Report — Generated on 30 Oct 2026, 04:45 PM IST</t>
+          <t>Live Roster Report — Generated on 30 Oct 2026, 08:35 PM IST</t>
         </is>
       </c>
     </row>
@@ -697,25 +697,25 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>109</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>₹35,511</t>
+          <t>₹43,491</t>
         </is>
       </c>
     </row>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>0</v>
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -803,13 +803,13 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="13" t="n">
-        <v>4</v>
-      </c>
       <c r="D13" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q90"/>
+  <dimension ref="A1:Q110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4882,32 +4882,32 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0153</t>
+          <t>TKPL-2026-0152</t>
         </is>
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>Gajaguduru mahammad nurulla</t>
+          <t>Niranjan Kumar</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>8328130920</t>
+          <t>7032538123</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>2005-06-22</t>
+          <t>2001-05-05</t>
         </is>
       </c>
       <c r="F49" s="21" t="inlineStr">
         <is>
-          <t>Narasapuram</t>
+          <t>T sundupalli</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -4917,14 +4917,10 @@
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J49" s="21" t="inlineStr">
-        <is>
-          <t>6 years</t>
-        </is>
-      </c>
+          <t>Left-arm Pace</t>
+        </is>
+      </c>
+      <c r="J49" s="21" t="inlineStr"/>
       <c r="K49" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -4937,7 +4933,7 @@
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0039</t>
+          <t>TKPL-RCPT-2026-0109</t>
         </is>
       </c>
       <c r="N49" s="22" t="inlineStr">
@@ -4947,12 +4943,12 @@
       </c>
       <c r="O49" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:10 PM</t>
+          <t>30-10-2026 08:30 PM</t>
         </is>
       </c>
       <c r="P49" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:09 PM</t>
+          <t>30-10-2026 01:06 PM</t>
         </is>
       </c>
       <c r="Q49" s="21" t="inlineStr">
@@ -4967,32 +4963,32 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0155</t>
+          <t>TKPL-2026-0153</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>K SHIVA</t>
+          <t>Gajaguduru mahammad nurulla</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t>9951549753</t>
+          <t>8328130920</t>
         </is>
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>1995-01-15</t>
+          <t>2005-06-22</t>
         </is>
       </c>
       <c r="F50" s="18" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Narasapuram</t>
         </is>
       </c>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
@@ -5002,10 +4998,14 @@
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J50" s="18" t="inlineStr"/>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J50" s="18" t="inlineStr">
+        <is>
+          <t>6 years</t>
+        </is>
+      </c>
       <c r="K50" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0040</t>
+          <t>TKPL-RCPT-2026-0039</t>
         </is>
       </c>
       <c r="N50" s="20" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="O50" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:13 PM</t>
+          <t>30-10-2026 01:10 PM</t>
         </is>
       </c>
       <c r="P50" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:12 PM</t>
+          <t>30-10-2026 01:09 PM</t>
         </is>
       </c>
       <c r="Q50" s="18" t="inlineStr">
@@ -5048,32 +5048,32 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0156</t>
+          <t>TKPL-2026-0154</t>
         </is>
       </c>
       <c r="C51" s="21" t="inlineStr">
         <is>
-          <t>G jaya prakash reddy</t>
+          <t>Venkatakumar S</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>8309293988</t>
+          <t>9390667626</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>2002-07-25</t>
+          <t>2002-02-04</t>
         </is>
       </c>
       <c r="F51" s="21" t="inlineStr">
         <is>
-          <t>Rajempet</t>
+          <t>Rayachoty  vemaplli   road B T palli</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
@@ -5083,14 +5083,10 @@
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J51" s="21" t="inlineStr">
-        <is>
-          <t>Atbpl</t>
-        </is>
-      </c>
+          <t>Left-arm Pace</t>
+        </is>
+      </c>
+      <c r="J51" s="21" t="inlineStr"/>
       <c r="K51" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5103,7 +5099,7 @@
       </c>
       <c r="M51" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0041</t>
+          <t>TKPL-RCPT-2026-0105</t>
         </is>
       </c>
       <c r="N51" s="22" t="inlineStr">
@@ -5113,12 +5109,12 @@
       </c>
       <c r="O51" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:15 PM</t>
+          <t>30-10-2026 08:16 PM</t>
         </is>
       </c>
       <c r="P51" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:15 PM</t>
+          <t>30-10-2026 01:11 PM</t>
         </is>
       </c>
       <c r="Q51" s="21" t="inlineStr">
@@ -5133,32 +5129,32 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0157</t>
+          <t>TKPL-2026-0155</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>Shaik Rizwan</t>
+          <t>K SHIVA</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t>9703546013</t>
+          <t>9951549753</t>
         </is>
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>1989-05-08</t>
+          <t>1995-01-15</t>
         </is>
       </c>
       <c r="F52" s="18" t="inlineStr">
         <is>
-          <t>Rayachoty</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
@@ -5168,7 +5164,7 @@
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Spin</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J52" s="18" t="inlineStr"/>
@@ -5184,7 +5180,7 @@
       </c>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0061</t>
+          <t>TKPL-RCPT-2026-0040</t>
         </is>
       </c>
       <c r="N52" s="20" t="inlineStr">
@@ -5194,17 +5190,17 @@
       </c>
       <c r="O52" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:47 PM</t>
+          <t>30-10-2026 01:13 PM</t>
         </is>
       </c>
       <c r="P52" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:17 PM</t>
+          <t>30-10-2026 01:12 PM</t>
         </is>
       </c>
       <c r="Q52" s="18" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -5214,27 +5210,27 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0159</t>
+          <t>TKPL-2026-0156</t>
         </is>
       </c>
       <c r="C53" s="21" t="inlineStr">
         <is>
-          <t>shaik Mynuddin</t>
+          <t>G jaya prakash reddy</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>8885266722</t>
+          <t>8309293988</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>1998-06-06</t>
+          <t>2002-07-25</t>
         </is>
       </c>
       <c r="F53" s="21" t="inlineStr">
         <is>
-          <t>Lakkireddy palli (m) ,Rayachoty</t>
+          <t>Rajempet</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
@@ -5254,7 +5250,7 @@
       </c>
       <c r="J53" s="21" t="inlineStr">
         <is>
-          <t>MNR cricket tournament, Vijay primier League, friends cricket league etc...</t>
+          <t>Atbpl</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -5269,7 +5265,7 @@
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0043</t>
+          <t>TKPL-RCPT-2026-0041</t>
         </is>
       </c>
       <c r="N53" s="22" t="inlineStr">
@@ -5279,12 +5275,12 @@
       </c>
       <c r="O53" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:22 PM</t>
+          <t>30-10-2026 01:15 PM</t>
         </is>
       </c>
       <c r="P53" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:22 PM</t>
+          <t>30-10-2026 01:15 PM</t>
         </is>
       </c>
       <c r="Q53" s="21" t="inlineStr">
@@ -5299,27 +5295,27 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0160</t>
+          <t>TKPL-2026-0157</t>
         </is>
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>Shaik Saddam Hussain</t>
+          <t>Shaik Rizwan</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>8374530338</t>
+          <t>9703546013</t>
         </is>
       </c>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>1995-06-05</t>
+          <t>1989-05-08</t>
         </is>
       </c>
       <c r="F54" s="18" t="inlineStr">
         <is>
-          <t>6-6, Thurakapalli, Gurrappagari Palli(Post), Veeraballi(M),YSR KADAPA (Dt))</t>
+          <t>Rayachoty</t>
         </is>
       </c>
       <c r="G54" s="17" t="inlineStr">
@@ -5334,7 +5330,7 @@
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>Right-arm Spin</t>
         </is>
       </c>
       <c r="J54" s="18" t="inlineStr"/>
@@ -5350,7 +5346,7 @@
       </c>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0044</t>
+          <t>TKPL-RCPT-2026-0061</t>
         </is>
       </c>
       <c r="N54" s="20" t="inlineStr">
@@ -5360,17 +5356,17 @@
       </c>
       <c r="O54" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:23 PM</t>
+          <t>30-10-2026 02:47 PM</t>
         </is>
       </c>
       <c r="P54" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:22 PM</t>
+          <t>30-10-2026 01:17 PM</t>
         </is>
       </c>
       <c r="Q54" s="18" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -5380,32 +5376,32 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0161</t>
+          <t>TKPL-2026-0159</t>
         </is>
       </c>
       <c r="C55" s="21" t="inlineStr">
         <is>
-          <t>Jaffar khan phatan</t>
+          <t>shaik Mynuddin</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>9160616545</t>
+          <t>8885266722</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>2001-11-15</t>
+          <t>1998-06-06</t>
         </is>
       </c>
       <c r="F55" s="21" t="inlineStr">
         <is>
-          <t>Nandalur mandal kadapa district</t>
+          <t>Lakkireddy palli (m) ,Rayachoty</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
@@ -5418,7 +5414,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J55" s="21" t="inlineStr"/>
+      <c r="J55" s="21" t="inlineStr">
+        <is>
+          <t>MNR cricket tournament, Vijay primier League, friends cricket league etc...</t>
+        </is>
+      </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0045</t>
+          <t>TKPL-RCPT-2026-0043</t>
         </is>
       </c>
       <c r="N55" s="22" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O55" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:27 PM</t>
+          <t>30-10-2026 01:22 PM</t>
         </is>
       </c>
       <c r="P55" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:26 PM</t>
+          <t>30-10-2026 01:22 PM</t>
         </is>
       </c>
       <c r="Q55" s="21" t="inlineStr">
@@ -5461,45 +5461,207 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
+          <t>TKPL-2026-0160</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>Shaik Saddam Hussain</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>8374530338</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>1995-06-05</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>6-6, Thurakapalli, Gurrappagari Palli(Post), Veeraballi(M),YSR KADAPA (Dt))</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J56" s="18" t="inlineStr"/>
+      <c r="K56" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L56" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M56" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0044</t>
+        </is>
+      </c>
+      <c r="N56" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O56" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 01:23 PM</t>
+        </is>
+      </c>
+      <c r="P56" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 01:22 PM</t>
+        </is>
+      </c>
+      <c r="Q56" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0161</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="inlineStr">
+        <is>
+          <t>Jaffar khan phatan</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>9160616545</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>2001-11-15</t>
+        </is>
+      </c>
+      <c r="F57" s="21" t="inlineStr">
+        <is>
+          <t>Nandalur mandal kadapa district</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J57" s="21" t="inlineStr"/>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L57" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M57" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0045</t>
+        </is>
+      </c>
+      <c r="N57" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O57" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 01:27 PM</t>
+        </is>
+      </c>
+      <c r="P57" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 01:26 PM</t>
+        </is>
+      </c>
+      <c r="Q57" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
           <t>TKPL-2026-0162</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C58" s="18" t="inlineStr">
         <is>
           <t>Mude Shankar naik</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>9502271805</t>
         </is>
       </c>
-      <c r="E56" s="17" t="inlineStr">
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>2008-06-26</t>
         </is>
       </c>
-      <c r="F56" s="18" t="inlineStr">
+      <c r="F58" s="18" t="inlineStr">
         <is>
           <t>Galiveedu</t>
         </is>
       </c>
-      <c r="G56" s="17" t="inlineStr">
+      <c r="G58" s="17" t="inlineStr">
         <is>
           <t>Batter</t>
         </is>
       </c>
-      <c r="H56" s="17" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
+      <c r="H58" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J56" s="18" t="inlineStr">
+      <c r="J58" s="18" t="inlineStr">
         <is>
           <t>51(21) 4s-5 6s-3
 50 runs in a limited over match. Super!. See on CricHeroes. https://cricheroes.in/scorecard/26220470/until-unity-club-/peruru-11-vs-ashok-11s
@@ -5509,200 +5671,34 @@
 https://crhero.link/campaign/apps</t>
         </is>
       </c>
-      <c r="K56" s="17" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L56" s="19" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="M56" s="17" t="inlineStr">
+      <c r="K58" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L58" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M58" s="17" t="inlineStr">
         <is>
           <t>TKPL-RCPT-2026-0048</t>
         </is>
       </c>
-      <c r="N56" s="20" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O56" s="17" t="inlineStr">
+      <c r="N58" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O58" s="17" t="inlineStr">
         <is>
           <t>30-10-2026 01:45 PM</t>
         </is>
       </c>
-      <c r="P56" s="17" t="inlineStr">
+      <c r="P58" s="17" t="inlineStr">
         <is>
           <t>30-10-2026 01:31 PM</t>
-        </is>
-      </c>
-      <c r="Q56" s="18" t="inlineStr">
-        <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="13" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="13" t="inlineStr">
-        <is>
-          <t>TKPL-2026-0163</t>
-        </is>
-      </c>
-      <c r="C57" s="21" t="inlineStr">
-        <is>
-          <t>Dasari palli Abhishek</t>
-        </is>
-      </c>
-      <c r="D57" s="13" t="inlineStr">
-        <is>
-          <t>9390757461</t>
-        </is>
-      </c>
-      <c r="E57" s="13" t="inlineStr">
-        <is>
-          <t>2005-07-19</t>
-        </is>
-      </c>
-      <c r="F57" s="21" t="inlineStr">
-        <is>
-          <t>Porumamilla</t>
-        </is>
-      </c>
-      <c r="G57" s="13" t="inlineStr">
-        <is>
-          <t>Batter</t>
-        </is>
-      </c>
-      <c r="H57" s="13" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J57" s="21" t="inlineStr">
-        <is>
-          <t>6years experience</t>
-        </is>
-      </c>
-      <c r="K57" s="13" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L57" s="19" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="M57" s="13" t="inlineStr">
-        <is>
-          <t>TKPL-RCPT-2026-0046</t>
-        </is>
-      </c>
-      <c r="N57" s="22" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O57" s="13" t="inlineStr">
-        <is>
-          <t>30-10-2026 01:43 PM</t>
-        </is>
-      </c>
-      <c r="P57" s="13" t="inlineStr">
-        <is>
-          <t>30-10-2026 01:42 PM</t>
-        </is>
-      </c>
-      <c r="Q57" s="21" t="inlineStr">
-        <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="17" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>TKPL-2026-0165</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="inlineStr">
-        <is>
-          <t>samuel chakravarthy</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr">
-        <is>
-          <t>9962511777</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>1983-07-11</t>
-        </is>
-      </c>
-      <c r="F58" s="18" t="inlineStr">
-        <is>
-          <t>Kadapa</t>
-        </is>
-      </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>All-Rounder</t>
-        </is>
-      </c>
-      <c r="H58" s="17" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I58" s="17" t="inlineStr">
-        <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J58" s="18" t="inlineStr"/>
-      <c r="K58" s="17" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L58" s="19" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="M58" s="17" t="inlineStr">
-        <is>
-          <t>TKPL-RCPT-2026-0050</t>
-        </is>
-      </c>
-      <c r="N58" s="20" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O58" s="17" t="inlineStr">
-        <is>
-          <t>30-10-2026 02:03 PM</t>
-        </is>
-      </c>
-      <c r="P58" s="17" t="inlineStr">
-        <is>
-          <t>30-10-2026 01:56 PM</t>
         </is>
       </c>
       <c r="Q58" s="18" t="inlineStr">
@@ -5717,32 +5713,32 @@
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0166</t>
+          <t>TKPL-2026-0163</t>
         </is>
       </c>
       <c r="C59" s="21" t="inlineStr">
         <is>
-          <t>M SYED NASRUDDIN</t>
+          <t>Dasari palli Abhishek</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>9494040272</t>
+          <t>9390757461</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>1997-08-08</t>
+          <t>2005-07-19</t>
         </is>
       </c>
       <c r="F59" s="21" t="inlineStr">
         <is>
-          <t>PRODDATUR</t>
+          <t>Porumamilla</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
@@ -5757,7 +5753,7 @@
       </c>
       <c r="J59" s="21" t="inlineStr">
         <is>
-          <t>I played lot's of tournament all over andhra pradesh</t>
+          <t>6years experience</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -5772,7 +5768,7 @@
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0049</t>
+          <t>TKPL-RCPT-2026-0046</t>
         </is>
       </c>
       <c r="N59" s="22" t="inlineStr">
@@ -5782,12 +5778,12 @@
       </c>
       <c r="O59" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:01 PM</t>
+          <t>30-10-2026 01:43 PM</t>
         </is>
       </c>
       <c r="P59" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:59 PM</t>
+          <t>30-10-2026 01:42 PM</t>
         </is>
       </c>
       <c r="Q59" s="21" t="inlineStr">
@@ -5802,37 +5798,37 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0167</t>
+          <t>TKPL-2026-0165</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>Syed yaseen</t>
+          <t>samuel chakravarthy</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>9542075835</t>
+          <t>9962511777</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>1994-07-24</t>
+          <t>1983-07-11</t>
         </is>
       </c>
       <c r="F60" s="18" t="inlineStr">
         <is>
-          <t>Rajampeta</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
@@ -5840,11 +5836,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J60" s="18" t="inlineStr">
-        <is>
-          <t>RMCL TOURNAMENT 5 TIMES WINNER HAS A CAPTAIN AND MANY TOURNAMENT WINNER IN RAJAMPETA</t>
-        </is>
-      </c>
+      <c r="J60" s="18" t="inlineStr"/>
       <c r="K60" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5857,7 +5849,7 @@
       </c>
       <c r="M60" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0051</t>
+          <t>TKPL-RCPT-2026-0050</t>
         </is>
       </c>
       <c r="N60" s="20" t="inlineStr">
@@ -5872,7 +5864,7 @@
       </c>
       <c r="P60" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:02 PM</t>
+          <t>30-10-2026 01:56 PM</t>
         </is>
       </c>
       <c r="Q60" s="18" t="inlineStr">
@@ -5887,27 +5879,27 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0168</t>
+          <t>TKPL-2026-0166</t>
         </is>
       </c>
       <c r="C61" s="21" t="inlineStr">
         <is>
-          <t>Pallapu sai</t>
+          <t>M SYED NASRUDDIN</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>9014830335</t>
+          <t>9494040272</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>2002-06-14</t>
+          <t>1997-08-08</t>
         </is>
       </c>
       <c r="F61" s="21" t="inlineStr">
         <is>
-          <t>Chinnanandem</t>
+          <t>PRODDATUR</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
@@ -5925,7 +5917,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J61" s="21" t="inlineStr"/>
+      <c r="J61" s="21" t="inlineStr">
+        <is>
+          <t>I played lot's of tournament all over andhra pradesh</t>
+        </is>
+      </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5938,7 +5934,7 @@
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0052</t>
+          <t>TKPL-RCPT-2026-0049</t>
         </is>
       </c>
       <c r="N61" s="22" t="inlineStr">
@@ -5948,12 +5944,12 @@
       </c>
       <c r="O61" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:27 PM</t>
+          <t>30-10-2026 02:01 PM</t>
         </is>
       </c>
       <c r="P61" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:26 PM</t>
+          <t>30-10-2026 01:59 PM</t>
         </is>
       </c>
       <c r="Q61" s="21" t="inlineStr">
@@ -5968,37 +5964,37 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0169</t>
+          <t>TKPL-2026-0167</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>Lavakumar gandikota</t>
+          <t>Syed yaseen</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>9603837873</t>
+          <t>9542075835</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>1995-06-08</t>
+          <t>1994-07-24</t>
         </is>
       </c>
       <c r="F62" s="18" t="inlineStr">
         <is>
-          <t>Rayachoty</t>
+          <t>Rajampeta</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
@@ -6006,7 +6002,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J62" s="18" t="inlineStr"/>
+      <c r="J62" s="18" t="inlineStr">
+        <is>
+          <t>RMCL TOURNAMENT 5 TIMES WINNER HAS A CAPTAIN AND MANY TOURNAMENT WINNER IN RAJAMPETA</t>
+        </is>
+      </c>
       <c r="K62" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="M62" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0053</t>
+          <t>TKPL-RCPT-2026-0051</t>
         </is>
       </c>
       <c r="N62" s="20" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="O62" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:31 PM</t>
+          <t>30-10-2026 02:03 PM</t>
         </is>
       </c>
       <c r="P62" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:30 PM</t>
+          <t>30-10-2026 02:02 PM</t>
         </is>
       </c>
       <c r="Q62" s="18" t="inlineStr">
@@ -6049,27 +6049,27 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0170</t>
+          <t>TKPL-2026-0168</t>
         </is>
       </c>
       <c r="C63" s="21" t="inlineStr">
         <is>
-          <t>Bhaskar Thirumalakonda</t>
+          <t>Pallapu sai</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>7794902066</t>
+          <t>9014830335</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>2000-10-22</t>
+          <t>2002-06-14</t>
         </is>
       </c>
       <c r="F63" s="21" t="inlineStr">
         <is>
-          <t>Galiveedu</t>
+          <t>Chinnanandem</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0054</t>
+          <t>TKPL-RCPT-2026-0052</t>
         </is>
       </c>
       <c r="N63" s="22" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="O63" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:32 PM</t>
+          <t>30-10-2026 02:27 PM</t>
         </is>
       </c>
       <c r="P63" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:31 PM</t>
+          <t>30-10-2026 02:26 PM</t>
         </is>
       </c>
       <c r="Q63" s="21" t="inlineStr">
@@ -6130,27 +6130,27 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0171</t>
+          <t>TKPL-2026-0169</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>THALLU IMRAN</t>
+          <t>Lavakumar gandikota</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>9182994104</t>
+          <t>9603837873</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>1997-07-10</t>
+          <t>1995-06-08</t>
         </is>
       </c>
       <c r="F64" s="18" t="inlineStr">
         <is>
-          <t>Rayachoti</t>
+          <t>Rayachoty</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
@@ -6168,11 +6168,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J64" s="18" t="inlineStr">
-        <is>
-          <t>RPL and local tournaments</t>
-        </is>
-      </c>
+      <c r="J64" s="18" t="inlineStr"/>
       <c r="K64" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6185,7 +6181,7 @@
       </c>
       <c r="M64" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0055</t>
+          <t>TKPL-RCPT-2026-0053</t>
         </is>
       </c>
       <c r="N64" s="20" t="inlineStr">
@@ -6195,12 +6191,12 @@
       </c>
       <c r="O64" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:38 PM</t>
+          <t>30-10-2026 02:31 PM</t>
         </is>
       </c>
       <c r="P64" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:37 PM</t>
+          <t>30-10-2026 02:30 PM</t>
         </is>
       </c>
       <c r="Q64" s="18" t="inlineStr">
@@ -6215,32 +6211,32 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0172</t>
+          <t>TKPL-2026-0170</t>
         </is>
       </c>
       <c r="C65" s="21" t="inlineStr">
         <is>
-          <t>P.munidhra</t>
+          <t>Bhaskar Thirumalakonda</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>6304924346</t>
+          <t>7794902066</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>2006-05-05</t>
+          <t>2000-10-22</t>
         </is>
       </c>
       <c r="F65" s="21" t="inlineStr">
         <is>
-          <t>Khajipet /pulluru</t>
+          <t>Galiveedu</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
@@ -6250,14 +6246,10 @@
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J65" s="21" t="inlineStr">
-        <is>
-          <t>Playing local Tournaments</t>
-        </is>
-      </c>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J65" s="21" t="inlineStr"/>
       <c r="K65" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6270,7 +6262,7 @@
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0056</t>
+          <t>TKPL-RCPT-2026-0054</t>
         </is>
       </c>
       <c r="N65" s="22" t="inlineStr">
@@ -6280,12 +6272,12 @@
       </c>
       <c r="O65" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:39 PM</t>
+          <t>30-10-2026 02:32 PM</t>
         </is>
       </c>
       <c r="P65" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:38 PM</t>
+          <t>30-10-2026 02:31 PM</t>
         </is>
       </c>
       <c r="Q65" s="21" t="inlineStr">
@@ -6300,27 +6292,27 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0174</t>
+          <t>TKPL-2026-0171</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>Bandla Nagaraj</t>
+          <t>THALLU IMRAN</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>8639151288</t>
+          <t>9182994104</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>1988-09-24</t>
+          <t>1997-07-10</t>
         </is>
       </c>
       <c r="F66" s="18" t="inlineStr">
         <is>
-          <t>Rajampeta,bhuvagiripalli</t>
+          <t>Rayachoti</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
@@ -6340,7 +6332,7 @@
       </c>
       <c r="J66" s="18" t="inlineStr">
         <is>
-          <t>TPL and KPL</t>
+          <t>RPL and local tournaments</t>
         </is>
       </c>
       <c r="K66" s="17" t="inlineStr">
@@ -6355,7 +6347,7 @@
       </c>
       <c r="M66" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0062</t>
+          <t>TKPL-RCPT-2026-0055</t>
         </is>
       </c>
       <c r="N66" s="20" t="inlineStr">
@@ -6365,12 +6357,12 @@
       </c>
       <c r="O66" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:49 PM</t>
+          <t>30-10-2026 02:38 PM</t>
         </is>
       </c>
       <c r="P66" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:49 PM</t>
+          <t>30-10-2026 02:37 PM</t>
         </is>
       </c>
       <c r="Q66" s="18" t="inlineStr">
@@ -6385,32 +6377,32 @@
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0175</t>
+          <t>TKPL-2026-0172</t>
         </is>
       </c>
       <c r="C67" s="21" t="inlineStr">
         <is>
-          <t>Kammineni pavan Kumar yadav</t>
+          <t>P.munidhra</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>7995878278</t>
+          <t>6304924346</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>1998-06-16</t>
+          <t>2006-05-05</t>
         </is>
       </c>
       <c r="F67" s="21" t="inlineStr">
         <is>
-          <t>Rayachoti</t>
+          <t>Khajipet /pulluru</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -6420,10 +6412,14 @@
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J67" s="21" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J67" s="21" t="inlineStr">
+        <is>
+          <t>Playing local Tournaments</t>
+        </is>
+      </c>
       <c r="K67" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6436,7 +6432,7 @@
       </c>
       <c r="M67" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0063</t>
+          <t>TKPL-RCPT-2026-0056</t>
         </is>
       </c>
       <c r="N67" s="22" t="inlineStr">
@@ -6446,12 +6442,12 @@
       </c>
       <c r="O67" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:00 PM</t>
+          <t>30-10-2026 02:39 PM</t>
         </is>
       </c>
       <c r="P67" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:52 PM</t>
+          <t>30-10-2026 02:38 PM</t>
         </is>
       </c>
       <c r="Q67" s="21" t="inlineStr">
@@ -6466,27 +6462,27 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0176</t>
+          <t>TKPL-2026-0173</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>Mekala Chandravasulu Reddy</t>
+          <t>Yellutla ravikumar naidu</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>9493353988</t>
+          <t>9705490252</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>1992-06-08</t>
+          <t>2005-03-16</t>
         </is>
       </c>
       <c r="F68" s="18" t="inlineStr">
         <is>
-          <t>Yerraguntla</t>
+          <t>Chinamandam</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
@@ -6496,19 +6492,15 @@
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J68" s="18" t="inlineStr">
-        <is>
-          <t>I have played 450 matches on cricheros profile</t>
-        </is>
-      </c>
+          <t>Left-arm Spin</t>
+        </is>
+      </c>
+      <c r="J68" s="18" t="inlineStr"/>
       <c r="K68" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6521,7 +6513,7 @@
       </c>
       <c r="M68" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0064</t>
+          <t>TKPL-RCPT-2026-0096</t>
         </is>
       </c>
       <c r="N68" s="20" t="inlineStr">
@@ -6531,12 +6523,12 @@
       </c>
       <c r="O68" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:11 PM</t>
+          <t>30-10-2026 07:02 PM</t>
         </is>
       </c>
       <c r="P68" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:04 PM</t>
+          <t>30-10-2026 02:48 PM</t>
         </is>
       </c>
       <c r="Q68" s="18" t="inlineStr">
@@ -6551,32 +6543,32 @@
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0178</t>
+          <t>TKPL-2026-0174</t>
         </is>
       </c>
       <c r="C69" s="21" t="inlineStr">
         <is>
-          <t>Shaik Ghouse mohiddin  ( mohid)</t>
+          <t>Bandla Nagaraj</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>7997116597</t>
+          <t>8639151288</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>1993-12-27</t>
+          <t>1988-09-24</t>
         </is>
       </c>
       <c r="F69" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Rajampeta,bhuvagiripalli</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -6589,7 +6581,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J69" s="21" t="inlineStr"/>
+      <c r="J69" s="21" t="inlineStr">
+        <is>
+          <t>TPL and KPL</t>
+        </is>
+      </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6602,7 +6598,7 @@
       </c>
       <c r="M69" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0065</t>
+          <t>TKPL-RCPT-2026-0062</t>
         </is>
       </c>
       <c r="N69" s="22" t="inlineStr">
@@ -6612,12 +6608,12 @@
       </c>
       <c r="O69" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:13 PM</t>
+          <t>30-10-2026 02:49 PM</t>
         </is>
       </c>
       <c r="P69" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:12 PM</t>
+          <t>30-10-2026 02:49 PM</t>
         </is>
       </c>
       <c r="Q69" s="21" t="inlineStr">
@@ -6632,32 +6628,32 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0179</t>
+          <t>TKPL-2026-0175</t>
         </is>
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>Shaik saif..@PINTU</t>
+          <t>Kammineni pavan Kumar yadav</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>8919628160</t>
+          <t>7995878278</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>2000-09-09</t>
+          <t>1998-06-16</t>
         </is>
       </c>
       <c r="F70" s="18" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Rayachoti</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
@@ -6667,14 +6663,10 @@
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J70" s="18" t="inlineStr">
-        <is>
-          <t>KKR..MPL LEAGUES</t>
-        </is>
-      </c>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J70" s="18" t="inlineStr"/>
       <c r="K70" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6687,7 +6679,7 @@
       </c>
       <c r="M70" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0066</t>
+          <t>TKPL-RCPT-2026-0063</t>
         </is>
       </c>
       <c r="N70" s="20" t="inlineStr">
@@ -6697,12 +6689,12 @@
       </c>
       <c r="O70" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:14 PM</t>
+          <t>30-10-2026 03:00 PM</t>
         </is>
       </c>
       <c r="P70" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:13 PM</t>
+          <t>30-10-2026 02:52 PM</t>
         </is>
       </c>
       <c r="Q70" s="18" t="inlineStr">
@@ -6717,27 +6709,27 @@
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0180</t>
+          <t>TKPL-2026-0176</t>
         </is>
       </c>
       <c r="C71" s="21" t="inlineStr">
         <is>
-          <t>SURENDRA KUMAR YADAV</t>
+          <t>Mekala Chandravasulu Reddy</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>9000555438</t>
+          <t>9493353988</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>1989-06-08</t>
+          <t>1992-06-08</t>
         </is>
       </c>
       <c r="F71" s="21" t="inlineStr">
         <is>
-          <t>KADAPA</t>
+          <t>Yerraguntla</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
@@ -6757,7 +6749,7 @@
       </c>
       <c r="J71" s="21" t="inlineStr">
         <is>
-          <t>JOURNALIST TOURNAMENTS</t>
+          <t>I have played 450 matches on cricheros profile</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -6772,7 +6764,7 @@
       </c>
       <c r="M71" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0067</t>
+          <t>TKPL-RCPT-2026-0064</t>
         </is>
       </c>
       <c r="N71" s="22" t="inlineStr">
@@ -6782,12 +6774,12 @@
       </c>
       <c r="O71" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:18 PM</t>
+          <t>30-10-2026 03:11 PM</t>
         </is>
       </c>
       <c r="P71" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:17 PM</t>
+          <t>30-10-2026 03:04 PM</t>
         </is>
       </c>
       <c r="Q71" s="21" t="inlineStr">
@@ -6802,32 +6794,32 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0181</t>
+          <t>TKPL-2026-0177</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>BANDELA PRAVEEN KUMAR</t>
+          <t>Yellutla Sree hari naidu</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>9493832807</t>
+          <t>6281999214</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>1992-02-29</t>
+          <t>2009-04-10</t>
         </is>
       </c>
       <c r="F72" s="18" t="inlineStr">
         <is>
-          <t>Nandimandalam</t>
+          <t>Chinamandam</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H72" s="17" t="inlineStr">
@@ -6840,11 +6832,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J72" s="18" t="inlineStr">
-        <is>
-          <t>I participate in state-wide revenue tournaments as part of the district team representing the Revenue Department.</t>
-        </is>
-      </c>
+      <c r="J72" s="18" t="inlineStr"/>
       <c r="K72" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6857,7 +6845,7 @@
       </c>
       <c r="M72" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0068</t>
+          <t>TKPL-RCPT-2026-0099</t>
         </is>
       </c>
       <c r="N72" s="20" t="inlineStr">
@@ -6867,12 +6855,12 @@
       </c>
       <c r="O72" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:18 PM</t>
+          <t>30-10-2026 07:06 PM</t>
         </is>
       </c>
       <c r="P72" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:18 PM</t>
+          <t>30-10-2026 03:06 PM</t>
         </is>
       </c>
       <c r="Q72" s="18" t="inlineStr">
@@ -6887,32 +6875,32 @@
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0182</t>
+          <t>TKPL-2026-0178</t>
         </is>
       </c>
       <c r="C73" s="21" t="inlineStr">
         <is>
-          <t>Bharath Kumar reddy</t>
+          <t>Shaik Ghouse mohiddin  ( mohid)</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>7981122958</t>
+          <t>7997116597</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>1993-12-27</t>
         </is>
       </c>
       <c r="F73" s="21" t="inlineStr">
         <is>
-          <t>Chinnamandem</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
@@ -6922,14 +6910,10 @@
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J73" s="21" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J73" s="21" t="inlineStr"/>
       <c r="K73" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6942,7 +6926,7 @@
       </c>
       <c r="M73" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0069</t>
+          <t>TKPL-RCPT-2026-0065</t>
         </is>
       </c>
       <c r="N73" s="22" t="inlineStr">
@@ -6952,12 +6936,12 @@
       </c>
       <c r="O73" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:22 PM</t>
+          <t>30-10-2026 03:13 PM</t>
         </is>
       </c>
       <c r="P73" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:21 PM</t>
+          <t>30-10-2026 03:12 PM</t>
         </is>
       </c>
       <c r="Q73" s="21" t="inlineStr">
@@ -6972,32 +6956,32 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0183</t>
+          <t>TKPL-2026-0179</t>
         </is>
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>Gantenapalli mahesh</t>
+          <t>Shaik saif..@PINTU</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>6281951630</t>
+          <t>8919628160</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>1996-06-05</t>
+          <t>2000-09-09</t>
         </is>
       </c>
       <c r="F74" s="18" t="inlineStr">
         <is>
-          <t>kadapa</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
@@ -7007,10 +6991,14 @@
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J74" s="18" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J74" s="18" t="inlineStr">
+        <is>
+          <t>KKR..MPL LEAGUES</t>
+        </is>
+      </c>
       <c r="K74" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7023,7 +7011,7 @@
       </c>
       <c r="M74" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0070</t>
+          <t>TKPL-RCPT-2026-0066</t>
         </is>
       </c>
       <c r="N74" s="20" t="inlineStr">
@@ -7033,12 +7021,12 @@
       </c>
       <c r="O74" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:27 PM</t>
+          <t>30-10-2026 03:14 PM</t>
         </is>
       </c>
       <c r="P74" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:26 PM</t>
+          <t>30-10-2026 03:13 PM</t>
         </is>
       </c>
       <c r="Q74" s="18" t="inlineStr">
@@ -7053,22 +7041,22 @@
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0184</t>
+          <t>TKPL-2026-0180</t>
         </is>
       </c>
       <c r="C75" s="21" t="inlineStr">
         <is>
-          <t>CHARU NAGARAJU</t>
+          <t>SURENDRA KUMAR YADAV</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>9160446640</t>
+          <t>9000555438</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>1992-04-03</t>
+          <t>1989-06-08</t>
         </is>
       </c>
       <c r="F75" s="21" t="inlineStr">
@@ -7093,7 +7081,7 @@
       </c>
       <c r="J75" s="21" t="inlineStr">
         <is>
-          <t>LOCAL TOURNAMNETS</t>
+          <t>JOURNALIST TOURNAMENTS</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -7108,7 +7096,7 @@
       </c>
       <c r="M75" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0071</t>
+          <t>TKPL-RCPT-2026-0067</t>
         </is>
       </c>
       <c r="N75" s="22" t="inlineStr">
@@ -7118,12 +7106,12 @@
       </c>
       <c r="O75" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:27 PM</t>
+          <t>30-10-2026 03:18 PM</t>
         </is>
       </c>
       <c r="P75" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:27 PM</t>
+          <t>30-10-2026 03:17 PM</t>
         </is>
       </c>
       <c r="Q75" s="21" t="inlineStr">
@@ -7138,32 +7126,32 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0185</t>
+          <t>TKPL-2026-0181</t>
         </is>
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>U.OBULESU</t>
+          <t>BANDELA PRAVEEN KUMAR</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t>9398778303</t>
+          <t>9493832807</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>1997-05-16</t>
+          <t>1992-02-29</t>
         </is>
       </c>
       <c r="F76" s="18" t="inlineStr">
         <is>
-          <t>Lakkireddipalli</t>
+          <t>Nandimandalam</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
@@ -7176,7 +7164,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J76" s="18" t="inlineStr"/>
+      <c r="J76" s="18" t="inlineStr">
+        <is>
+          <t>I participate in state-wide revenue tournaments as part of the district team representing the Revenue Department.</t>
+        </is>
+      </c>
       <c r="K76" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7189,7 +7181,7 @@
       </c>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0077</t>
+          <t>TKPL-RCPT-2026-0068</t>
         </is>
       </c>
       <c r="N76" s="20" t="inlineStr">
@@ -7199,17 +7191,17 @@
       </c>
       <c r="O76" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:50 PM</t>
+          <t>30-10-2026 03:18 PM</t>
         </is>
       </c>
       <c r="P76" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:29 PM</t>
+          <t>30-10-2026 03:18 PM</t>
         </is>
       </c>
       <c r="Q76" s="18" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7219,32 +7211,32 @@
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0186</t>
+          <t>TKPL-2026-0182</t>
         </is>
       </c>
       <c r="C77" s="21" t="inlineStr">
         <is>
-          <t>Dinesh Don Don</t>
+          <t>Bharath Kumar reddy</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>7386474099</t>
+          <t>7981122958</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>2000-11-25</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="F77" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Chinnamandem</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
@@ -7254,12 +7246,12 @@
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J77" s="21" t="inlineStr">
         <is>
-          <t>Played Big Tournaments</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -7274,7 +7266,7 @@
       </c>
       <c r="M77" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0078</t>
+          <t>TKPL-RCPT-2026-0069</t>
         </is>
       </c>
       <c r="N77" s="22" t="inlineStr">
@@ -7284,17 +7276,17 @@
       </c>
       <c r="O77" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:50 PM</t>
+          <t>30-10-2026 03:22 PM</t>
         </is>
       </c>
       <c r="P77" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:29 PM</t>
+          <t>30-10-2026 03:21 PM</t>
         </is>
       </c>
       <c r="Q77" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7304,27 +7296,27 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0187</t>
+          <t>TKPL-2026-0183</t>
         </is>
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>Danger Man Ravi</t>
+          <t>Gantenapalli mahesh</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>9052561634</t>
+          <t>6281951630</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>2000-01-13</t>
+          <t>1996-06-05</t>
         </is>
       </c>
       <c r="F78" s="18" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>kadapa</t>
         </is>
       </c>
       <c r="G78" s="17" t="inlineStr">
@@ -7342,11 +7334,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J78" s="18" t="inlineStr">
-        <is>
-          <t>Tournament experience 15 years</t>
-        </is>
-      </c>
+      <c r="J78" s="18" t="inlineStr"/>
       <c r="K78" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7359,7 +7347,7 @@
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0074</t>
+          <t>TKPL-RCPT-2026-0070</t>
         </is>
       </c>
       <c r="N78" s="20" t="inlineStr">
@@ -7369,12 +7357,12 @@
       </c>
       <c r="O78" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:32 PM</t>
+          <t>30-10-2026 03:27 PM</t>
         </is>
       </c>
       <c r="P78" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:31 PM</t>
+          <t>30-10-2026 03:26 PM</t>
         </is>
       </c>
       <c r="Q78" s="18" t="inlineStr">
@@ -7389,32 +7377,32 @@
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0188</t>
+          <t>TKPL-2026-0184</t>
         </is>
       </c>
       <c r="C79" s="21" t="inlineStr">
         <is>
-          <t>Crazy boy mp</t>
+          <t>CHARU NAGARAJU</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>9000814023</t>
+          <t>9160446640</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>1995-08-22</t>
+          <t>1992-04-03</t>
         </is>
       </c>
       <c r="F79" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>KADAPA</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H79" s="13" t="inlineStr">
@@ -7427,7 +7415,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J79" s="21" t="inlineStr"/>
+      <c r="J79" s="21" t="inlineStr">
+        <is>
+          <t>LOCAL TOURNAMNETS</t>
+        </is>
+      </c>
       <c r="K79" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7440,7 +7432,7 @@
       </c>
       <c r="M79" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0076</t>
+          <t>TKPL-RCPT-2026-0071</t>
         </is>
       </c>
       <c r="N79" s="22" t="inlineStr">
@@ -7450,17 +7442,17 @@
       </c>
       <c r="O79" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:50 PM</t>
+          <t>30-10-2026 03:27 PM</t>
         </is>
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:31 PM</t>
+          <t>30-10-2026 03:27 PM</t>
         </is>
       </c>
       <c r="Q79" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7470,27 +7462,27 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0189</t>
+          <t>TKPL-2026-0185</t>
         </is>
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>RAJA</t>
+          <t>U.OBULESU</t>
         </is>
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t>9398317906</t>
+          <t>9398778303</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>1999-09-15</t>
+          <t>1997-05-16</t>
         </is>
       </c>
       <c r="F80" s="18" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Lakkireddipalli</t>
         </is>
       </c>
       <c r="G80" s="17" t="inlineStr">
@@ -7521,7 +7513,7 @@
       </c>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0075</t>
+          <t>TKPL-RCPT-2026-0077</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
@@ -7531,17 +7523,17 @@
       </c>
       <c r="O80" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:47 PM</t>
+          <t>30-10-2026 03:50 PM</t>
         </is>
       </c>
       <c r="P80" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:46 PM</t>
+          <t>30-10-2026 03:29 PM</t>
         </is>
       </c>
       <c r="Q80" s="18" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7551,27 +7543,27 @@
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0190</t>
+          <t>TKPL-2026-0186</t>
         </is>
       </c>
       <c r="C81" s="21" t="inlineStr">
         <is>
-          <t>Nachu.vinodkumar</t>
+          <t>Dinesh Don Don</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>8499806339</t>
+          <t>7386474099</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>1995-07-10</t>
+          <t>2000-11-25</t>
         </is>
       </c>
       <c r="F81" s="21" t="inlineStr">
         <is>
-          <t>Annamayya district.galiveedu.</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
@@ -7586,12 +7578,12 @@
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Spin</t>
+          <t>Right-arm Pace</t>
         </is>
       </c>
       <c r="J81" s="21" t="inlineStr">
         <is>
-          <t>ATPBL Kadapa king team. south zone Mumbai club. International matches Nepal premier leag</t>
+          <t>Played Big Tournaments</t>
         </is>
       </c>
       <c r="K81" s="13" t="inlineStr">
@@ -7606,7 +7598,7 @@
       </c>
       <c r="M81" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0079</t>
+          <t>TKPL-RCPT-2026-0078</t>
         </is>
       </c>
       <c r="N81" s="22" t="inlineStr">
@@ -7616,17 +7608,17 @@
       </c>
       <c r="O81" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:54 PM</t>
+          <t>30-10-2026 03:50 PM</t>
         </is>
       </c>
       <c r="P81" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:54 PM</t>
+          <t>30-10-2026 03:29 PM</t>
         </is>
       </c>
       <c r="Q81" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7636,27 +7628,27 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0191</t>
+          <t>TKPL-2026-0187</t>
         </is>
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>Giri</t>
+          <t>Danger Man Ravi</t>
         </is>
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t>7989571634</t>
+          <t>9052561634</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>1997-06-02</t>
+          <t>2000-01-13</t>
         </is>
       </c>
       <c r="F82" s="18" t="inlineStr">
         <is>
-          <t>Vempalli</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G82" s="17" t="inlineStr">
@@ -7666,17 +7658,17 @@
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
-          <t>Left-arm Pace</t>
+          <t>Right-arm Pace</t>
         </is>
       </c>
       <c r="J82" s="18" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Tournament experience 15 years</t>
         </is>
       </c>
       <c r="K82" s="17" t="inlineStr">
@@ -7691,7 +7683,7 @@
       </c>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0088</t>
+          <t>TKPL-RCPT-2026-0074</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
@@ -7701,12 +7693,12 @@
       </c>
       <c r="O82" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:30 PM</t>
+          <t>30-10-2026 03:32 PM</t>
         </is>
       </c>
       <c r="P82" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:56 PM</t>
+          <t>30-10-2026 03:31 PM</t>
         </is>
       </c>
       <c r="Q82" s="18" t="inlineStr">
@@ -7721,32 +7713,32 @@
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0192</t>
+          <t>TKPL-2026-0188</t>
         </is>
       </c>
       <c r="C83" s="21" t="inlineStr">
         <is>
-          <t>D  Nagarjuna Reddy</t>
+          <t>Crazy boy mp</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>7396440670</t>
+          <t>9000814023</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>2008-06-16</t>
+          <t>1995-08-22</t>
         </is>
       </c>
       <c r="F83" s="21" t="inlineStr">
         <is>
-          <t>Chakrayapeta town</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
@@ -7759,11 +7751,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J83" s="21" t="inlineStr">
-        <is>
-          <t>Chakrayapeta  youth tournament</t>
-        </is>
-      </c>
+      <c r="J83" s="21" t="inlineStr"/>
       <c r="K83" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7776,7 +7764,7 @@
       </c>
       <c r="M83" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0080</t>
+          <t>TKPL-RCPT-2026-0076</t>
         </is>
       </c>
       <c r="N83" s="22" t="inlineStr">
@@ -7786,17 +7774,17 @@
       </c>
       <c r="O83" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:06 PM</t>
+          <t>30-10-2026 03:50 PM</t>
         </is>
       </c>
       <c r="P83" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:04 PM</t>
+          <t>30-10-2026 03:31 PM</t>
         </is>
       </c>
       <c r="Q83" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7806,37 +7794,37 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0193</t>
+          <t>TKPL-2026-0189</t>
         </is>
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>MOTAPOTHULA VAMSI (PANT)</t>
+          <t>RAJA</t>
         </is>
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t>8309585550</t>
+          <t>9398317906</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>2002-04-06</t>
+          <t>1999-09-15</t>
         </is>
       </c>
       <c r="F84" s="18" t="inlineStr">
         <is>
-          <t>SAVISETTIPALLI</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G84" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I84" s="17" t="inlineStr">
@@ -7844,11 +7832,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J84" s="18" t="inlineStr">
-        <is>
-          <t>6years experience many trophies win</t>
-        </is>
-      </c>
+      <c r="J84" s="18" t="inlineStr"/>
       <c r="K84" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7861,7 +7845,7 @@
       </c>
       <c r="M84" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0081</t>
+          <t>TKPL-RCPT-2026-0075</t>
         </is>
       </c>
       <c r="N84" s="20" t="inlineStr">
@@ -7871,12 +7855,12 @@
       </c>
       <c r="O84" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:06 PM</t>
+          <t>30-10-2026 03:47 PM</t>
         </is>
       </c>
       <c r="P84" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:05 PM</t>
+          <t>30-10-2026 03:46 PM</t>
         </is>
       </c>
       <c r="Q84" s="18" t="inlineStr">
@@ -7891,27 +7875,27 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0194</t>
+          <t>TKPL-2026-0190</t>
         </is>
       </c>
       <c r="C85" s="21" t="inlineStr">
         <is>
-          <t>ARSHAD PATAN</t>
+          <t>Nachu.vinodkumar</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>8309771127</t>
+          <t>8499806339</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>2007-07-09</t>
+          <t>1995-07-10</t>
         </is>
       </c>
       <c r="F85" s="21" t="inlineStr">
         <is>
-          <t>Kadapa: ayesha shool near pedda darga</t>
+          <t>Annamayya district.galiveedu.</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
@@ -7926,13 +7910,12 @@
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>Right-arm Spin</t>
         </is>
       </c>
       <c r="J85" s="21" t="inlineStr">
         <is>
-          <t>ATBPL-1
-ANDHRA TENNIS BALL PERMIER LEAUGE</t>
+          <t>ATPBL Kadapa king team. south zone Mumbai club. International matches Nepal premier leag</t>
         </is>
       </c>
       <c r="K85" s="13" t="inlineStr">
@@ -7947,7 +7930,7 @@
       </c>
       <c r="M85" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0082</t>
+          <t>TKPL-RCPT-2026-0079</t>
         </is>
       </c>
       <c r="N85" s="22" t="inlineStr">
@@ -7957,12 +7940,12 @@
       </c>
       <c r="O85" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:11 PM</t>
+          <t>30-10-2026 03:54 PM</t>
         </is>
       </c>
       <c r="P85" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:09 PM</t>
+          <t>30-10-2026 03:54 PM</t>
         </is>
       </c>
       <c r="Q85" s="21" t="inlineStr">
@@ -7977,27 +7960,27 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0195</t>
+          <t>TKPL-2026-0191</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>M SUBBA REDDY</t>
+          <t>Giri</t>
         </is>
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t>9052632763</t>
+          <t>7989571634</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>1987-06-06</t>
+          <t>1997-06-02</t>
         </is>
       </c>
       <c r="F86" s="18" t="inlineStr">
         <is>
-          <t>Khajipet</t>
+          <t>Vempalli</t>
         </is>
       </c>
       <c r="G86" s="17" t="inlineStr">
@@ -8007,17 +7990,17 @@
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>Left-arm Pace</t>
         </is>
       </c>
       <c r="J86" s="18" t="inlineStr">
         <is>
-          <t>Nill</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="K86" s="17" t="inlineStr">
@@ -8032,7 +8015,7 @@
       </c>
       <c r="M86" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0083</t>
+          <t>TKPL-RCPT-2026-0088</t>
         </is>
       </c>
       <c r="N86" s="20" t="inlineStr">
@@ -8042,12 +8025,12 @@
       </c>
       <c r="O86" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:15 PM</t>
+          <t>30-10-2026 04:30 PM</t>
         </is>
       </c>
       <c r="P86" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:14 PM</t>
+          <t>30-10-2026 03:56 PM</t>
         </is>
       </c>
       <c r="Q86" s="18" t="inlineStr">
@@ -8062,32 +8045,32 @@
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0196</t>
+          <t>TKPL-2026-0192</t>
         </is>
       </c>
       <c r="C87" s="21" t="inlineStr">
         <is>
-          <t>Eswar Beema</t>
+          <t>D  Nagarjuna Reddy</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>7337007666</t>
+          <t>7396440670</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>1993-04-04</t>
+          <t>2008-06-16</t>
         </is>
       </c>
       <c r="F87" s="21" t="inlineStr">
         <is>
-          <t>Kamalapuram</t>
+          <t>Chakrayapeta town</t>
         </is>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -8100,7 +8083,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J87" s="21" t="inlineStr"/>
+      <c r="J87" s="21" t="inlineStr">
+        <is>
+          <t>Chakrayapeta  youth tournament</t>
+        </is>
+      </c>
       <c r="K87" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -8113,7 +8100,7 @@
       </c>
       <c r="M87" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0084</t>
+          <t>TKPL-RCPT-2026-0080</t>
         </is>
       </c>
       <c r="N87" s="22" t="inlineStr">
@@ -8123,12 +8110,12 @@
       </c>
       <c r="O87" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:17 PM</t>
+          <t>30-10-2026 04:06 PM</t>
         </is>
       </c>
       <c r="P87" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:16 PM</t>
+          <t>30-10-2026 04:04 PM</t>
         </is>
       </c>
       <c r="Q87" s="21" t="inlineStr">
@@ -8143,27 +8130,27 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0197</t>
+          <t>TKPL-2026-0193</t>
         </is>
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>Sameer</t>
+          <t>MOTAPOTHULA VAMSI (PANT)</t>
         </is>
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t>7013094749</t>
+          <t>8309585550</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>2002-10-08</t>
+          <t>2002-04-06</t>
         </is>
       </c>
       <c r="F88" s="18" t="inlineStr">
         <is>
-          <t>Yerraguntla</t>
+          <t>SAVISETTIPALLI</t>
         </is>
       </c>
       <c r="G88" s="17" t="inlineStr">
@@ -8178,12 +8165,12 @@
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
-          <t>Left-arm Spin</t>
+          <t>Right-arm Pace</t>
         </is>
       </c>
       <c r="J88" s="18" t="inlineStr">
         <is>
-          <t>I played lots of tournaments I’m a player of the 7s x1 team</t>
+          <t>6years experience many trophies win</t>
         </is>
       </c>
       <c r="K88" s="17" t="inlineStr">
@@ -8198,7 +8185,7 @@
       </c>
       <c r="M88" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0087</t>
+          <t>TKPL-RCPT-2026-0081</t>
         </is>
       </c>
       <c r="N88" s="20" t="inlineStr">
@@ -8208,12 +8195,12 @@
       </c>
       <c r="O88" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:29 PM</t>
+          <t>30-10-2026 04:06 PM</t>
         </is>
       </c>
       <c r="P88" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:26 PM</t>
+          <t>30-10-2026 04:05 PM</t>
         </is>
       </c>
       <c r="Q88" s="18" t="inlineStr">
@@ -8228,27 +8215,27 @@
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0198</t>
+          <t>TKPL-2026-0194</t>
         </is>
       </c>
       <c r="C89" s="21" t="inlineStr">
         <is>
-          <t>Barigela Suvarthaiah</t>
+          <t>ARSHAD PATAN</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>8125231723</t>
+          <t>8309771127</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>1989-06-25</t>
+          <t>2007-07-09</t>
         </is>
       </c>
       <c r="F89" s="21" t="inlineStr">
         <is>
-          <t>RTPP</t>
+          <t>Kadapa: ayesha shool near pedda darga</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
@@ -8266,7 +8253,12 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J89" s="21" t="inlineStr"/>
+      <c r="J89" s="21" t="inlineStr">
+        <is>
+          <t>ATBPL-1
+ANDHRA TENNIS BALL PERMIER LEAUGE</t>
+        </is>
+      </c>
       <c r="K89" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -8279,7 +8271,7 @@
       </c>
       <c r="M89" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0086</t>
+          <t>TKPL-RCPT-2026-0082</t>
         </is>
       </c>
       <c r="N89" s="22" t="inlineStr">
@@ -8289,12 +8281,12 @@
       </c>
       <c r="O89" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:28 PM</t>
+          <t>30-10-2026 04:11 PM</t>
         </is>
       </c>
       <c r="P89" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:27 PM</t>
+          <t>30-10-2026 04:09 PM</t>
         </is>
       </c>
       <c r="Q89" s="21" t="inlineStr">
@@ -8309,87 +8301,1735 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
+          <t>TKPL-2026-0195</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>M SUBBA REDDY</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>9052632763</t>
+        </is>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>1987-06-06</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>Khajipet</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I90" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J90" s="18" t="inlineStr">
+        <is>
+          <t>Nill</t>
+        </is>
+      </c>
+      <c r="K90" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L90" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M90" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0083</t>
+        </is>
+      </c>
+      <c r="N90" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O90" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:15 PM</t>
+        </is>
+      </c>
+      <c r="P90" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:14 PM</t>
+        </is>
+      </c>
+      <c r="Q90" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0196</t>
+        </is>
+      </c>
+      <c r="C91" s="21" t="inlineStr">
+        <is>
+          <t>Eswar Beema</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>7337007666</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>1993-04-04</t>
+        </is>
+      </c>
+      <c r="F91" s="21" t="inlineStr">
+        <is>
+          <t>Kamalapuram</t>
+        </is>
+      </c>
+      <c r="G91" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H91" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J91" s="21" t="inlineStr"/>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L91" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M91" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0084</t>
+        </is>
+      </c>
+      <c r="N91" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O91" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:17 PM</t>
+        </is>
+      </c>
+      <c r="P91" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:16 PM</t>
+        </is>
+      </c>
+      <c r="Q91" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0197</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>Sameer</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="inlineStr">
+        <is>
+          <t>7013094749</t>
+        </is>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>2002-10-08</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>Yerraguntla</t>
+        </is>
+      </c>
+      <c r="G92" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H92" s="17" t="inlineStr">
+        <is>
+          <t>Left Hand</t>
+        </is>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>Left-arm Spin</t>
+        </is>
+      </c>
+      <c r="J92" s="18" t="inlineStr">
+        <is>
+          <t>I played lots of tournaments I’m a player of the 7s x1 team</t>
+        </is>
+      </c>
+      <c r="K92" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L92" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M92" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0087</t>
+        </is>
+      </c>
+      <c r="N92" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O92" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:29 PM</t>
+        </is>
+      </c>
+      <c r="P92" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:26 PM</t>
+        </is>
+      </c>
+      <c r="Q92" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="13" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0198</t>
+        </is>
+      </c>
+      <c r="C93" s="21" t="inlineStr">
+        <is>
+          <t>Barigela Suvarthaiah</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>8125231723</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>1989-06-25</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="inlineStr">
+        <is>
+          <t>RTPP</t>
+        </is>
+      </c>
+      <c r="G93" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H93" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J93" s="21" t="inlineStr"/>
+      <c r="K93" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L93" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M93" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0086</t>
+        </is>
+      </c>
+      <c r="N93" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O93" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:28 PM</t>
+        </is>
+      </c>
+      <c r="P93" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:27 PM</t>
+        </is>
+      </c>
+      <c r="Q93" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
           <t>TKPL-2026-0199</t>
         </is>
       </c>
-      <c r="C90" s="18" t="inlineStr">
+      <c r="C94" s="18" t="inlineStr">
         <is>
           <t>krishnareddy sirigireddy</t>
         </is>
       </c>
-      <c r="D90" s="17" t="inlineStr">
+      <c r="D94" s="17" t="inlineStr">
         <is>
           <t>9177757989</t>
         </is>
       </c>
-      <c r="E90" s="17" t="inlineStr">
+      <c r="E94" s="17" t="inlineStr">
         <is>
           <t>1985-05-30</t>
         </is>
       </c>
-      <c r="F90" s="18" t="inlineStr">
+      <c r="F94" s="18" t="inlineStr">
         <is>
           <t>Pulivendula</t>
         </is>
       </c>
-      <c r="G90" s="17" t="inlineStr">
+      <c r="G94" s="17" t="inlineStr">
         <is>
           <t>All-Rounder</t>
         </is>
       </c>
-      <c r="H90" s="17" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I90" s="17" t="inlineStr">
+      <c r="H94" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
         <is>
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J90" s="18" t="inlineStr">
+      <c r="J94" s="18" t="inlineStr">
         <is>
           <t>Rayalasima cricket  tournament winner</t>
         </is>
       </c>
-      <c r="K90" s="17" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L90" s="19" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="M90" s="17" t="inlineStr">
+      <c r="K94" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L94" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M94" s="17" t="inlineStr">
         <is>
           <t>TKPL-RCPT-2026-0089</t>
         </is>
       </c>
-      <c r="N90" s="20" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O90" s="17" t="inlineStr">
+      <c r="N94" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O94" s="17" t="inlineStr">
         <is>
           <t>30-10-2026 04:40 PM</t>
         </is>
       </c>
-      <c r="P90" s="17" t="inlineStr">
+      <c r="P94" s="17" t="inlineStr">
         <is>
           <t>30-10-2026 04:29 PM</t>
         </is>
       </c>
-      <c r="Q90" s="18" t="inlineStr">
+      <c r="Q94" s="18" t="inlineStr">
         <is>
           <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0200</t>
+        </is>
+      </c>
+      <c r="C95" s="21" t="inlineStr">
+        <is>
+          <t>pradeep reddy</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>9573562254</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>1995-10-30</t>
+        </is>
+      </c>
+      <c r="F95" s="21" t="inlineStr">
+        <is>
+          <t>Kadapa</t>
+        </is>
+      </c>
+      <c r="G95" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H95" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J95" s="21" t="inlineStr"/>
+      <c r="K95" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L95" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M95" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0090</t>
+        </is>
+      </c>
+      <c r="N95" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O95" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:55 PM</t>
+        </is>
+      </c>
+      <c r="P95" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:47 PM</t>
+        </is>
+      </c>
+      <c r="Q95" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0201</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>B. naveen</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="inlineStr">
+        <is>
+          <t>9392008312</t>
+        </is>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>2006-05-05</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>Veeraballi</t>
+        </is>
+      </c>
+      <c r="G96" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H96" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J96" s="18" t="inlineStr">
+        <is>
+          <t>Playing tournaments</t>
+        </is>
+      </c>
+      <c r="K96" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L96" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M96" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0091</t>
+        </is>
+      </c>
+      <c r="N96" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O96" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:14 PM</t>
+        </is>
+      </c>
+      <c r="P96" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:13 PM</t>
+        </is>
+      </c>
+      <c r="Q96" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0203</t>
+        </is>
+      </c>
+      <c r="C97" s="21" t="inlineStr">
+        <is>
+          <t>RAJASEKHAR SIDDAM</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>7780259251</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="inlineStr">
+        <is>
+          <t>1988-05-01</t>
+        </is>
+      </c>
+      <c r="F97" s="21" t="inlineStr">
+        <is>
+          <t>Marripalli,veerapunayunipalli,kadapa.</t>
+        </is>
+      </c>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>Wicketkeeper</t>
+        </is>
+      </c>
+      <c r="H97" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J97" s="21" t="inlineStr"/>
+      <c r="K97" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L97" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M97" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0107</t>
+        </is>
+      </c>
+      <c r="N97" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O97" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:29 PM</t>
+        </is>
+      </c>
+      <c r="P97" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:23 PM</t>
+        </is>
+      </c>
+      <c r="Q97" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="17" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0204</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>Kanakanti Mohanreddy</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="inlineStr">
+        <is>
+          <t>9390439310</t>
+        </is>
+      </c>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>2000-10-04</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>Rayachoti</t>
+        </is>
+      </c>
+      <c r="G98" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H98" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J98" s="18" t="inlineStr"/>
+      <c r="K98" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L98" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M98" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0092</t>
+        </is>
+      </c>
+      <c r="N98" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O98" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:32 PM</t>
+        </is>
+      </c>
+      <c r="P98" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:31 PM</t>
+        </is>
+      </c>
+      <c r="Q98" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="13" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0205</t>
+        </is>
+      </c>
+      <c r="C99" s="21" t="inlineStr">
+        <is>
+          <t>Shameerbasha</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>8121724624</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="inlineStr">
+        <is>
+          <t>1993-06-26</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="inlineStr">
+        <is>
+          <t>Proddatur</t>
+        </is>
+      </c>
+      <c r="G99" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H99" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Spin</t>
+        </is>
+      </c>
+      <c r="J99" s="21" t="inlineStr"/>
+      <c r="K99" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L99" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M99" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0093</t>
+        </is>
+      </c>
+      <c r="N99" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O99" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:01 PM</t>
+        </is>
+      </c>
+      <c r="P99" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:59 PM</t>
+        </is>
+      </c>
+      <c r="Q99" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0206</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>Abbas Shaik</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="inlineStr">
+        <is>
+          <t>7993419095</t>
+        </is>
+      </c>
+      <c r="E100" s="17" t="inlineStr">
+        <is>
+          <t>1999-08-25</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>Yerraguntla</t>
+        </is>
+      </c>
+      <c r="G100" s="17" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H100" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J100" s="18" t="inlineStr"/>
+      <c r="K100" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L100" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M100" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0094</t>
+        </is>
+      </c>
+      <c r="N100" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O100" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:06 PM</t>
+        </is>
+      </c>
+      <c r="P100" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:05 PM</t>
+        </is>
+      </c>
+      <c r="Q100" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0207</t>
+        </is>
+      </c>
+      <c r="C101" s="21" t="inlineStr">
+        <is>
+          <t>Potu Chandra</t>
+        </is>
+      </c>
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>8885333362</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr">
+        <is>
+          <t>1991-05-30</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="inlineStr">
+        <is>
+          <t>Y S R Kadapa</t>
+        </is>
+      </c>
+      <c r="G101" s="13" t="inlineStr">
+        <is>
+          <t>Wicketkeeper</t>
+        </is>
+      </c>
+      <c r="H101" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J101" s="21" t="inlineStr"/>
+      <c r="K101" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L101" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M101" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0108</t>
+        </is>
+      </c>
+      <c r="N101" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O101" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:29 PM</t>
+        </is>
+      </c>
+      <c r="P101" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:20 PM</t>
+        </is>
+      </c>
+      <c r="Q101" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0208</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>S Malli Naidu</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t>6302935195</t>
+        </is>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>2005-06-15</t>
+        </is>
+      </c>
+      <c r="F102" s="18" t="inlineStr">
+        <is>
+          <t>Rayachoty</t>
+        </is>
+      </c>
+      <c r="G102" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H102" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J102" s="18" t="inlineStr">
+        <is>
+          <t>Local tournaments and other tournaments</t>
+        </is>
+      </c>
+      <c r="K102" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L102" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M102" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0095</t>
+        </is>
+      </c>
+      <c r="N102" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O102" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:51 PM</t>
+        </is>
+      </c>
+      <c r="P102" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:48 PM</t>
+        </is>
+      </c>
+      <c r="Q102" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0209</t>
+        </is>
+      </c>
+      <c r="C103" s="21" t="inlineStr">
+        <is>
+          <t>PUSHPAGIRI CHANDRAKANTH</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>9347305959</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="inlineStr">
+        <is>
+          <t>1993-06-12</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="inlineStr">
+        <is>
+          <t>VEERAPUNAYUNIPALLI, kadapa</t>
+        </is>
+      </c>
+      <c r="G103" s="13" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H103" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J103" s="21" t="inlineStr"/>
+      <c r="K103" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L103" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M103" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0097</t>
+        </is>
+      </c>
+      <c r="N103" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O103" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:03 PM</t>
+        </is>
+      </c>
+      <c r="P103" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:00 PM</t>
+        </is>
+      </c>
+      <c r="Q103" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="17" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0210</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>Yorker Yunus</t>
+        </is>
+      </c>
+      <c r="D104" s="17" t="inlineStr">
+        <is>
+          <t>7095231174</t>
+        </is>
+      </c>
+      <c r="E104" s="17" t="inlineStr">
+        <is>
+          <t>2005-03-28</t>
+        </is>
+      </c>
+      <c r="F104" s="18" t="inlineStr">
+        <is>
+          <t>Nandimandalam , kadapa district</t>
+        </is>
+      </c>
+      <c r="G104" s="17" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H104" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I104" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J104" s="18" t="inlineStr">
+        <is>
+          <t>Pulivendula tournaments and produtur tournament</t>
+        </is>
+      </c>
+      <c r="K104" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L104" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M104" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0098</t>
+        </is>
+      </c>
+      <c r="N104" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O104" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:04 PM</t>
+        </is>
+      </c>
+      <c r="P104" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:03 PM</t>
+        </is>
+      </c>
+      <c r="Q104" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0211</t>
+        </is>
+      </c>
+      <c r="C105" s="21" t="inlineStr">
+        <is>
+          <t>Jalla mahesh Kumar</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>8142609575</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr">
+        <is>
+          <t>1991-06-18</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="inlineStr">
+        <is>
+          <t>Rayachoty</t>
+        </is>
+      </c>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H105" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J105" s="21" t="inlineStr"/>
+      <c r="K105" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L105" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M105" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0100</t>
+        </is>
+      </c>
+      <c r="N105" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O105" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:08 PM</t>
+        </is>
+      </c>
+      <c r="P105" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:06 PM</t>
+        </is>
+      </c>
+      <c r="Q105" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0213</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>Pandiboti jagadeesh</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t>6303081193</t>
+        </is>
+      </c>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t>2003-06-10</t>
+        </is>
+      </c>
+      <c r="F106" s="18" t="inlineStr">
+        <is>
+          <t>Chakrayapeta</t>
+        </is>
+      </c>
+      <c r="G106" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H106" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I106" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J106" s="18" t="inlineStr"/>
+      <c r="K106" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L106" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M106" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0101</t>
+        </is>
+      </c>
+      <c r="N106" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O106" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:40 PM</t>
+        </is>
+      </c>
+      <c r="P106" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:36 PM</t>
+        </is>
+      </c>
+      <c r="Q106" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0214</t>
+        </is>
+      </c>
+      <c r="C107" s="21" t="inlineStr">
+        <is>
+          <t>Y Dharma Teja</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>9963603701</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="inlineStr">
+        <is>
+          <t>2008-01-04</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H107" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J107" s="21" t="inlineStr"/>
+      <c r="K107" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L107" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M107" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0102</t>
+        </is>
+      </c>
+      <c r="N107" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O107" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:42 PM</t>
+        </is>
+      </c>
+      <c r="P107" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:39 PM</t>
+        </is>
+      </c>
+      <c r="Q107" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0215</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>PALEM CHANDU</t>
+        </is>
+      </c>
+      <c r="D108" s="17" t="inlineStr">
+        <is>
+          <t>7093616070</t>
+        </is>
+      </c>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t>2008-08-10</t>
+        </is>
+      </c>
+      <c r="F108" s="18" t="inlineStr">
+        <is>
+          <t>Gonumakulapalli</t>
+        </is>
+      </c>
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H108" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J108" s="18" t="inlineStr">
+        <is>
+          <t>U-12 south zone  u-16 districts  30+ local tournaments</t>
+        </is>
+      </c>
+      <c r="K108" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L108" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M108" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0103</t>
+        </is>
+      </c>
+      <c r="N108" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O108" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:08 PM</t>
+        </is>
+      </c>
+      <c r="P108" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:06 PM</t>
+        </is>
+      </c>
+      <c r="Q108" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="13" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0216</t>
+        </is>
+      </c>
+      <c r="C109" s="21" t="inlineStr">
+        <is>
+          <t>Moillacheru Mahesh</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>6304114231</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>1998-06-20</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G109" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H109" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J109" s="21" t="inlineStr"/>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L109" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M109" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0104</t>
+        </is>
+      </c>
+      <c r="N109" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O109" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:12 PM</t>
+        </is>
+      </c>
+      <c r="P109" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:11 PM</t>
+        </is>
+      </c>
+      <c r="Q109" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="17" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0217</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>Kasthuri saikumar(power sai)</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t>8886440355</t>
+        </is>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>1998-06-11</t>
+        </is>
+      </c>
+      <c r="F110" s="18" t="inlineStr">
+        <is>
+          <t>Nandhimandalam</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H110" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J110" s="18" t="inlineStr">
+        <is>
+          <t>Local tournaments</t>
+        </is>
+      </c>
+      <c r="K110" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L110" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M110" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0106</t>
+        </is>
+      </c>
+      <c r="N110" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O110" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:24 PM</t>
+        </is>
+      </c>
+      <c r="P110" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:23 PM</t>
+        </is>
+      </c>
+      <c r="Q110" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q90"/>
+  <autoFilter ref="A1:Q110"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8400,7 +10040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8847,32 +10487,32 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0152</t>
+          <t>TKPL-2026-0158</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>Niranjan Kumar</t>
+          <t>Shaikbabaji</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>7032538123</t>
+          <t>9885626641</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>2001-05-05</t>
+          <t>1996-01-17</t>
         </is>
       </c>
       <c r="F6" s="18" t="inlineStr">
         <is>
-          <t>T sundupalli</t>
+          <t>Nagulaguttapalli</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
@@ -8882,10 +10522,14 @@
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>Left-arm Pace</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr"/>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>I have  local tournaments  experience</t>
+        </is>
+      </c>
       <c r="K6" s="17" t="inlineStr">
         <is>
           <t>Submitted</t>
@@ -8913,7 +10557,7 @@
       </c>
       <c r="P6" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:06 PM</t>
+          <t>30-10-2026 01:19 PM</t>
         </is>
       </c>
       <c r="Q6" s="18" t="inlineStr">
@@ -8928,32 +10572,32 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0154</t>
+          <t>TKPL-2026-0164</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>Venkatakumar S</t>
+          <t>Bhanu prakash</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>9390667626</t>
+          <t>9100859612</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>2002-02-04</t>
+          <t>2008-09-21</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t>Rayachoty  vemaplli   road B T palli</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -8963,10 +10607,14 @@
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>Left-arm Pace</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr"/>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>Renadu titians and pai viecory tirupati</t>
+        </is>
+      </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
           <t>Submitted</t>
@@ -8994,7 +10642,7 @@
       </c>
       <c r="P7" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:11 PM</t>
+          <t>30-10-2026 01:49 PM</t>
         </is>
       </c>
       <c r="Q7" s="21" t="inlineStr">
@@ -9009,27 +10657,27 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0158</t>
+          <t>TKPL-2026-0202</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>Shaikbabaji</t>
+          <t>R shahabuddin</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>9885626641</t>
+          <t>8639460531</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>1996-01-17</t>
+          <t>2009-08-20</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">
         <is>
-          <t>Nagulaguttapalli</t>
+          <t>Khajipeta</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
@@ -9047,11 +10695,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>I have  local tournaments  experience</t>
-        </is>
-      </c>
+      <c r="J8" s="18" t="inlineStr"/>
       <c r="K8" s="17" t="inlineStr">
         <is>
           <t>Submitted</t>
@@ -9079,7 +10723,7 @@
       </c>
       <c r="P8" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:19 PM</t>
+          <t>30-10-2026 05:16 PM</t>
         </is>
       </c>
       <c r="Q8" s="18" t="inlineStr">
@@ -9094,27 +10738,27 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0164</t>
+          <t>TKPL-2026-0212</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>Bhanu prakash</t>
+          <t>Rachamallu Mallikarjuna Reddy</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>9100859612</t>
+          <t>9652490435</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>2008-09-21</t>
+          <t>1990-07-06</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Vempalli</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
@@ -9132,11 +10776,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t>Renadu titians and pai viecory tirupati</t>
-        </is>
-      </c>
+      <c r="J9" s="21" t="inlineStr"/>
       <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Submitted</t>
@@ -9164,7 +10804,7 @@
       </c>
       <c r="P9" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:49 PM</t>
+          <t>30-10-2026 07:32 PM</t>
         </is>
       </c>
       <c r="Q9" s="21" t="inlineStr">
@@ -9173,170 +10813,8 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>TKPL-2026-0173</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Yellutla ravikumar naidu</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>9705490252</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>2005-03-16</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>Chinamandam</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>All-Rounder</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>Left Hand</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>Left-arm Spin</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="inlineStr"/>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L10" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P10" s="17" t="inlineStr">
-        <is>
-          <t>30-10-2026 02:48 PM</t>
-        </is>
-      </c>
-      <c r="Q10" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>TKPL-2026-0177</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>Yellutla Sree hari naidu</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>6281999214</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>2009-04-10</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>Chinamandam</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>All-Rounder</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="inlineStr"/>
-      <c r="K11" s="13" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L11" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="M11" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="22" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P11" s="13" t="inlineStr">
-        <is>
-          <t>30-10-2026 03:06 PM</t>
-        </is>
-      </c>
-      <c r="Q11" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q11"/>
+  <autoFilter ref="A1:Q9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9347,7 +10825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:Q118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13767,17 +15245,17 @@
       <c r="J53" s="21" t="inlineStr"/>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L53" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L53" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TKPL-RCPT-2026-0109</t>
         </is>
       </c>
       <c r="N53" s="22" t="inlineStr">
@@ -13787,7 +15265,7 @@
       </c>
       <c r="O53" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30-10-2026 08:30 PM</t>
         </is>
       </c>
       <c r="P53" s="13" t="inlineStr">
@@ -13797,7 +15275,7 @@
       </c>
       <c r="Q53" s="21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -13933,17 +15411,17 @@
       <c r="J55" s="21" t="inlineStr"/>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L55" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L55" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TKPL-RCPT-2026-0105</t>
         </is>
       </c>
       <c r="N55" s="22" t="inlineStr">
@@ -13953,7 +15431,7 @@
       </c>
       <c r="O55" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30-10-2026 08:16 PM</t>
         </is>
       </c>
       <c r="P55" s="13" t="inlineStr">
@@ -13963,7 +15441,7 @@
       </c>
       <c r="Q55" s="21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -15517,17 +16995,17 @@
       <c r="J74" s="18" t="inlineStr"/>
       <c r="K74" s="17" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L74" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L74" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M74" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TKPL-RCPT-2026-0096</t>
         </is>
       </c>
       <c r="N74" s="20" t="inlineStr">
@@ -15537,7 +17015,7 @@
       </c>
       <c r="O74" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30-10-2026 07:02 PM</t>
         </is>
       </c>
       <c r="P74" s="17" t="inlineStr">
@@ -15547,7 +17025,7 @@
       </c>
       <c r="Q74" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -15849,17 +17327,17 @@
       <c r="J78" s="18" t="inlineStr"/>
       <c r="K78" s="17" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L78" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L78" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TKPL-RCPT-2026-0099</t>
         </is>
       </c>
       <c r="N78" s="20" t="inlineStr">
@@ -15869,7 +17347,7 @@
       </c>
       <c r="O78" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30-10-2026 07:06 PM</t>
         </is>
       </c>
       <c r="P78" s="17" t="inlineStr">
@@ -15879,7 +17357,7 @@
       </c>
       <c r="Q78" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -17726,8 +19204,1486 @@
         </is>
       </c>
     </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0200</t>
+        </is>
+      </c>
+      <c r="C101" s="21" t="inlineStr">
+        <is>
+          <t>pradeep reddy</t>
+        </is>
+      </c>
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>9573562254</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr">
+        <is>
+          <t>1995-10-30</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="inlineStr">
+        <is>
+          <t>Kadapa</t>
+        </is>
+      </c>
+      <c r="G101" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H101" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J101" s="21" t="inlineStr"/>
+      <c r="K101" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L101" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M101" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0090</t>
+        </is>
+      </c>
+      <c r="N101" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O101" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:55 PM</t>
+        </is>
+      </c>
+      <c r="P101" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 04:47 PM</t>
+        </is>
+      </c>
+      <c r="Q101" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0201</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>B. naveen</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t>9392008312</t>
+        </is>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>2006-05-05</t>
+        </is>
+      </c>
+      <c r="F102" s="18" t="inlineStr">
+        <is>
+          <t>Veeraballi</t>
+        </is>
+      </c>
+      <c r="G102" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H102" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J102" s="18" t="inlineStr">
+        <is>
+          <t>Playing tournaments</t>
+        </is>
+      </c>
+      <c r="K102" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L102" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M102" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0091</t>
+        </is>
+      </c>
+      <c r="N102" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O102" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:14 PM</t>
+        </is>
+      </c>
+      <c r="P102" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:13 PM</t>
+        </is>
+      </c>
+      <c r="Q102" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0202</t>
+        </is>
+      </c>
+      <c r="C103" s="21" t="inlineStr">
+        <is>
+          <t>R shahabuddin</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>8639460531</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="inlineStr">
+        <is>
+          <t>2009-08-20</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="inlineStr">
+        <is>
+          <t>Khajipeta</t>
+        </is>
+      </c>
+      <c r="G103" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H103" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J103" s="21" t="inlineStr"/>
+      <c r="K103" s="13" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="L103" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M103" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O103" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P103" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:16 PM</t>
+        </is>
+      </c>
+      <c r="Q103" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="17" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0203</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>RAJASEKHAR SIDDAM</t>
+        </is>
+      </c>
+      <c r="D104" s="17" t="inlineStr">
+        <is>
+          <t>7780259251</t>
+        </is>
+      </c>
+      <c r="E104" s="17" t="inlineStr">
+        <is>
+          <t>1988-05-01</t>
+        </is>
+      </c>
+      <c r="F104" s="18" t="inlineStr">
+        <is>
+          <t>Marripalli,veerapunayunipalli,kadapa.</t>
+        </is>
+      </c>
+      <c r="G104" s="17" t="inlineStr">
+        <is>
+          <t>Wicketkeeper</t>
+        </is>
+      </c>
+      <c r="H104" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I104" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J104" s="18" t="inlineStr"/>
+      <c r="K104" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L104" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M104" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0107</t>
+        </is>
+      </c>
+      <c r="N104" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O104" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:29 PM</t>
+        </is>
+      </c>
+      <c r="P104" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:23 PM</t>
+        </is>
+      </c>
+      <c r="Q104" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0204</t>
+        </is>
+      </c>
+      <c r="C105" s="21" t="inlineStr">
+        <is>
+          <t>Kanakanti Mohanreddy</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>9390439310</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr">
+        <is>
+          <t>2000-10-04</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="inlineStr">
+        <is>
+          <t>Rayachoti</t>
+        </is>
+      </c>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H105" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J105" s="21" t="inlineStr"/>
+      <c r="K105" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L105" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M105" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0092</t>
+        </is>
+      </c>
+      <c r="N105" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O105" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:32 PM</t>
+        </is>
+      </c>
+      <c r="P105" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:31 PM</t>
+        </is>
+      </c>
+      <c r="Q105" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0205</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>Shameerbasha</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="inlineStr">
+        <is>
+          <t>8121724624</t>
+        </is>
+      </c>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t>1993-06-26</t>
+        </is>
+      </c>
+      <c r="F106" s="18" t="inlineStr">
+        <is>
+          <t>Proddatur</t>
+        </is>
+      </c>
+      <c r="G106" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H106" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I106" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Spin</t>
+        </is>
+      </c>
+      <c r="J106" s="18" t="inlineStr"/>
+      <c r="K106" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L106" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M106" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0093</t>
+        </is>
+      </c>
+      <c r="N106" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O106" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:01 PM</t>
+        </is>
+      </c>
+      <c r="P106" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 05:59 PM</t>
+        </is>
+      </c>
+      <c r="Q106" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0206</t>
+        </is>
+      </c>
+      <c r="C107" s="21" t="inlineStr">
+        <is>
+          <t>Abbas Shaik</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>7993419095</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="inlineStr">
+        <is>
+          <t>1999-08-25</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="inlineStr">
+        <is>
+          <t>Yerraguntla</t>
+        </is>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H107" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J107" s="21" t="inlineStr"/>
+      <c r="K107" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L107" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M107" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0094</t>
+        </is>
+      </c>
+      <c r="N107" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O107" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:06 PM</t>
+        </is>
+      </c>
+      <c r="P107" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:05 PM</t>
+        </is>
+      </c>
+      <c r="Q107" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0207</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>Potu Chandra</t>
+        </is>
+      </c>
+      <c r="D108" s="17" t="inlineStr">
+        <is>
+          <t>8885333362</t>
+        </is>
+      </c>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t>1991-05-30</t>
+        </is>
+      </c>
+      <c r="F108" s="18" t="inlineStr">
+        <is>
+          <t>Y S R Kadapa</t>
+        </is>
+      </c>
+      <c r="G108" s="17" t="inlineStr">
+        <is>
+          <t>Wicketkeeper</t>
+        </is>
+      </c>
+      <c r="H108" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J108" s="18" t="inlineStr"/>
+      <c r="K108" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L108" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M108" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0108</t>
+        </is>
+      </c>
+      <c r="N108" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O108" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:29 PM</t>
+        </is>
+      </c>
+      <c r="P108" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:20 PM</t>
+        </is>
+      </c>
+      <c r="Q108" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="13" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0208</t>
+        </is>
+      </c>
+      <c r="C109" s="21" t="inlineStr">
+        <is>
+          <t>S Malli Naidu</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>6302935195</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>2005-06-15</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="inlineStr">
+        <is>
+          <t>Rayachoty</t>
+        </is>
+      </c>
+      <c r="G109" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H109" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J109" s="21" t="inlineStr">
+        <is>
+          <t>Local tournaments and other tournaments</t>
+        </is>
+      </c>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L109" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M109" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0095</t>
+        </is>
+      </c>
+      <c r="N109" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O109" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:51 PM</t>
+        </is>
+      </c>
+      <c r="P109" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 06:48 PM</t>
+        </is>
+      </c>
+      <c r="Q109" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="17" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0209</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>PUSHPAGIRI CHANDRAKANTH</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t>9347305959</t>
+        </is>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>1993-06-12</t>
+        </is>
+      </c>
+      <c r="F110" s="18" t="inlineStr">
+        <is>
+          <t>VEERAPUNAYUNIPALLI, kadapa</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H110" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J110" s="18" t="inlineStr"/>
+      <c r="K110" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L110" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M110" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0097</t>
+        </is>
+      </c>
+      <c r="N110" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O110" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:03 PM</t>
+        </is>
+      </c>
+      <c r="P110" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:00 PM</t>
+        </is>
+      </c>
+      <c r="Q110" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0210</t>
+        </is>
+      </c>
+      <c r="C111" s="21" t="inlineStr">
+        <is>
+          <t>Yorker Yunus</t>
+        </is>
+      </c>
+      <c r="D111" s="13" t="inlineStr">
+        <is>
+          <t>7095231174</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>2005-03-28</t>
+        </is>
+      </c>
+      <c r="F111" s="21" t="inlineStr">
+        <is>
+          <t>Nandimandalam , kadapa district</t>
+        </is>
+      </c>
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H111" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J111" s="21" t="inlineStr">
+        <is>
+          <t>Pulivendula tournaments and produtur tournament</t>
+        </is>
+      </c>
+      <c r="K111" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L111" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M111" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0098</t>
+        </is>
+      </c>
+      <c r="N111" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O111" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:04 PM</t>
+        </is>
+      </c>
+      <c r="P111" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:03 PM</t>
+        </is>
+      </c>
+      <c r="Q111" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="17" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0211</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>Jalla mahesh Kumar</t>
+        </is>
+      </c>
+      <c r="D112" s="17" t="inlineStr">
+        <is>
+          <t>8142609575</t>
+        </is>
+      </c>
+      <c r="E112" s="17" t="inlineStr">
+        <is>
+          <t>1991-06-18</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>Rayachoty</t>
+        </is>
+      </c>
+      <c r="G112" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H112" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J112" s="18" t="inlineStr"/>
+      <c r="K112" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L112" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M112" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0100</t>
+        </is>
+      </c>
+      <c r="N112" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O112" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:08 PM</t>
+        </is>
+      </c>
+      <c r="P112" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:06 PM</t>
+        </is>
+      </c>
+      <c r="Q112" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0212</t>
+        </is>
+      </c>
+      <c r="C113" s="21" t="inlineStr">
+        <is>
+          <t>Rachamallu Mallikarjuna Reddy</t>
+        </is>
+      </c>
+      <c r="D113" s="13" t="inlineStr">
+        <is>
+          <t>9652490435</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>1990-07-06</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t>Vempalli</t>
+        </is>
+      </c>
+      <c r="G113" s="13" t="inlineStr">
+        <is>
+          <t>Wicketkeeper</t>
+        </is>
+      </c>
+      <c r="H113" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J113" s="21" t="inlineStr"/>
+      <c r="K113" s="13" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="L113" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M113" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O113" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P113" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:32 PM</t>
+        </is>
+      </c>
+      <c r="Q113" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="17" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0213</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
+        <is>
+          <t>Pandiboti jagadeesh</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="inlineStr">
+        <is>
+          <t>6303081193</t>
+        </is>
+      </c>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>2003-06-10</t>
+        </is>
+      </c>
+      <c r="F114" s="18" t="inlineStr">
+        <is>
+          <t>Chakrayapeta</t>
+        </is>
+      </c>
+      <c r="G114" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H114" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I114" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J114" s="18" t="inlineStr"/>
+      <c r="K114" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L114" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M114" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0101</t>
+        </is>
+      </c>
+      <c r="N114" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O114" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:40 PM</t>
+        </is>
+      </c>
+      <c r="P114" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:36 PM</t>
+        </is>
+      </c>
+      <c r="Q114" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="13" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0214</t>
+        </is>
+      </c>
+      <c r="C115" s="21" t="inlineStr">
+        <is>
+          <t>Y Dharma Teja</t>
+        </is>
+      </c>
+      <c r="D115" s="13" t="inlineStr">
+        <is>
+          <t>9963603701</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="inlineStr">
+        <is>
+          <t>2008-01-04</t>
+        </is>
+      </c>
+      <c r="F115" s="21" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G115" s="13" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H115" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J115" s="21" t="inlineStr"/>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L115" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M115" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0102</t>
+        </is>
+      </c>
+      <c r="N115" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O115" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:42 PM</t>
+        </is>
+      </c>
+      <c r="P115" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 07:39 PM</t>
+        </is>
+      </c>
+      <c r="Q115" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="17" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0215</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>PALEM CHANDU</t>
+        </is>
+      </c>
+      <c r="D116" s="17" t="inlineStr">
+        <is>
+          <t>7093616070</t>
+        </is>
+      </c>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t>2008-08-10</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="inlineStr">
+        <is>
+          <t>Gonumakulapalli</t>
+        </is>
+      </c>
+      <c r="G116" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H116" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J116" s="18" t="inlineStr">
+        <is>
+          <t>U-12 south zone  u-16 districts  30+ local tournaments</t>
+        </is>
+      </c>
+      <c r="K116" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L116" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M116" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0103</t>
+        </is>
+      </c>
+      <c r="N116" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O116" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:08 PM</t>
+        </is>
+      </c>
+      <c r="P116" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:06 PM</t>
+        </is>
+      </c>
+      <c r="Q116" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="13" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0216</t>
+        </is>
+      </c>
+      <c r="C117" s="21" t="inlineStr">
+        <is>
+          <t>Moillacheru Mahesh</t>
+        </is>
+      </c>
+      <c r="D117" s="13" t="inlineStr">
+        <is>
+          <t>6304114231</t>
+        </is>
+      </c>
+      <c r="E117" s="13" t="inlineStr">
+        <is>
+          <t>1998-06-20</t>
+        </is>
+      </c>
+      <c r="F117" s="21" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G117" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H117" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J117" s="21" t="inlineStr"/>
+      <c r="K117" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L117" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M117" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0104</t>
+        </is>
+      </c>
+      <c r="N117" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O117" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:12 PM</t>
+        </is>
+      </c>
+      <c r="P117" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:11 PM</t>
+        </is>
+      </c>
+      <c r="Q117" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0217</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>Kasthuri saikumar(power sai)</t>
+        </is>
+      </c>
+      <c r="D118" s="17" t="inlineStr">
+        <is>
+          <t>8886440355</t>
+        </is>
+      </c>
+      <c r="E118" s="17" t="inlineStr">
+        <is>
+          <t>1998-06-11</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>Nandhimandalam</t>
+        </is>
+      </c>
+      <c r="G118" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H118" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I118" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J118" s="18" t="inlineStr">
+        <is>
+          <t>Local tournaments</t>
+        </is>
+      </c>
+      <c r="K118" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L118" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M118" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0106</t>
+        </is>
+      </c>
+      <c r="N118" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O118" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:24 PM</t>
+        </is>
+      </c>
+      <c r="P118" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:23 PM</t>
+        </is>
+      </c>
+      <c r="Q118" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q100"/>
+  <autoFilter ref="A1:Q118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/TKPL_Registered_Players.xlsx
+++ b/reports/TKPL_Registered_Players.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Summary Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Approved &amp; Verified (109)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Payment Pending (8)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="All Registrations (117)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Approved &amp; Verified (133)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Payment Pending (10)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All Registrations (143)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Approved &amp; Verified (109)'!$A$1:$Q$110</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Payment Pending (8)'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Registrations (117)'!$A$1:$Q$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Approved &amp; Verified (133)'!$A$1:$Q$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Payment Pending (10)'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Registrations (143)'!$A$1:$Q$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -665,7 +665,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Live Roster Report — Generated on 30 Oct 2026, 08:35 PM IST</t>
+          <t>Live Roster Report — Generated on 31 Oct 2026, 01:00 PM IST</t>
         </is>
       </c>
     </row>
@@ -697,25 +697,25 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>143</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>₹43,491</t>
+          <t>₹53,067</t>
         </is>
       </c>
     </row>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>0</v>
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -803,13 +803,13 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q110"/>
+  <dimension ref="A1:Q134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5376,27 +5376,27 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0159</t>
+          <t>TKPL-2026-0158</t>
         </is>
       </c>
       <c r="C55" s="21" t="inlineStr">
         <is>
-          <t>shaik Mynuddin</t>
+          <t>Shaikbabaji</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>8885266722</t>
+          <t>9885626641</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>1998-06-06</t>
+          <t>1996-01-17</t>
         </is>
       </c>
       <c r="F55" s="21" t="inlineStr">
         <is>
-          <t>Lakkireddy palli (m) ,Rayachoty</t>
+          <t>Nagulaguttapalli</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="J55" s="21" t="inlineStr">
         <is>
-          <t>MNR cricket tournament, Vijay primier League, friends cricket league etc...</t>
+          <t>I have  local tournaments  experience</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0043</t>
+          <t>TKPL-RCPT-2026-0130</t>
         </is>
       </c>
       <c r="N55" s="22" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O55" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:22 PM</t>
+          <t>31-10-2026 11:12 AM</t>
         </is>
       </c>
       <c r="P55" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:22 PM</t>
+          <t>30-10-2026 01:19 PM</t>
         </is>
       </c>
       <c r="Q55" s="21" t="inlineStr">
@@ -5461,27 +5461,27 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0160</t>
+          <t>TKPL-2026-0159</t>
         </is>
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>Shaik Saddam Hussain</t>
+          <t>shaik Mynuddin</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
         <is>
-          <t>8374530338</t>
+          <t>8885266722</t>
         </is>
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>1995-06-05</t>
+          <t>1998-06-06</t>
         </is>
       </c>
       <c r="F56" s="18" t="inlineStr">
         <is>
-          <t>6-6, Thurakapalli, Gurrappagari Palli(Post), Veeraballi(M),YSR KADAPA (Dt))</t>
+          <t>Lakkireddy palli (m) ,Rayachoty</t>
         </is>
       </c>
       <c r="G56" s="17" t="inlineStr">
@@ -5499,7 +5499,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J56" s="18" t="inlineStr"/>
+      <c r="J56" s="18" t="inlineStr">
+        <is>
+          <t>MNR cricket tournament, Vijay primier League, friends cricket league etc...</t>
+        </is>
+      </c>
       <c r="K56" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5512,7 +5516,7 @@
       </c>
       <c r="M56" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0044</t>
+          <t>TKPL-RCPT-2026-0043</t>
         </is>
       </c>
       <c r="N56" s="20" t="inlineStr">
@@ -5522,7 +5526,7 @@
       </c>
       <c r="O56" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:23 PM</t>
+          <t>30-10-2026 01:22 PM</t>
         </is>
       </c>
       <c r="P56" s="17" t="inlineStr">
@@ -5542,32 +5546,32 @@
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0161</t>
+          <t>TKPL-2026-0160</t>
         </is>
       </c>
       <c r="C57" s="21" t="inlineStr">
         <is>
-          <t>Jaffar khan phatan</t>
+          <t>Shaik Saddam Hussain</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>9160616545</t>
+          <t>8374530338</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>2001-11-15</t>
+          <t>1995-06-05</t>
         </is>
       </c>
       <c r="F57" s="21" t="inlineStr">
         <is>
-          <t>Nandalur mandal kadapa district</t>
+          <t>6-6, Thurakapalli, Gurrappagari Palli(Post), Veeraballi(M),YSR KADAPA (Dt))</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
@@ -5593,7 +5597,7 @@
       </c>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0045</t>
+          <t>TKPL-RCPT-2026-0044</t>
         </is>
       </c>
       <c r="N57" s="22" t="inlineStr">
@@ -5603,12 +5607,12 @@
       </c>
       <c r="O57" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:27 PM</t>
+          <t>30-10-2026 01:23 PM</t>
         </is>
       </c>
       <c r="P57" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:26 PM</t>
+          <t>30-10-2026 01:22 PM</t>
         </is>
       </c>
       <c r="Q57" s="21" t="inlineStr">
@@ -5623,45 +5627,126 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
+          <t>TKPL-2026-0161</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>Jaffar khan phatan</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>9160616545</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>2001-11-15</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>Nandalur mandal kadapa district</t>
+        </is>
+      </c>
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H58" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J58" s="18" t="inlineStr"/>
+      <c r="K58" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L58" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M58" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0045</t>
+        </is>
+      </c>
+      <c r="N58" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O58" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 01:27 PM</t>
+        </is>
+      </c>
+      <c r="P58" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 01:26 PM</t>
+        </is>
+      </c>
+      <c r="Q58" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
           <t>TKPL-2026-0162</t>
         </is>
       </c>
-      <c r="C58" s="18" t="inlineStr">
+      <c r="C59" s="21" t="inlineStr">
         <is>
           <t>Mude Shankar naik</t>
         </is>
       </c>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>9502271805</t>
         </is>
       </c>
-      <c r="E58" s="17" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>2008-06-26</t>
         </is>
       </c>
-      <c r="F58" s="18" t="inlineStr">
+      <c r="F59" s="21" t="inlineStr">
         <is>
           <t>Galiveedu</t>
         </is>
       </c>
-      <c r="G58" s="17" t="inlineStr">
+      <c r="G59" s="13" t="inlineStr">
         <is>
           <t>Batter</t>
         </is>
       </c>
-      <c r="H58" s="17" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I58" s="17" t="inlineStr">
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J58" s="18" t="inlineStr">
+      <c r="J59" s="21" t="inlineStr">
         <is>
           <t>51(21) 4s-5 6s-3
 50 runs in a limited over match. Super!. See on CricHeroes. https://cricheroes.in/scorecard/26220470/until-unity-club-/peruru-11-vs-ashok-11s
@@ -5671,119 +5756,34 @@
 https://crhero.link/campaign/apps</t>
         </is>
       </c>
-      <c r="K58" s="17" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L58" s="19" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="M58" s="17" t="inlineStr">
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L59" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M59" s="13" t="inlineStr">
         <is>
           <t>TKPL-RCPT-2026-0048</t>
         </is>
       </c>
-      <c r="N58" s="20" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O58" s="17" t="inlineStr">
+      <c r="N59" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O59" s="13" t="inlineStr">
         <is>
           <t>30-10-2026 01:45 PM</t>
         </is>
       </c>
-      <c r="P58" s="17" t="inlineStr">
+      <c r="P59" s="13" t="inlineStr">
         <is>
           <t>30-10-2026 01:31 PM</t>
-        </is>
-      </c>
-      <c r="Q58" s="18" t="inlineStr">
-        <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="13" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="13" t="inlineStr">
-        <is>
-          <t>TKPL-2026-0163</t>
-        </is>
-      </c>
-      <c r="C59" s="21" t="inlineStr">
-        <is>
-          <t>Dasari palli Abhishek</t>
-        </is>
-      </c>
-      <c r="D59" s="13" t="inlineStr">
-        <is>
-          <t>9390757461</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
-        <is>
-          <t>2005-07-19</t>
-        </is>
-      </c>
-      <c r="F59" s="21" t="inlineStr">
-        <is>
-          <t>Porumamilla</t>
-        </is>
-      </c>
-      <c r="G59" s="13" t="inlineStr">
-        <is>
-          <t>Batter</t>
-        </is>
-      </c>
-      <c r="H59" s="13" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J59" s="21" t="inlineStr">
-        <is>
-          <t>6years experience</t>
-        </is>
-      </c>
-      <c r="K59" s="13" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L59" s="19" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="M59" s="13" t="inlineStr">
-        <is>
-          <t>TKPL-RCPT-2026-0046</t>
-        </is>
-      </c>
-      <c r="N59" s="22" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O59" s="13" t="inlineStr">
-        <is>
-          <t>30-10-2026 01:43 PM</t>
-        </is>
-      </c>
-      <c r="P59" s="13" t="inlineStr">
-        <is>
-          <t>30-10-2026 01:42 PM</t>
         </is>
       </c>
       <c r="Q59" s="21" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0165</t>
+          <t>TKPL-2026-0163</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>samuel chakravarthy</t>
+          <t>Dasari palli Abhishek</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>9962511777</t>
+          <t>9390757461</t>
         </is>
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>1983-07-11</t>
+          <t>2005-07-19</t>
         </is>
       </c>
       <c r="F60" s="18" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Porumamilla</t>
         </is>
       </c>
       <c r="G60" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
@@ -5836,7 +5836,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J60" s="18" t="inlineStr"/>
+      <c r="J60" s="18" t="inlineStr">
+        <is>
+          <t>6years experience</t>
+        </is>
+      </c>
       <c r="K60" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5849,7 +5853,7 @@
       </c>
       <c r="M60" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0050</t>
+          <t>TKPL-RCPT-2026-0046</t>
         </is>
       </c>
       <c r="N60" s="20" t="inlineStr">
@@ -5859,12 +5863,12 @@
       </c>
       <c r="O60" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:03 PM</t>
+          <t>30-10-2026 01:43 PM</t>
         </is>
       </c>
       <c r="P60" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:56 PM</t>
+          <t>30-10-2026 01:42 PM</t>
         </is>
       </c>
       <c r="Q60" s="18" t="inlineStr">
@@ -5879,27 +5883,27 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0166</t>
+          <t>TKPL-2026-0165</t>
         </is>
       </c>
       <c r="C61" s="21" t="inlineStr">
         <is>
-          <t>M SYED NASRUDDIN</t>
+          <t>samuel chakravarthy</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>9494040272</t>
+          <t>9962511777</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>1997-08-08</t>
+          <t>1983-07-11</t>
         </is>
       </c>
       <c r="F61" s="21" t="inlineStr">
         <is>
-          <t>PRODDATUR</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
@@ -5917,11 +5921,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J61" s="21" t="inlineStr">
-        <is>
-          <t>I played lot's of tournament all over andhra pradesh</t>
-        </is>
-      </c>
+      <c r="J61" s="21" t="inlineStr"/>
       <c r="K61" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0049</t>
+          <t>TKPL-RCPT-2026-0050</t>
         </is>
       </c>
       <c r="N61" s="22" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="O61" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:01 PM</t>
+          <t>30-10-2026 02:03 PM</t>
         </is>
       </c>
       <c r="P61" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:59 PM</t>
+          <t>30-10-2026 01:56 PM</t>
         </is>
       </c>
       <c r="Q61" s="21" t="inlineStr">
@@ -5964,37 +5964,37 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0167</t>
+          <t>TKPL-2026-0166</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>Syed yaseen</t>
+          <t>M SYED NASRUDDIN</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>9542075835</t>
+          <t>9494040272</t>
         </is>
       </c>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>1994-07-24</t>
+          <t>1997-08-08</t>
         </is>
       </c>
       <c r="F62" s="18" t="inlineStr">
         <is>
-          <t>Rajampeta</t>
+          <t>PRODDATUR</t>
         </is>
       </c>
       <c r="G62" s="17" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="J62" s="18" t="inlineStr">
         <is>
-          <t>RMCL TOURNAMENT 5 TIMES WINNER HAS A CAPTAIN AND MANY TOURNAMENT WINNER IN RAJAMPETA</t>
+          <t>I played lot's of tournament all over andhra pradesh</t>
         </is>
       </c>
       <c r="K62" s="17" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="M62" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0051</t>
+          <t>TKPL-RCPT-2026-0049</t>
         </is>
       </c>
       <c r="N62" s="20" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="O62" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:03 PM</t>
+          <t>30-10-2026 02:01 PM</t>
         </is>
       </c>
       <c r="P62" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:02 PM</t>
+          <t>30-10-2026 01:59 PM</t>
         </is>
       </c>
       <c r="Q62" s="18" t="inlineStr">
@@ -6049,37 +6049,37 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0168</t>
+          <t>TKPL-2026-0167</t>
         </is>
       </c>
       <c r="C63" s="21" t="inlineStr">
         <is>
-          <t>Pallapu sai</t>
+          <t>Syed yaseen</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>9014830335</t>
+          <t>9542075835</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>2002-06-14</t>
+          <t>1994-07-24</t>
         </is>
       </c>
       <c r="F63" s="21" t="inlineStr">
         <is>
-          <t>Chinnanandem</t>
+          <t>Rajampeta</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I63" s="13" t="inlineStr">
@@ -6087,7 +6087,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J63" s="21" t="inlineStr"/>
+      <c r="J63" s="21" t="inlineStr">
+        <is>
+          <t>RMCL TOURNAMENT 5 TIMES WINNER HAS A CAPTAIN AND MANY TOURNAMENT WINNER IN RAJAMPETA</t>
+        </is>
+      </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6100,7 +6104,7 @@
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0052</t>
+          <t>TKPL-RCPT-2026-0051</t>
         </is>
       </c>
       <c r="N63" s="22" t="inlineStr">
@@ -6110,12 +6114,12 @@
       </c>
       <c r="O63" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:27 PM</t>
+          <t>30-10-2026 02:03 PM</t>
         </is>
       </c>
       <c r="P63" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:26 PM</t>
+          <t>30-10-2026 02:02 PM</t>
         </is>
       </c>
       <c r="Q63" s="21" t="inlineStr">
@@ -6130,27 +6134,27 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0169</t>
+          <t>TKPL-2026-0168</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>Lavakumar gandikota</t>
+          <t>Pallapu sai</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
-          <t>9603837873</t>
+          <t>9014830335</t>
         </is>
       </c>
       <c r="E64" s="17" t="inlineStr">
         <is>
-          <t>1995-06-08</t>
+          <t>2002-06-14</t>
         </is>
       </c>
       <c r="F64" s="18" t="inlineStr">
         <is>
-          <t>Rayachoty</t>
+          <t>Chinnanandem</t>
         </is>
       </c>
       <c r="G64" s="17" t="inlineStr">
@@ -6181,7 +6185,7 @@
       </c>
       <c r="M64" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0053</t>
+          <t>TKPL-RCPT-2026-0052</t>
         </is>
       </c>
       <c r="N64" s="20" t="inlineStr">
@@ -6191,12 +6195,12 @@
       </c>
       <c r="O64" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:31 PM</t>
+          <t>30-10-2026 02:27 PM</t>
         </is>
       </c>
       <c r="P64" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:30 PM</t>
+          <t>30-10-2026 02:26 PM</t>
         </is>
       </c>
       <c r="Q64" s="18" t="inlineStr">
@@ -6211,27 +6215,27 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0170</t>
+          <t>TKPL-2026-0169</t>
         </is>
       </c>
       <c r="C65" s="21" t="inlineStr">
         <is>
-          <t>Bhaskar Thirumalakonda</t>
+          <t>Lavakumar gandikota</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>7794902066</t>
+          <t>9603837873</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>2000-10-22</t>
+          <t>1995-06-08</t>
         </is>
       </c>
       <c r="F65" s="21" t="inlineStr">
         <is>
-          <t>Galiveedu</t>
+          <t>Rayachoty</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
@@ -6262,7 +6266,7 @@
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0054</t>
+          <t>TKPL-RCPT-2026-0053</t>
         </is>
       </c>
       <c r="N65" s="22" t="inlineStr">
@@ -6272,12 +6276,12 @@
       </c>
       <c r="O65" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:32 PM</t>
+          <t>30-10-2026 02:31 PM</t>
         </is>
       </c>
       <c r="P65" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:31 PM</t>
+          <t>30-10-2026 02:30 PM</t>
         </is>
       </c>
       <c r="Q65" s="21" t="inlineStr">
@@ -6292,27 +6296,27 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0171</t>
+          <t>TKPL-2026-0170</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>THALLU IMRAN</t>
+          <t>Bhaskar Thirumalakonda</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
         <is>
-          <t>9182994104</t>
+          <t>7794902066</t>
         </is>
       </c>
       <c r="E66" s="17" t="inlineStr">
         <is>
-          <t>1997-07-10</t>
+          <t>2000-10-22</t>
         </is>
       </c>
       <c r="F66" s="18" t="inlineStr">
         <is>
-          <t>Rayachoti</t>
+          <t>Galiveedu</t>
         </is>
       </c>
       <c r="G66" s="17" t="inlineStr">
@@ -6330,11 +6334,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J66" s="18" t="inlineStr">
-        <is>
-          <t>RPL and local tournaments</t>
-        </is>
-      </c>
+      <c r="J66" s="18" t="inlineStr"/>
       <c r="K66" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="M66" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0055</t>
+          <t>TKPL-RCPT-2026-0054</t>
         </is>
       </c>
       <c r="N66" s="20" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="O66" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:38 PM</t>
+          <t>30-10-2026 02:32 PM</t>
         </is>
       </c>
       <c r="P66" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:37 PM</t>
+          <t>30-10-2026 02:31 PM</t>
         </is>
       </c>
       <c r="Q66" s="18" t="inlineStr">
@@ -6377,32 +6377,32 @@
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0172</t>
+          <t>TKPL-2026-0171</t>
         </is>
       </c>
       <c r="C67" s="21" t="inlineStr">
         <is>
-          <t>P.munidhra</t>
+          <t>THALLU IMRAN</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>6304924346</t>
+          <t>9182994104</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>2006-05-05</t>
+          <t>1997-07-10</t>
         </is>
       </c>
       <c r="F67" s="21" t="inlineStr">
         <is>
-          <t>Khajipet /pulluru</t>
+          <t>Rayachoti</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -6412,12 +6412,12 @@
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Right-arm Pace</t>
         </is>
       </c>
       <c r="J67" s="21" t="inlineStr">
         <is>
-          <t>Playing local Tournaments</t>
+          <t>RPL and local tournaments</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="M67" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0056</t>
+          <t>TKPL-RCPT-2026-0055</t>
         </is>
       </c>
       <c r="N67" s="22" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="O67" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:39 PM</t>
+          <t>30-10-2026 02:38 PM</t>
         </is>
       </c>
       <c r="P67" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:38 PM</t>
+          <t>30-10-2026 02:37 PM</t>
         </is>
       </c>
       <c r="Q67" s="21" t="inlineStr">
@@ -6462,45 +6462,49 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0173</t>
+          <t>TKPL-2026-0172</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>Yellutla ravikumar naidu</t>
+          <t>P.munidhra</t>
         </is>
       </c>
       <c r="D68" s="17" t="inlineStr">
         <is>
-          <t>9705490252</t>
+          <t>6304924346</t>
         </is>
       </c>
       <c r="E68" s="17" t="inlineStr">
         <is>
-          <t>2005-03-16</t>
+          <t>2006-05-05</t>
         </is>
       </c>
       <c r="F68" s="18" t="inlineStr">
         <is>
-          <t>Chinamandam</t>
+          <t>Khajipet /pulluru</t>
         </is>
       </c>
       <c r="G68" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>Left-arm Spin</t>
-        </is>
-      </c>
-      <c r="J68" s="18" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J68" s="18" t="inlineStr">
+        <is>
+          <t>Playing local Tournaments</t>
+        </is>
+      </c>
       <c r="K68" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6513,7 +6517,7 @@
       </c>
       <c r="M68" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0096</t>
+          <t>TKPL-RCPT-2026-0056</t>
         </is>
       </c>
       <c r="N68" s="20" t="inlineStr">
@@ -6523,12 +6527,12 @@
       </c>
       <c r="O68" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 07:02 PM</t>
+          <t>30-10-2026 02:39 PM</t>
         </is>
       </c>
       <c r="P68" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:48 PM</t>
+          <t>30-10-2026 02:38 PM</t>
         </is>
       </c>
       <c r="Q68" s="18" t="inlineStr">
@@ -6543,27 +6547,27 @@
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0174</t>
+          <t>TKPL-2026-0173</t>
         </is>
       </c>
       <c r="C69" s="21" t="inlineStr">
         <is>
-          <t>Bandla Nagaraj</t>
+          <t>Yellutla ravikumar naidu</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>8639151288</t>
+          <t>9705490252</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>1988-09-24</t>
+          <t>2005-03-16</t>
         </is>
       </c>
       <c r="F69" s="21" t="inlineStr">
         <is>
-          <t>Rajampeta,bhuvagiripalli</t>
+          <t>Chinamandam</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
@@ -6573,19 +6577,15 @@
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J69" s="21" t="inlineStr">
-        <is>
-          <t>TPL and KPL</t>
-        </is>
-      </c>
+          <t>Left-arm Spin</t>
+        </is>
+      </c>
+      <c r="J69" s="21" t="inlineStr"/>
       <c r="K69" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="M69" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0062</t>
+          <t>TKPL-RCPT-2026-0096</t>
         </is>
       </c>
       <c r="N69" s="22" t="inlineStr">
@@ -6608,12 +6608,12 @@
       </c>
       <c r="O69" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:49 PM</t>
+          <t>30-10-2026 07:02 PM</t>
         </is>
       </c>
       <c r="P69" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 02:49 PM</t>
+          <t>30-10-2026 02:48 PM</t>
         </is>
       </c>
       <c r="Q69" s="21" t="inlineStr">
@@ -6628,27 +6628,27 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0175</t>
+          <t>TKPL-2026-0174</t>
         </is>
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>Kammineni pavan Kumar yadav</t>
+          <t>Bandla Nagaraj</t>
         </is>
       </c>
       <c r="D70" s="17" t="inlineStr">
         <is>
-          <t>7995878278</t>
+          <t>8639151288</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
         <is>
-          <t>1998-06-16</t>
+          <t>1988-09-24</t>
         </is>
       </c>
       <c r="F70" s="18" t="inlineStr">
         <is>
-          <t>Rayachoti</t>
+          <t>Rajampeta,bhuvagiripalli</t>
         </is>
       </c>
       <c r="G70" s="17" t="inlineStr">
@@ -6666,7 +6666,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J70" s="18" t="inlineStr"/>
+      <c r="J70" s="18" t="inlineStr">
+        <is>
+          <t>TPL and KPL</t>
+        </is>
+      </c>
       <c r="K70" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6679,7 +6683,7 @@
       </c>
       <c r="M70" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0063</t>
+          <t>TKPL-RCPT-2026-0062</t>
         </is>
       </c>
       <c r="N70" s="20" t="inlineStr">
@@ -6689,12 +6693,12 @@
       </c>
       <c r="O70" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:00 PM</t>
+          <t>30-10-2026 02:49 PM</t>
         </is>
       </c>
       <c r="P70" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 02:52 PM</t>
+          <t>30-10-2026 02:49 PM</t>
         </is>
       </c>
       <c r="Q70" s="18" t="inlineStr">
@@ -6709,27 +6713,27 @@
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0176</t>
+          <t>TKPL-2026-0175</t>
         </is>
       </c>
       <c r="C71" s="21" t="inlineStr">
         <is>
-          <t>Mekala Chandravasulu Reddy</t>
+          <t>Kammineni pavan Kumar yadav</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>9493353988</t>
+          <t>7995878278</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>1992-06-08</t>
+          <t>1998-06-16</t>
         </is>
       </c>
       <c r="F71" s="21" t="inlineStr">
         <is>
-          <t>Yerraguntla</t>
+          <t>Rayachoti</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr">
@@ -6747,11 +6751,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J71" s="21" t="inlineStr">
-        <is>
-          <t>I have played 450 matches on cricheros profile</t>
-        </is>
-      </c>
+      <c r="J71" s="21" t="inlineStr"/>
       <c r="K71" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="M71" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0064</t>
+          <t>TKPL-RCPT-2026-0063</t>
         </is>
       </c>
       <c r="N71" s="22" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="O71" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:11 PM</t>
+          <t>30-10-2026 03:00 PM</t>
         </is>
       </c>
       <c r="P71" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:04 PM</t>
+          <t>30-10-2026 02:52 PM</t>
         </is>
       </c>
       <c r="Q71" s="21" t="inlineStr">
@@ -6794,27 +6794,27 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0177</t>
+          <t>TKPL-2026-0176</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>Yellutla Sree hari naidu</t>
+          <t>Mekala Chandravasulu Reddy</t>
         </is>
       </c>
       <c r="D72" s="17" t="inlineStr">
         <is>
-          <t>6281999214</t>
+          <t>9493353988</t>
         </is>
       </c>
       <c r="E72" s="17" t="inlineStr">
         <is>
-          <t>2009-04-10</t>
+          <t>1992-06-08</t>
         </is>
       </c>
       <c r="F72" s="18" t="inlineStr">
         <is>
-          <t>Chinamandam</t>
+          <t>Yerraguntla</t>
         </is>
       </c>
       <c r="G72" s="17" t="inlineStr">
@@ -6832,7 +6832,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J72" s="18" t="inlineStr"/>
+      <c r="J72" s="18" t="inlineStr">
+        <is>
+          <t>I have played 450 matches on cricheros profile</t>
+        </is>
+      </c>
       <c r="K72" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -6845,7 +6849,7 @@
       </c>
       <c r="M72" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0099</t>
+          <t>TKPL-RCPT-2026-0064</t>
         </is>
       </c>
       <c r="N72" s="20" t="inlineStr">
@@ -6855,12 +6859,12 @@
       </c>
       <c r="O72" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 07:06 PM</t>
+          <t>30-10-2026 03:11 PM</t>
         </is>
       </c>
       <c r="P72" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:06 PM</t>
+          <t>30-10-2026 03:04 PM</t>
         </is>
       </c>
       <c r="Q72" s="18" t="inlineStr">
@@ -6875,32 +6879,32 @@
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0178</t>
+          <t>TKPL-2026-0177</t>
         </is>
       </c>
       <c r="C73" s="21" t="inlineStr">
         <is>
-          <t>Shaik Ghouse mohiddin  ( mohid)</t>
+          <t>Yellutla Sree hari naidu</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>7997116597</t>
+          <t>6281999214</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>1993-12-27</t>
+          <t>2009-04-10</t>
         </is>
       </c>
       <c r="F73" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Chinamandam</t>
         </is>
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H73" s="13" t="inlineStr">
@@ -6926,7 +6930,7 @@
       </c>
       <c r="M73" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0065</t>
+          <t>TKPL-RCPT-2026-0099</t>
         </is>
       </c>
       <c r="N73" s="22" t="inlineStr">
@@ -6936,12 +6940,12 @@
       </c>
       <c r="O73" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:13 PM</t>
+          <t>30-10-2026 07:06 PM</t>
         </is>
       </c>
       <c r="P73" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:12 PM</t>
+          <t>30-10-2026 03:06 PM</t>
         </is>
       </c>
       <c r="Q73" s="21" t="inlineStr">
@@ -6956,22 +6960,22 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0179</t>
+          <t>TKPL-2026-0178</t>
         </is>
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>Shaik saif..@PINTU</t>
+          <t>Shaik Ghouse mohiddin  ( mohid)</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
-          <t>8919628160</t>
+          <t>7997116597</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>2000-09-09</t>
+          <t>1993-12-27</t>
         </is>
       </c>
       <c r="F74" s="18" t="inlineStr">
@@ -6981,7 +6985,7 @@
       </c>
       <c r="G74" s="17" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
@@ -6991,14 +6995,10 @@
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J74" s="18" t="inlineStr">
-        <is>
-          <t>KKR..MPL LEAGUES</t>
-        </is>
-      </c>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J74" s="18" t="inlineStr"/>
       <c r="K74" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="M74" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0066</t>
+          <t>TKPL-RCPT-2026-0065</t>
         </is>
       </c>
       <c r="N74" s="20" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="O74" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:14 PM</t>
+          <t>30-10-2026 03:13 PM</t>
         </is>
       </c>
       <c r="P74" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:13 PM</t>
+          <t>30-10-2026 03:12 PM</t>
         </is>
       </c>
       <c r="Q74" s="18" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0180</t>
+          <t>TKPL-2026-0179</t>
         </is>
       </c>
       <c r="C75" s="21" t="inlineStr">
         <is>
-          <t>SURENDRA KUMAR YADAV</t>
+          <t>Shaik saif..@PINTU</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>9000555438</t>
+          <t>8919628160</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>1989-06-08</t>
+          <t>2000-09-09</t>
         </is>
       </c>
       <c r="F75" s="21" t="inlineStr">
         <is>
-          <t>KADAPA</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H75" s="13" t="inlineStr">
@@ -7076,12 +7076,12 @@
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J75" s="21" t="inlineStr">
         <is>
-          <t>JOURNALIST TOURNAMENTS</t>
+          <t>KKR..MPL LEAGUES</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="M75" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0067</t>
+          <t>TKPL-RCPT-2026-0066</t>
         </is>
       </c>
       <c r="N75" s="22" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="O75" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:18 PM</t>
+          <t>30-10-2026 03:14 PM</t>
         </is>
       </c>
       <c r="P75" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:17 PM</t>
+          <t>30-10-2026 03:13 PM</t>
         </is>
       </c>
       <c r="Q75" s="21" t="inlineStr">
@@ -7126,32 +7126,32 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0181</t>
+          <t>TKPL-2026-0180</t>
         </is>
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>BANDELA PRAVEEN KUMAR</t>
+          <t>SURENDRA KUMAR YADAV</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t>9493832807</t>
+          <t>9000555438</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>1992-02-29</t>
+          <t>1989-06-08</t>
         </is>
       </c>
       <c r="F76" s="18" t="inlineStr">
         <is>
-          <t>Nandimandalam</t>
+          <t>KADAPA</t>
         </is>
       </c>
       <c r="G76" s="17" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="J76" s="18" t="inlineStr">
         <is>
-          <t>I participate in state-wide revenue tournaments as part of the district team representing the Revenue Department.</t>
+          <t>JOURNALIST TOURNAMENTS</t>
         </is>
       </c>
       <c r="K76" s="17" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0068</t>
+          <t>TKPL-RCPT-2026-0067</t>
         </is>
       </c>
       <c r="N76" s="20" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="P76" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:18 PM</t>
+          <t>30-10-2026 03:17 PM</t>
         </is>
       </c>
       <c r="Q76" s="18" t="inlineStr">
@@ -7211,32 +7211,32 @@
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0182</t>
+          <t>TKPL-2026-0181</t>
         </is>
       </c>
       <c r="C77" s="21" t="inlineStr">
         <is>
-          <t>Bharath Kumar reddy</t>
+          <t>BANDELA PRAVEEN KUMAR</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>7981122958</t>
+          <t>9493832807</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>2000-01-01</t>
+          <t>1992-02-29</t>
         </is>
       </c>
       <c r="F77" s="21" t="inlineStr">
         <is>
-          <t>Chinnamandem</t>
+          <t>Nandimandalam</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Right-arm Pace</t>
         </is>
       </c>
       <c r="J77" s="21" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>I participate in state-wide revenue tournaments as part of the district team representing the Revenue Department.</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="M77" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0069</t>
+          <t>TKPL-RCPT-2026-0068</t>
         </is>
       </c>
       <c r="N77" s="22" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O77" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:22 PM</t>
+          <t>30-10-2026 03:18 PM</t>
         </is>
       </c>
       <c r="P77" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:21 PM</t>
+          <t>30-10-2026 03:18 PM</t>
         </is>
       </c>
       <c r="Q77" s="21" t="inlineStr">
@@ -7296,32 +7296,32 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0183</t>
+          <t>TKPL-2026-0182</t>
         </is>
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>Gantenapalli mahesh</t>
+          <t>Bharath Kumar reddy</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>6281951630</t>
+          <t>7981122958</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>1996-06-05</t>
+          <t>2000-01-01</t>
         </is>
       </c>
       <c r="F78" s="18" t="inlineStr">
         <is>
-          <t>kadapa</t>
+          <t>Chinnamandem</t>
         </is>
       </c>
       <c r="G78" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
@@ -7331,10 +7331,14 @@
       </c>
       <c r="I78" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J78" s="18" t="inlineStr"/>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J78" s="18" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7347,7 +7351,7 @@
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0070</t>
+          <t>TKPL-RCPT-2026-0069</t>
         </is>
       </c>
       <c r="N78" s="20" t="inlineStr">
@@ -7357,12 +7361,12 @@
       </c>
       <c r="O78" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:27 PM</t>
+          <t>30-10-2026 03:22 PM</t>
         </is>
       </c>
       <c r="P78" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:26 PM</t>
+          <t>30-10-2026 03:21 PM</t>
         </is>
       </c>
       <c r="Q78" s="18" t="inlineStr">
@@ -7377,27 +7381,27 @@
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0184</t>
+          <t>TKPL-2026-0183</t>
         </is>
       </c>
       <c r="C79" s="21" t="inlineStr">
         <is>
-          <t>CHARU NAGARAJU</t>
+          <t>Gantenapalli mahesh</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>9160446640</t>
+          <t>6281951630</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>1992-04-03</t>
+          <t>1996-06-05</t>
         </is>
       </c>
       <c r="F79" s="21" t="inlineStr">
         <is>
-          <t>KADAPA</t>
+          <t>kadapa</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
@@ -7415,11 +7419,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J79" s="21" t="inlineStr">
-        <is>
-          <t>LOCAL TOURNAMNETS</t>
-        </is>
-      </c>
+      <c r="J79" s="21" t="inlineStr"/>
       <c r="K79" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="M79" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0071</t>
+          <t>TKPL-RCPT-2026-0070</t>
         </is>
       </c>
       <c r="N79" s="22" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="P79" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:27 PM</t>
+          <t>30-10-2026 03:26 PM</t>
         </is>
       </c>
       <c r="Q79" s="21" t="inlineStr">
@@ -7462,32 +7462,32 @@
       </c>
       <c r="B80" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0185</t>
+          <t>TKPL-2026-0184</t>
         </is>
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>U.OBULESU</t>
+          <t>CHARU NAGARAJU</t>
         </is>
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
-          <t>9398778303</t>
+          <t>9160446640</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>1997-05-16</t>
+          <t>1992-04-03</t>
         </is>
       </c>
       <c r="F80" s="18" t="inlineStr">
         <is>
-          <t>Lakkireddipalli</t>
+          <t>KADAPA</t>
         </is>
       </c>
       <c r="G80" s="17" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H80" s="17" t="inlineStr">
@@ -7500,7 +7500,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J80" s="18" t="inlineStr"/>
+      <c r="J80" s="18" t="inlineStr">
+        <is>
+          <t>LOCAL TOURNAMNETS</t>
+        </is>
+      </c>
       <c r="K80" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7513,7 +7517,7 @@
       </c>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0077</t>
+          <t>TKPL-RCPT-2026-0071</t>
         </is>
       </c>
       <c r="N80" s="20" t="inlineStr">
@@ -7523,17 +7527,17 @@
       </c>
       <c r="O80" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:50 PM</t>
+          <t>30-10-2026 03:27 PM</t>
         </is>
       </c>
       <c r="P80" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:29 PM</t>
+          <t>30-10-2026 03:27 PM</t>
         </is>
       </c>
       <c r="Q80" s="18" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7543,32 +7547,32 @@
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0186</t>
+          <t>TKPL-2026-0185</t>
         </is>
       </c>
       <c r="C81" s="21" t="inlineStr">
         <is>
-          <t>Dinesh Don Don</t>
+          <t>U.OBULESU</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>7386474099</t>
+          <t>9398778303</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>2000-11-25</t>
+          <t>1997-05-16</t>
         </is>
       </c>
       <c r="F81" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Lakkireddipalli</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
@@ -7581,11 +7585,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J81" s="21" t="inlineStr">
-        <is>
-          <t>Played Big Tournaments</t>
-        </is>
-      </c>
+      <c r="J81" s="21" t="inlineStr"/>
       <c r="K81" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="M81" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0078</t>
+          <t>TKPL-RCPT-2026-0077</t>
         </is>
       </c>
       <c r="N81" s="22" t="inlineStr">
@@ -7628,22 +7628,22 @@
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0187</t>
+          <t>TKPL-2026-0186</t>
         </is>
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>Danger Man Ravi</t>
+          <t>Dinesh Don Don</t>
         </is>
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
-          <t>9052561634</t>
+          <t>7386474099</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>2000-01-13</t>
+          <t>2000-11-25</t>
         </is>
       </c>
       <c r="F82" s="18" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="J82" s="18" t="inlineStr">
         <is>
-          <t>Tournament experience 15 years</t>
+          <t>Played Big Tournaments</t>
         </is>
       </c>
       <c r="K82" s="17" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0074</t>
+          <t>TKPL-RCPT-2026-0078</t>
         </is>
       </c>
       <c r="N82" s="20" t="inlineStr">
@@ -7693,17 +7693,17 @@
       </c>
       <c r="O82" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:32 PM</t>
+          <t>30-10-2026 03:50 PM</t>
         </is>
       </c>
       <c r="P82" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:31 PM</t>
+          <t>30-10-2026 03:29 PM</t>
         </is>
       </c>
       <c r="Q82" s="18" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7713,22 +7713,22 @@
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0188</t>
+          <t>TKPL-2026-0187</t>
         </is>
       </c>
       <c r="C83" s="21" t="inlineStr">
         <is>
-          <t>Crazy boy mp</t>
+          <t>Danger Man Ravi</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>9000814023</t>
+          <t>9052561634</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>1995-08-22</t>
+          <t>2000-01-13</t>
         </is>
       </c>
       <c r="F83" s="21" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
@@ -7751,7 +7751,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J83" s="21" t="inlineStr"/>
+      <c r="J83" s="21" t="inlineStr">
+        <is>
+          <t>Tournament experience 15 years</t>
+        </is>
+      </c>
       <c r="K83" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7764,7 +7768,7 @@
       </c>
       <c r="M83" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0076</t>
+          <t>TKPL-RCPT-2026-0074</t>
         </is>
       </c>
       <c r="N83" s="22" t="inlineStr">
@@ -7774,7 +7778,7 @@
       </c>
       <c r="O83" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:50 PM</t>
+          <t>30-10-2026 03:32 PM</t>
         </is>
       </c>
       <c r="P83" s="13" t="inlineStr">
@@ -7784,7 +7788,7 @@
       </c>
       <c r="Q83" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7794,22 +7798,22 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0189</t>
+          <t>TKPL-2026-0188</t>
         </is>
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>RAJA</t>
+          <t>Crazy boy mp</t>
         </is>
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
-          <t>9398317906</t>
+          <t>9000814023</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>1999-09-15</t>
+          <t>1995-08-22</t>
         </is>
       </c>
       <c r="F84" s="18" t="inlineStr">
@@ -7819,7 +7823,7 @@
       </c>
       <c r="G84" s="17" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H84" s="17" t="inlineStr">
@@ -7845,7 +7849,7 @@
       </c>
       <c r="M84" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0075</t>
+          <t>TKPL-RCPT-2026-0076</t>
         </is>
       </c>
       <c r="N84" s="20" t="inlineStr">
@@ -7855,17 +7859,17 @@
       </c>
       <c r="O84" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:47 PM</t>
+          <t>30-10-2026 03:50 PM</t>
         </is>
       </c>
       <c r="P84" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:46 PM</t>
+          <t>30-10-2026 03:31 PM</t>
         </is>
       </c>
       <c r="Q84" s="18" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -7875,32 +7879,32 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0190</t>
+          <t>TKPL-2026-0189</t>
         </is>
       </c>
       <c r="C85" s="21" t="inlineStr">
         <is>
-          <t>Nachu.vinodkumar</t>
+          <t>RAJA</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>8499806339</t>
+          <t>9398317906</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>1995-07-10</t>
+          <t>1999-09-15</t>
         </is>
       </c>
       <c r="F85" s="21" t="inlineStr">
         <is>
-          <t>Annamayya district.galiveedu.</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -7910,14 +7914,10 @@
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Spin</t>
-        </is>
-      </c>
-      <c r="J85" s="21" t="inlineStr">
-        <is>
-          <t>ATPBL Kadapa king team. south zone Mumbai club. International matches Nepal premier leag</t>
-        </is>
-      </c>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J85" s="21" t="inlineStr"/>
       <c r="K85" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="M85" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0079</t>
+          <t>TKPL-RCPT-2026-0075</t>
         </is>
       </c>
       <c r="N85" s="22" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="O85" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:54 PM</t>
+          <t>30-10-2026 03:47 PM</t>
         </is>
       </c>
       <c r="P85" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 03:54 PM</t>
+          <t>30-10-2026 03:46 PM</t>
         </is>
       </c>
       <c r="Q85" s="21" t="inlineStr">
@@ -7960,27 +7960,27 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0191</t>
+          <t>TKPL-2026-0190</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>Giri</t>
+          <t>Nachu.vinodkumar</t>
         </is>
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t>7989571634</t>
+          <t>8499806339</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>1997-06-02</t>
+          <t>1995-07-10</t>
         </is>
       </c>
       <c r="F86" s="18" t="inlineStr">
         <is>
-          <t>Vempalli</t>
+          <t>Annamayya district.galiveedu.</t>
         </is>
       </c>
       <c r="G86" s="17" t="inlineStr">
@@ -7990,17 +7990,17 @@
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
-          <t>Left-arm Pace</t>
+          <t>Right-arm Spin</t>
         </is>
       </c>
       <c r="J86" s="18" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>ATPBL Kadapa king team. south zone Mumbai club. International matches Nepal premier leag</t>
         </is>
       </c>
       <c r="K86" s="17" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="M86" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0088</t>
+          <t>TKPL-RCPT-2026-0079</t>
         </is>
       </c>
       <c r="N86" s="20" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="O86" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:30 PM</t>
+          <t>30-10-2026 03:54 PM</t>
         </is>
       </c>
       <c r="P86" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 03:56 PM</t>
+          <t>30-10-2026 03:54 PM</t>
         </is>
       </c>
       <c r="Q86" s="18" t="inlineStr">
@@ -8045,47 +8045,47 @@
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0192</t>
+          <t>TKPL-2026-0191</t>
         </is>
       </c>
       <c r="C87" s="21" t="inlineStr">
         <is>
-          <t>D  Nagarjuna Reddy</t>
+          <t>Giri</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>7396440670</t>
+          <t>7989571634</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>2008-06-16</t>
+          <t>1997-06-02</t>
         </is>
       </c>
       <c r="F87" s="21" t="inlineStr">
         <is>
-          <t>Chakrayapeta town</t>
+          <t>Vempalli</t>
         </is>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>Left-arm Pace</t>
         </is>
       </c>
       <c r="J87" s="21" t="inlineStr">
         <is>
-          <t>Chakrayapeta  youth tournament</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="K87" s="13" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="M87" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0080</t>
+          <t>TKPL-RCPT-2026-0088</t>
         </is>
       </c>
       <c r="N87" s="22" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O87" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:06 PM</t>
+          <t>30-10-2026 04:30 PM</t>
         </is>
       </c>
       <c r="P87" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:04 PM</t>
+          <t>30-10-2026 03:56 PM</t>
         </is>
       </c>
       <c r="Q87" s="21" t="inlineStr">
@@ -8130,37 +8130,37 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0193</t>
+          <t>TKPL-2026-0192</t>
         </is>
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>MOTAPOTHULA VAMSI (PANT)</t>
+          <t>D  Nagarjuna Reddy</t>
         </is>
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t>8309585550</t>
+          <t>7396440670</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>2002-04-06</t>
+          <t>2008-06-16</t>
         </is>
       </c>
       <c r="F88" s="18" t="inlineStr">
         <is>
-          <t>SAVISETTIPALLI</t>
+          <t>Chakrayapeta town</t>
         </is>
       </c>
       <c r="G88" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I88" s="17" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="J88" s="18" t="inlineStr">
         <is>
-          <t>6years experience many trophies win</t>
+          <t>Chakrayapeta  youth tournament</t>
         </is>
       </c>
       <c r="K88" s="17" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="M88" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0081</t>
+          <t>TKPL-RCPT-2026-0080</t>
         </is>
       </c>
       <c r="N88" s="20" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="P88" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:05 PM</t>
+          <t>30-10-2026 04:04 PM</t>
         </is>
       </c>
       <c r="Q88" s="18" t="inlineStr">
@@ -8215,27 +8215,27 @@
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0194</t>
+          <t>TKPL-2026-0193</t>
         </is>
       </c>
       <c r="C89" s="21" t="inlineStr">
         <is>
-          <t>ARSHAD PATAN</t>
+          <t>MOTAPOTHULA VAMSI (PANT)</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
-          <t>8309771127</t>
+          <t>8309585550</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>2007-07-09</t>
+          <t>2002-04-06</t>
         </is>
       </c>
       <c r="F89" s="21" t="inlineStr">
         <is>
-          <t>Kadapa: ayesha shool near pedda darga</t>
+          <t>SAVISETTIPALLI</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr">
@@ -8255,8 +8255,7 @@
       </c>
       <c r="J89" s="21" t="inlineStr">
         <is>
-          <t>ATBPL-1
-ANDHRA TENNIS BALL PERMIER LEAUGE</t>
+          <t>6years experience many trophies win</t>
         </is>
       </c>
       <c r="K89" s="13" t="inlineStr">
@@ -8271,7 +8270,7 @@
       </c>
       <c r="M89" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0082</t>
+          <t>TKPL-RCPT-2026-0081</t>
         </is>
       </c>
       <c r="N89" s="22" t="inlineStr">
@@ -8281,12 +8280,12 @@
       </c>
       <c r="O89" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:11 PM</t>
+          <t>30-10-2026 04:06 PM</t>
         </is>
       </c>
       <c r="P89" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:09 PM</t>
+          <t>30-10-2026 04:05 PM</t>
         </is>
       </c>
       <c r="Q89" s="21" t="inlineStr">
@@ -8301,27 +8300,27 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0195</t>
+          <t>TKPL-2026-0194</t>
         </is>
       </c>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>M SUBBA REDDY</t>
+          <t>ARSHAD PATAN</t>
         </is>
       </c>
       <c r="D90" s="17" t="inlineStr">
         <is>
-          <t>9052632763</t>
+          <t>8309771127</t>
         </is>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>1987-06-06</t>
+          <t>2007-07-09</t>
         </is>
       </c>
       <c r="F90" s="18" t="inlineStr">
         <is>
-          <t>Khajipet</t>
+          <t>Kadapa: ayesha shool near pedda darga</t>
         </is>
       </c>
       <c r="G90" s="17" t="inlineStr">
@@ -8341,7 +8340,8 @@
       </c>
       <c r="J90" s="18" t="inlineStr">
         <is>
-          <t>Nill</t>
+          <t>ATBPL-1
+ANDHRA TENNIS BALL PERMIER LEAUGE</t>
         </is>
       </c>
       <c r="K90" s="17" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="M90" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0083</t>
+          <t>TKPL-RCPT-2026-0082</t>
         </is>
       </c>
       <c r="N90" s="20" t="inlineStr">
@@ -8366,12 +8366,12 @@
       </c>
       <c r="O90" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:15 PM</t>
+          <t>30-10-2026 04:11 PM</t>
         </is>
       </c>
       <c r="P90" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:14 PM</t>
+          <t>30-10-2026 04:09 PM</t>
         </is>
       </c>
       <c r="Q90" s="18" t="inlineStr">
@@ -8386,27 +8386,27 @@
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0196</t>
+          <t>TKPL-2026-0195</t>
         </is>
       </c>
       <c r="C91" s="21" t="inlineStr">
         <is>
-          <t>Eswar Beema</t>
+          <t>M SUBBA REDDY</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>7337007666</t>
+          <t>9052632763</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>1993-04-04</t>
+          <t>1987-06-06</t>
         </is>
       </c>
       <c r="F91" s="21" t="inlineStr">
         <is>
-          <t>Kamalapuram</t>
+          <t>Khajipet</t>
         </is>
       </c>
       <c r="G91" s="13" t="inlineStr">
@@ -8424,7 +8424,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J91" s="21" t="inlineStr"/>
+      <c r="J91" s="21" t="inlineStr">
+        <is>
+          <t>Nill</t>
+        </is>
+      </c>
       <c r="K91" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -8437,7 +8441,7 @@
       </c>
       <c r="M91" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0084</t>
+          <t>TKPL-RCPT-2026-0083</t>
         </is>
       </c>
       <c r="N91" s="22" t="inlineStr">
@@ -8447,12 +8451,12 @@
       </c>
       <c r="O91" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:17 PM</t>
+          <t>30-10-2026 04:15 PM</t>
         </is>
       </c>
       <c r="P91" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:16 PM</t>
+          <t>30-10-2026 04:14 PM</t>
         </is>
       </c>
       <c r="Q91" s="21" t="inlineStr">
@@ -8467,27 +8471,27 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0197</t>
+          <t>TKPL-2026-0196</t>
         </is>
       </c>
       <c r="C92" s="18" t="inlineStr">
         <is>
-          <t>Sameer</t>
+          <t>Eswar Beema</t>
         </is>
       </c>
       <c r="D92" s="17" t="inlineStr">
         <is>
-          <t>7013094749</t>
+          <t>7337007666</t>
         </is>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>2002-10-08</t>
+          <t>1993-04-04</t>
         </is>
       </c>
       <c r="F92" s="18" t="inlineStr">
         <is>
-          <t>Yerraguntla</t>
+          <t>Kamalapuram</t>
         </is>
       </c>
       <c r="G92" s="17" t="inlineStr">
@@ -8497,19 +8501,15 @@
       </c>
       <c r="H92" s="17" t="inlineStr">
         <is>
-          <t>Left Hand</t>
+          <t>Right Hand</t>
         </is>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
-          <t>Left-arm Spin</t>
-        </is>
-      </c>
-      <c r="J92" s="18" t="inlineStr">
-        <is>
-          <t>I played lots of tournaments I’m a player of the 7s x1 team</t>
-        </is>
-      </c>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J92" s="18" t="inlineStr"/>
       <c r="K92" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="M92" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0087</t>
+          <t>TKPL-RCPT-2026-0084</t>
         </is>
       </c>
       <c r="N92" s="20" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="O92" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:29 PM</t>
+          <t>30-10-2026 04:17 PM</t>
         </is>
       </c>
       <c r="P92" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:26 PM</t>
+          <t>30-10-2026 04:16 PM</t>
         </is>
       </c>
       <c r="Q92" s="18" t="inlineStr">
@@ -8552,27 +8552,27 @@
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0198</t>
+          <t>TKPL-2026-0197</t>
         </is>
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>Barigela Suvarthaiah</t>
+          <t>Sameer</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>8125231723</t>
+          <t>7013094749</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>1989-06-25</t>
+          <t>2002-10-08</t>
         </is>
       </c>
       <c r="F93" s="21" t="inlineStr">
         <is>
-          <t>RTPP</t>
+          <t>Yerraguntla</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
@@ -8582,15 +8582,19 @@
       </c>
       <c r="H93" s="13" t="inlineStr">
         <is>
-          <t>Right Hand</t>
+          <t>Left Hand</t>
         </is>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J93" s="21" t="inlineStr"/>
+          <t>Left-arm Spin</t>
+        </is>
+      </c>
+      <c r="J93" s="21" t="inlineStr">
+        <is>
+          <t>I played lots of tournaments I’m a player of the 7s x1 team</t>
+        </is>
+      </c>
       <c r="K93" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -8603,7 +8607,7 @@
       </c>
       <c r="M93" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0086</t>
+          <t>TKPL-RCPT-2026-0087</t>
         </is>
       </c>
       <c r="N93" s="22" t="inlineStr">
@@ -8613,12 +8617,12 @@
       </c>
       <c r="O93" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:28 PM</t>
+          <t>30-10-2026 04:29 PM</t>
         </is>
       </c>
       <c r="P93" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:27 PM</t>
+          <t>30-10-2026 04:26 PM</t>
         </is>
       </c>
       <c r="Q93" s="21" t="inlineStr">
@@ -8633,27 +8637,27 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0199</t>
+          <t>TKPL-2026-0198</t>
         </is>
       </c>
       <c r="C94" s="18" t="inlineStr">
         <is>
-          <t>krishnareddy sirigireddy</t>
+          <t>Barigela Suvarthaiah</t>
         </is>
       </c>
       <c r="D94" s="17" t="inlineStr">
         <is>
-          <t>9177757989</t>
+          <t>8125231723</t>
         </is>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>1985-05-30</t>
+          <t>1989-06-25</t>
         </is>
       </c>
       <c r="F94" s="18" t="inlineStr">
         <is>
-          <t>Pulivendula</t>
+          <t>RTPP</t>
         </is>
       </c>
       <c r="G94" s="17" t="inlineStr">
@@ -8671,11 +8675,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J94" s="18" t="inlineStr">
-        <is>
-          <t>Rayalasima cricket  tournament winner</t>
-        </is>
-      </c>
+      <c r="J94" s="18" t="inlineStr"/>
       <c r="K94" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="M94" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0089</t>
+          <t>TKPL-RCPT-2026-0086</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
@@ -8698,12 +8698,12 @@
       </c>
       <c r="O94" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:40 PM</t>
+          <t>30-10-2026 04:28 PM</t>
         </is>
       </c>
       <c r="P94" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 04:29 PM</t>
+          <t>30-10-2026 04:27 PM</t>
         </is>
       </c>
       <c r="Q94" s="18" t="inlineStr">
@@ -8718,27 +8718,27 @@
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0200</t>
+          <t>TKPL-2026-0199</t>
         </is>
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>pradeep reddy</t>
+          <t>krishnareddy sirigireddy</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>9573562254</t>
+          <t>9177757989</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>1995-10-30</t>
+          <t>1985-05-30</t>
         </is>
       </c>
       <c r="F95" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Pulivendula</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
@@ -8756,7 +8756,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J95" s="21" t="inlineStr"/>
+      <c r="J95" s="21" t="inlineStr">
+        <is>
+          <t>Rayalasima cricket  tournament winner</t>
+        </is>
+      </c>
       <c r="K95" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -8769,7 +8773,7 @@
       </c>
       <c r="M95" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0090</t>
+          <t>TKPL-RCPT-2026-0089</t>
         </is>
       </c>
       <c r="N95" s="22" t="inlineStr">
@@ -8779,12 +8783,12 @@
       </c>
       <c r="O95" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:55 PM</t>
+          <t>30-10-2026 04:40 PM</t>
         </is>
       </c>
       <c r="P95" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 04:47 PM</t>
+          <t>30-10-2026 04:29 PM</t>
         </is>
       </c>
       <c r="Q95" s="21" t="inlineStr">
@@ -8799,27 +8803,27 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0201</t>
+          <t>TKPL-2026-0200</t>
         </is>
       </c>
       <c r="C96" s="18" t="inlineStr">
         <is>
-          <t>B. naveen</t>
+          <t>pradeep reddy</t>
         </is>
       </c>
       <c r="D96" s="17" t="inlineStr">
         <is>
-          <t>9392008312</t>
+          <t>9573562254</t>
         </is>
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>2006-05-05</t>
+          <t>1995-10-30</t>
         </is>
       </c>
       <c r="F96" s="18" t="inlineStr">
         <is>
-          <t>Veeraballi</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G96" s="17" t="inlineStr">
@@ -8837,11 +8841,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J96" s="18" t="inlineStr">
-        <is>
-          <t>Playing tournaments</t>
-        </is>
-      </c>
+      <c r="J96" s="18" t="inlineStr"/>
       <c r="K96" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="M96" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0091</t>
+          <t>TKPL-RCPT-2026-0090</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="O96" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 05:14 PM</t>
+          <t>30-10-2026 04:55 PM</t>
         </is>
       </c>
       <c r="P96" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 05:13 PM</t>
+          <t>30-10-2026 04:47 PM</t>
         </is>
       </c>
       <c r="Q96" s="18" t="inlineStr">
@@ -8884,32 +8884,32 @@
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0203</t>
+          <t>TKPL-2026-0201</t>
         </is>
       </c>
       <c r="C97" s="21" t="inlineStr">
         <is>
-          <t>RAJASEKHAR SIDDAM</t>
+          <t>B. naveen</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>7780259251</t>
+          <t>9392008312</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>1988-05-01</t>
+          <t>2006-05-05</t>
         </is>
       </c>
       <c r="F97" s="21" t="inlineStr">
         <is>
-          <t>Marripalli,veerapunayunipalli,kadapa.</t>
+          <t>Veeraballi</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H97" s="13" t="inlineStr">
@@ -8922,7 +8922,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J97" s="21" t="inlineStr"/>
+      <c r="J97" s="21" t="inlineStr">
+        <is>
+          <t>Playing tournaments</t>
+        </is>
+      </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -8935,7 +8939,7 @@
       </c>
       <c r="M97" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0107</t>
+          <t>TKPL-RCPT-2026-0091</t>
         </is>
       </c>
       <c r="N97" s="22" t="inlineStr">
@@ -8945,17 +8949,17 @@
       </c>
       <c r="O97" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 08:29 PM</t>
+          <t>30-10-2026 05:14 PM</t>
         </is>
       </c>
       <c r="P97" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 05:23 PM</t>
+          <t>30-10-2026 05:13 PM</t>
         </is>
       </c>
       <c r="Q97" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -8965,27 +8969,27 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0204</t>
+          <t>TKPL-2026-0202</t>
         </is>
       </c>
       <c r="C98" s="18" t="inlineStr">
         <is>
-          <t>Kanakanti Mohanreddy</t>
+          <t>R shahabuddin</t>
         </is>
       </c>
       <c r="D98" s="17" t="inlineStr">
         <is>
-          <t>9390439310</t>
+          <t>8639460531</t>
         </is>
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>2000-10-04</t>
+          <t>2009-08-20</t>
         </is>
       </c>
       <c r="F98" s="18" t="inlineStr">
         <is>
-          <t>Rayachoti</t>
+          <t>Khajipeta</t>
         </is>
       </c>
       <c r="G98" s="17" t="inlineStr">
@@ -9016,7 +9020,7 @@
       </c>
       <c r="M98" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0092</t>
+          <t>TKPL-RCPT-2026-0112</t>
         </is>
       </c>
       <c r="N98" s="20" t="inlineStr">
@@ -9026,12 +9030,12 @@
       </c>
       <c r="O98" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 05:32 PM</t>
+          <t>30-10-2026 10:17 PM</t>
         </is>
       </c>
       <c r="P98" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 05:31 PM</t>
+          <t>30-10-2026 05:16 PM</t>
         </is>
       </c>
       <c r="Q98" s="18" t="inlineStr">
@@ -9046,32 +9050,32 @@
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0205</t>
+          <t>TKPL-2026-0203</t>
         </is>
       </c>
       <c r="C99" s="21" t="inlineStr">
         <is>
-          <t>Shameerbasha</t>
+          <t>RAJASEKHAR SIDDAM</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr">
         <is>
-          <t>8121724624</t>
+          <t>7780259251</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>1993-06-26</t>
+          <t>1988-05-01</t>
         </is>
       </c>
       <c r="F99" s="21" t="inlineStr">
         <is>
-          <t>Proddatur</t>
+          <t>Marripalli,veerapunayunipalli,kadapa.</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H99" s="13" t="inlineStr">
@@ -9081,7 +9085,7 @@
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Spin</t>
+          <t>Right-arm Pace</t>
         </is>
       </c>
       <c r="J99" s="21" t="inlineStr"/>
@@ -9097,7 +9101,7 @@
       </c>
       <c r="M99" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0093</t>
+          <t>TKPL-RCPT-2026-0107</t>
         </is>
       </c>
       <c r="N99" s="22" t="inlineStr">
@@ -9107,17 +9111,17 @@
       </c>
       <c r="O99" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 06:01 PM</t>
+          <t>30-10-2026 08:29 PM</t>
         </is>
       </c>
       <c r="P99" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 05:59 PM</t>
+          <t>30-10-2026 05:23 PM</t>
         </is>
       </c>
       <c r="Q99" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -9127,32 +9131,32 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0206</t>
+          <t>TKPL-2026-0204</t>
         </is>
       </c>
       <c r="C100" s="18" t="inlineStr">
         <is>
-          <t>Abbas Shaik</t>
+          <t>Kanakanti Mohanreddy</t>
         </is>
       </c>
       <c r="D100" s="17" t="inlineStr">
         <is>
-          <t>7993419095</t>
+          <t>9390439310</t>
         </is>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>1999-08-25</t>
+          <t>2000-10-04</t>
         </is>
       </c>
       <c r="F100" s="18" t="inlineStr">
         <is>
-          <t>Yerraguntla</t>
+          <t>Rayachoti</t>
         </is>
       </c>
       <c r="G100" s="17" t="inlineStr">
         <is>
-          <t>Batter</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H100" s="17" t="inlineStr">
@@ -9178,7 +9182,7 @@
       </c>
       <c r="M100" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0094</t>
+          <t>TKPL-RCPT-2026-0092</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
@@ -9188,12 +9192,12 @@
       </c>
       <c r="O100" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 06:06 PM</t>
+          <t>30-10-2026 05:32 PM</t>
         </is>
       </c>
       <c r="P100" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 06:05 PM</t>
+          <t>30-10-2026 05:31 PM</t>
         </is>
       </c>
       <c r="Q100" s="18" t="inlineStr">
@@ -9208,32 +9212,32 @@
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0207</t>
+          <t>TKPL-2026-0205</t>
         </is>
       </c>
       <c r="C101" s="21" t="inlineStr">
         <is>
-          <t>Potu Chandra</t>
+          <t>Shameerbasha</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
         <is>
-          <t>8885333362</t>
+          <t>8121724624</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>1991-05-30</t>
+          <t>1993-06-26</t>
         </is>
       </c>
       <c r="F101" s="21" t="inlineStr">
         <is>
-          <t>Y S R Kadapa</t>
+          <t>Proddatur</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H101" s="13" t="inlineStr">
@@ -9243,7 +9247,7 @@
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
+          <t>Right-arm Spin</t>
         </is>
       </c>
       <c r="J101" s="21" t="inlineStr"/>
@@ -9259,7 +9263,7 @@
       </c>
       <c r="M101" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0108</t>
+          <t>TKPL-RCPT-2026-0093</t>
         </is>
       </c>
       <c r="N101" s="22" t="inlineStr">
@@ -9269,17 +9273,17 @@
       </c>
       <c r="O101" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 08:29 PM</t>
+          <t>30-10-2026 06:01 PM</t>
         </is>
       </c>
       <c r="P101" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 06:20 PM</t>
+          <t>30-10-2026 05:59 PM</t>
         </is>
       </c>
       <c r="Q101" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed upon verified Razorpay payment.</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9293,32 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0208</t>
+          <t>TKPL-2026-0206</t>
         </is>
       </c>
       <c r="C102" s="18" t="inlineStr">
         <is>
-          <t>S Malli Naidu</t>
+          <t>Abbas Shaik</t>
         </is>
       </c>
       <c r="D102" s="17" t="inlineStr">
         <is>
-          <t>6302935195</t>
+          <t>7993419095</t>
         </is>
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>2005-06-15</t>
+          <t>1999-08-25</t>
         </is>
       </c>
       <c r="F102" s="18" t="inlineStr">
         <is>
-          <t>Rayachoty</t>
+          <t>Yerraguntla</t>
         </is>
       </c>
       <c r="G102" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Batter</t>
         </is>
       </c>
       <c r="H102" s="17" t="inlineStr">
@@ -9327,11 +9331,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J102" s="18" t="inlineStr">
-        <is>
-          <t>Local tournaments and other tournaments</t>
-        </is>
-      </c>
+      <c r="J102" s="18" t="inlineStr"/>
       <c r="K102" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="M102" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0095</t>
+          <t>TKPL-RCPT-2026-0094</t>
         </is>
       </c>
       <c r="N102" s="20" t="inlineStr">
@@ -9354,12 +9354,12 @@
       </c>
       <c r="O102" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 06:51 PM</t>
+          <t>30-10-2026 06:06 PM</t>
         </is>
       </c>
       <c r="P102" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 06:48 PM</t>
+          <t>30-10-2026 06:05 PM</t>
         </is>
       </c>
       <c r="Q102" s="18" t="inlineStr">
@@ -9374,32 +9374,32 @@
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0209</t>
+          <t>TKPL-2026-0207</t>
         </is>
       </c>
       <c r="C103" s="21" t="inlineStr">
         <is>
-          <t>PUSHPAGIRI CHANDRAKANTH</t>
+          <t>Potu Chandra</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>9347305959</t>
+          <t>8885333362</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>1993-06-12</t>
+          <t>1991-05-30</t>
         </is>
       </c>
       <c r="F103" s="21" t="inlineStr">
         <is>
-          <t>VEERAPUNAYUNIPALLI, kadapa</t>
+          <t>Y S R Kadapa</t>
         </is>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H103" s="13" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="M103" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0097</t>
+          <t>TKPL-RCPT-2026-0108</t>
         </is>
       </c>
       <c r="N103" s="22" t="inlineStr">
@@ -9435,17 +9435,17 @@
       </c>
       <c r="O103" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 07:03 PM</t>
+          <t>30-10-2026 08:29 PM</t>
         </is>
       </c>
       <c r="P103" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 07:00 PM</t>
+          <t>30-10-2026 06:20 PM</t>
         </is>
       </c>
       <c r="Q103" s="21" t="inlineStr">
         <is>
-          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -9455,32 +9455,32 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0210</t>
+          <t>TKPL-2026-0208</t>
         </is>
       </c>
       <c r="C104" s="18" t="inlineStr">
         <is>
-          <t>Yorker Yunus</t>
+          <t>S Malli Naidu</t>
         </is>
       </c>
       <c r="D104" s="17" t="inlineStr">
         <is>
-          <t>7095231174</t>
+          <t>6302935195</t>
         </is>
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>2005-03-28</t>
+          <t>2005-06-15</t>
         </is>
       </c>
       <c r="F104" s="18" t="inlineStr">
         <is>
-          <t>Nandimandalam , kadapa district</t>
+          <t>Rayachoty</t>
         </is>
       </c>
       <c r="G104" s="17" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H104" s="17" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="J104" s="18" t="inlineStr">
         <is>
-          <t>Pulivendula tournaments and produtur tournament</t>
+          <t>Local tournaments and other tournaments</t>
         </is>
       </c>
       <c r="K104" s="17" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="M104" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0098</t>
+          <t>TKPL-RCPT-2026-0095</t>
         </is>
       </c>
       <c r="N104" s="20" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="O104" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 07:04 PM</t>
+          <t>30-10-2026 06:51 PM</t>
         </is>
       </c>
       <c r="P104" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 07:03 PM</t>
+          <t>30-10-2026 06:48 PM</t>
         </is>
       </c>
       <c r="Q104" s="18" t="inlineStr">
@@ -9540,32 +9540,32 @@
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0211</t>
+          <t>TKPL-2026-0209</t>
         </is>
       </c>
       <c r="C105" s="21" t="inlineStr">
         <is>
-          <t>Jalla mahesh Kumar</t>
+          <t>PUSHPAGIRI CHANDRAKANTH</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>8142609575</t>
+          <t>9347305959</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>1991-06-18</t>
+          <t>1993-06-12</t>
         </is>
       </c>
       <c r="F105" s="21" t="inlineStr">
         <is>
-          <t>Rayachoty</t>
+          <t>VEERAPUNAYUNIPALLI, kadapa</t>
         </is>
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H105" s="13" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="M105" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0100</t>
+          <t>TKPL-RCPT-2026-0097</t>
         </is>
       </c>
       <c r="N105" s="22" t="inlineStr">
@@ -9601,12 +9601,12 @@
       </c>
       <c r="O105" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 07:08 PM</t>
+          <t>30-10-2026 07:03 PM</t>
         </is>
       </c>
       <c r="P105" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 07:06 PM</t>
+          <t>30-10-2026 07:00 PM</t>
         </is>
       </c>
       <c r="Q105" s="21" t="inlineStr">
@@ -9621,32 +9621,32 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0213</t>
+          <t>TKPL-2026-0210</t>
         </is>
       </c>
       <c r="C106" s="18" t="inlineStr">
         <is>
-          <t>Pandiboti jagadeesh</t>
+          <t>Yorker Yunus</t>
         </is>
       </c>
       <c r="D106" s="17" t="inlineStr">
         <is>
-          <t>6303081193</t>
+          <t>7095231174</t>
         </is>
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>2003-06-10</t>
+          <t>2005-03-28</t>
         </is>
       </c>
       <c r="F106" s="18" t="inlineStr">
         <is>
-          <t>Chakrayapeta</t>
+          <t>Nandimandalam , kadapa district</t>
         </is>
       </c>
       <c r="G106" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H106" s="17" t="inlineStr">
@@ -9659,7 +9659,11 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J106" s="18" t="inlineStr"/>
+      <c r="J106" s="18" t="inlineStr">
+        <is>
+          <t>Pulivendula tournaments and produtur tournament</t>
+        </is>
+      </c>
       <c r="K106" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -9672,7 +9676,7 @@
       </c>
       <c r="M106" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0101</t>
+          <t>TKPL-RCPT-2026-0098</t>
         </is>
       </c>
       <c r="N106" s="20" t="inlineStr">
@@ -9682,12 +9686,12 @@
       </c>
       <c r="O106" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 07:40 PM</t>
+          <t>30-10-2026 07:04 PM</t>
         </is>
       </c>
       <c r="P106" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 07:36 PM</t>
+          <t>30-10-2026 07:03 PM</t>
         </is>
       </c>
       <c r="Q106" s="18" t="inlineStr">
@@ -9702,32 +9706,32 @@
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0214</t>
+          <t>TKPL-2026-0211</t>
         </is>
       </c>
       <c r="C107" s="21" t="inlineStr">
         <is>
-          <t>Y Dharma Teja</t>
+          <t>Jalla mahesh Kumar</t>
         </is>
       </c>
       <c r="D107" s="13" t="inlineStr">
         <is>
-          <t>9963603701</t>
+          <t>8142609575</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>2008-01-04</t>
+          <t>1991-06-18</t>
         </is>
       </c>
       <c r="F107" s="21" t="inlineStr">
         <is>
-          <t>Pulivendula</t>
+          <t>Rayachoty</t>
         </is>
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
-          <t>Bowler</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H107" s="13" t="inlineStr">
@@ -9753,7 +9757,7 @@
       </c>
       <c r="M107" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0102</t>
+          <t>TKPL-RCPT-2026-0100</t>
         </is>
       </c>
       <c r="N107" s="22" t="inlineStr">
@@ -9763,12 +9767,12 @@
       </c>
       <c r="O107" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 07:42 PM</t>
+          <t>30-10-2026 07:08 PM</t>
         </is>
       </c>
       <c r="P107" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 07:39 PM</t>
+          <t>30-10-2026 07:06 PM</t>
         </is>
       </c>
       <c r="Q107" s="21" t="inlineStr">
@@ -9783,27 +9787,27 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0215</t>
+          <t>TKPL-2026-0213</t>
         </is>
       </c>
       <c r="C108" s="18" t="inlineStr">
         <is>
-          <t>PALEM CHANDU</t>
+          <t>Pandiboti jagadeesh</t>
         </is>
       </c>
       <c r="D108" s="17" t="inlineStr">
         <is>
-          <t>7093616070</t>
+          <t>6303081193</t>
         </is>
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>2008-08-10</t>
+          <t>2003-06-10</t>
         </is>
       </c>
       <c r="F108" s="18" t="inlineStr">
         <is>
-          <t>Gonumakulapalli</t>
+          <t>Chakrayapeta</t>
         </is>
       </c>
       <c r="G108" s="17" t="inlineStr">
@@ -9821,11 +9825,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J108" s="18" t="inlineStr">
-        <is>
-          <t>U-12 south zone  u-16 districts  30+ local tournaments</t>
-        </is>
-      </c>
+      <c r="J108" s="18" t="inlineStr"/>
       <c r="K108" s="17" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="M108" s="17" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0103</t>
+          <t>TKPL-RCPT-2026-0101</t>
         </is>
       </c>
       <c r="N108" s="20" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="O108" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 08:08 PM</t>
+          <t>30-10-2026 07:40 PM</t>
         </is>
       </c>
       <c r="P108" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 08:06 PM</t>
+          <t>30-10-2026 07:36 PM</t>
         </is>
       </c>
       <c r="Q108" s="18" t="inlineStr">
@@ -9868,22 +9868,22 @@
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0216</t>
+          <t>TKPL-2026-0214</t>
         </is>
       </c>
       <c r="C109" s="21" t="inlineStr">
         <is>
-          <t>Moillacheru Mahesh</t>
+          <t>Y Dharma Teja</t>
         </is>
       </c>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>6304114231</t>
+          <t>9963603701</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>1998-06-20</t>
+          <t>2008-01-04</t>
         </is>
       </c>
       <c r="F109" s="21" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H109" s="13" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="M109" s="13" t="inlineStr">
         <is>
-          <t>TKPL-RCPT-2026-0104</t>
+          <t>TKPL-RCPT-2026-0102</t>
         </is>
       </c>
       <c r="N109" s="22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="O109" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 08:12 PM</t>
+          <t>30-10-2026 07:42 PM</t>
         </is>
       </c>
       <c r="P109" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 08:11 PM</t>
+          <t>30-10-2026 07:39 PM</t>
         </is>
       </c>
       <c r="Q109" s="21" t="inlineStr">
@@ -9949,87 +9949,2087 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
+          <t>TKPL-2026-0215</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>PALEM CHANDU</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="inlineStr">
+        <is>
+          <t>7093616070</t>
+        </is>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>2008-08-10</t>
+        </is>
+      </c>
+      <c r="F110" s="18" t="inlineStr">
+        <is>
+          <t>Gonumakulapalli</t>
+        </is>
+      </c>
+      <c r="G110" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H110" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J110" s="18" t="inlineStr">
+        <is>
+          <t>U-12 south zone  u-16 districts  30+ local tournaments</t>
+        </is>
+      </c>
+      <c r="K110" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L110" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M110" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0103</t>
+        </is>
+      </c>
+      <c r="N110" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O110" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:08 PM</t>
+        </is>
+      </c>
+      <c r="P110" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:06 PM</t>
+        </is>
+      </c>
+      <c r="Q110" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0216</t>
+        </is>
+      </c>
+      <c r="C111" s="21" t="inlineStr">
+        <is>
+          <t>Moillacheru Mahesh</t>
+        </is>
+      </c>
+      <c r="D111" s="13" t="inlineStr">
+        <is>
+          <t>6304114231</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>1998-06-20</t>
+        </is>
+      </c>
+      <c r="F111" s="21" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H111" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J111" s="21" t="inlineStr"/>
+      <c r="K111" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L111" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M111" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0104</t>
+        </is>
+      </c>
+      <c r="N111" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O111" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:12 PM</t>
+        </is>
+      </c>
+      <c r="P111" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 08:11 PM</t>
+        </is>
+      </c>
+      <c r="Q111" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="17" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="17" t="inlineStr">
+        <is>
           <t>TKPL-2026-0217</t>
         </is>
       </c>
-      <c r="C110" s="18" t="inlineStr">
+      <c r="C112" s="18" t="inlineStr">
         <is>
           <t>Kasthuri saikumar(power sai)</t>
         </is>
       </c>
-      <c r="D110" s="17" t="inlineStr">
+      <c r="D112" s="17" t="inlineStr">
         <is>
           <t>8886440355</t>
         </is>
       </c>
-      <c r="E110" s="17" t="inlineStr">
+      <c r="E112" s="17" t="inlineStr">
         <is>
           <t>1998-06-11</t>
         </is>
       </c>
-      <c r="F110" s="18" t="inlineStr">
+      <c r="F112" s="18" t="inlineStr">
         <is>
           <t>Nandhimandalam</t>
         </is>
       </c>
-      <c r="G110" s="17" t="inlineStr">
+      <c r="G112" s="17" t="inlineStr">
         <is>
           <t>All-Rounder</t>
         </is>
       </c>
-      <c r="H110" s="17" t="inlineStr">
-        <is>
-          <t>Right Hand</t>
-        </is>
-      </c>
-      <c r="I110" s="17" t="inlineStr">
+      <c r="H112" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
         <is>
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J110" s="18" t="inlineStr">
+      <c r="J112" s="18" t="inlineStr">
         <is>
           <t>Local tournaments</t>
         </is>
       </c>
-      <c r="K110" s="17" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="L110" s="19" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="M110" s="17" t="inlineStr">
+      <c r="K112" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L112" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M112" s="17" t="inlineStr">
         <is>
           <t>TKPL-RCPT-2026-0106</t>
         </is>
       </c>
-      <c r="N110" s="20" t="inlineStr">
-        <is>
-          <t>₹399</t>
-        </is>
-      </c>
-      <c r="O110" s="17" t="inlineStr">
+      <c r="N112" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O112" s="17" t="inlineStr">
         <is>
           <t>30-10-2026 08:24 PM</t>
         </is>
       </c>
-      <c r="P110" s="17" t="inlineStr">
+      <c r="P112" s="17" t="inlineStr">
         <is>
           <t>30-10-2026 08:23 PM</t>
         </is>
       </c>
-      <c r="Q110" s="18" t="inlineStr">
+      <c r="Q112" s="18" t="inlineStr">
         <is>
           <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0218</t>
+        </is>
+      </c>
+      <c r="C113" s="21" t="inlineStr">
+        <is>
+          <t>D SUBHAN</t>
+        </is>
+      </c>
+      <c r="D113" s="13" t="inlineStr">
+        <is>
+          <t>7659847184</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>1996-05-15</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t>GUDIPADU</t>
+        </is>
+      </c>
+      <c r="G113" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H113" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J113" s="21" t="inlineStr"/>
+      <c r="K113" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L113" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M113" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0110</t>
+        </is>
+      </c>
+      <c r="N113" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O113" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:09 PM</t>
+        </is>
+      </c>
+      <c r="P113" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:08 PM</t>
+        </is>
+      </c>
+      <c r="Q113" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="17" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0219</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
+        <is>
+          <t>R SIRAJUDDIN</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="inlineStr">
+        <is>
+          <t>8341772788</t>
+        </is>
+      </c>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>1995-06-05</t>
+        </is>
+      </c>
+      <c r="F114" s="18" t="inlineStr">
+        <is>
+          <t>KHAJIPETA</t>
+        </is>
+      </c>
+      <c r="G114" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H114" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I114" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J114" s="18" t="inlineStr">
+        <is>
+          <t>Recent jan 2025 -NATIONAL CHAMPIONSHIP</t>
+        </is>
+      </c>
+      <c r="K114" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L114" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M114" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0111</t>
+        </is>
+      </c>
+      <c r="N114" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O114" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:13 PM</t>
+        </is>
+      </c>
+      <c r="P114" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:13 PM</t>
+        </is>
+      </c>
+      <c r="Q114" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="13" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0220</t>
+        </is>
+      </c>
+      <c r="C115" s="21" t="inlineStr">
+        <is>
+          <t>P.Manikanta</t>
+        </is>
+      </c>
+      <c r="D115" s="13" t="inlineStr">
+        <is>
+          <t>9381010023</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="inlineStr">
+        <is>
+          <t>1995-06-16</t>
+        </is>
+      </c>
+      <c r="F115" s="21" t="inlineStr">
+        <is>
+          <t>Lakkireddy palli (m) ,Rayachoty</t>
+        </is>
+      </c>
+      <c r="G115" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H115" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J115" s="21" t="inlineStr">
+        <is>
+          <t>Ysr premier league, Dudekala palli cricket league</t>
+        </is>
+      </c>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L115" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M115" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0113</t>
+        </is>
+      </c>
+      <c r="N115" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O115" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:46 PM</t>
+        </is>
+      </c>
+      <c r="P115" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:45 PM</t>
+        </is>
+      </c>
+      <c r="Q115" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="17" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0221</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>G.Nagendra</t>
+        </is>
+      </c>
+      <c r="D116" s="17" t="inlineStr">
+        <is>
+          <t>9849873443</t>
+        </is>
+      </c>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t>1995-06-02</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="inlineStr">
+        <is>
+          <t>Lakkireddy palli</t>
+        </is>
+      </c>
+      <c r="G116" s="17" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H116" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J116" s="18" t="inlineStr">
+        <is>
+          <t>RPL premier league, Ysr cricket league</t>
+        </is>
+      </c>
+      <c r="K116" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L116" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M116" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0114</t>
+        </is>
+      </c>
+      <c r="N116" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O116" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 11:01 PM</t>
+        </is>
+      </c>
+      <c r="P116" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 11:00 PM</t>
+        </is>
+      </c>
+      <c r="Q116" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="13" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0222</t>
+        </is>
+      </c>
+      <c r="C117" s="21" t="inlineStr">
+        <is>
+          <t>penchalaiah chepuri</t>
+        </is>
+      </c>
+      <c r="D117" s="13" t="inlineStr">
+        <is>
+          <t>6360920486</t>
+        </is>
+      </c>
+      <c r="E117" s="13" t="inlineStr">
+        <is>
+          <t>1990-06-20</t>
+        </is>
+      </c>
+      <c r="F117" s="21" t="inlineStr">
+        <is>
+          <t>S K R nagar  madhavaram 1 , sidhout mandal, kadapa</t>
+        </is>
+      </c>
+      <c r="G117" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H117" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J117" s="21" t="inlineStr"/>
+      <c r="K117" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L117" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M117" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0115</t>
+        </is>
+      </c>
+      <c r="N117" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O117" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 11:39 PM</t>
+        </is>
+      </c>
+      <c r="P117" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 11:38 PM</t>
+        </is>
+      </c>
+      <c r="Q117" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0224</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>Sreekrishna .P</t>
+        </is>
+      </c>
+      <c r="D118" s="17" t="inlineStr">
+        <is>
+          <t>9642237511</t>
+        </is>
+      </c>
+      <c r="E118" s="17" t="inlineStr">
+        <is>
+          <t>1994-02-20</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>Devaragutta palli</t>
+        </is>
+      </c>
+      <c r="G118" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H118" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I118" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J118" s="18" t="inlineStr"/>
+      <c r="K118" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L118" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M118" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0116</t>
+        </is>
+      </c>
+      <c r="N118" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O118" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:34 AM</t>
+        </is>
+      </c>
+      <c r="P118" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:33 AM</t>
+        </is>
+      </c>
+      <c r="Q118" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="13" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0225</t>
+        </is>
+      </c>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>Duggineni Ramaiah</t>
+        </is>
+      </c>
+      <c r="D119" s="13" t="inlineStr">
+        <is>
+          <t>6300723321</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="inlineStr">
+        <is>
+          <t>2001-06-04</t>
+        </is>
+      </c>
+      <c r="F119" s="21" t="inlineStr">
+        <is>
+          <t>Badvel</t>
+        </is>
+      </c>
+      <c r="G119" s="13" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H119" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J119" s="21" t="inlineStr"/>
+      <c r="K119" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L119" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M119" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0117</t>
+        </is>
+      </c>
+      <c r="N119" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O119" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:36 AM</t>
+        </is>
+      </c>
+      <c r="P119" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:35 AM</t>
+        </is>
+      </c>
+      <c r="Q119" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="17" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0226</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>Suneel K</t>
+        </is>
+      </c>
+      <c r="D120" s="17" t="inlineStr">
+        <is>
+          <t>8008353200</t>
+        </is>
+      </c>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t>1991-07-17</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>Proddatur</t>
+        </is>
+      </c>
+      <c r="G120" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H120" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J120" s="18" t="inlineStr"/>
+      <c r="K120" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L120" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M120" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0118</t>
+        </is>
+      </c>
+      <c r="N120" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O120" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:40 AM</t>
+        </is>
+      </c>
+      <c r="P120" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:39 AM</t>
+        </is>
+      </c>
+      <c r="Q120" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0227</t>
+        </is>
+      </c>
+      <c r="C121" s="21" t="inlineStr">
+        <is>
+          <t>Komma sai karthik reddy</t>
+        </is>
+      </c>
+      <c r="D121" s="13" t="inlineStr">
+        <is>
+          <t>6281530172</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G121" s="13" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H121" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J121" s="21" t="inlineStr">
+        <is>
+          <t>Yes sir</t>
+        </is>
+      </c>
+      <c r="K121" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L121" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M121" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0119</t>
+        </is>
+      </c>
+      <c r="N121" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O121" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:41 AM</t>
+        </is>
+      </c>
+      <c r="P121" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:40 AM</t>
+        </is>
+      </c>
+      <c r="Q121" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="17" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0228</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>Nagendra yadav</t>
+        </is>
+      </c>
+      <c r="D122" s="17" t="inlineStr">
+        <is>
+          <t>6305023573</t>
+        </is>
+      </c>
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t>2000-10-03</t>
+        </is>
+      </c>
+      <c r="F122" s="18" t="inlineStr">
+        <is>
+          <t>Badvel</t>
+        </is>
+      </c>
+      <c r="G122" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H122" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J122" s="18" t="inlineStr"/>
+      <c r="K122" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L122" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M122" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0120</t>
+        </is>
+      </c>
+      <c r="N122" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O122" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:54 AM</t>
+        </is>
+      </c>
+      <c r="P122" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:53 AM</t>
+        </is>
+      </c>
+      <c r="Q122" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="13" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0229</t>
+        </is>
+      </c>
+      <c r="C123" s="21" t="inlineStr">
+        <is>
+          <t>Dinesh Vulli</t>
+        </is>
+      </c>
+      <c r="D123" s="13" t="inlineStr">
+        <is>
+          <t>8919184201</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>1990-07-10</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="inlineStr">
+        <is>
+          <t>Proddatur</t>
+        </is>
+      </c>
+      <c r="G123" s="13" t="inlineStr">
+        <is>
+          <t>Wicketkeeper</t>
+        </is>
+      </c>
+      <c r="H123" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J123" s="21" t="inlineStr">
+        <is>
+          <t>All local tourments played</t>
+        </is>
+      </c>
+      <c r="K123" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L123" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M123" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0121</t>
+        </is>
+      </c>
+      <c r="N123" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O123" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 07:06 AM</t>
+        </is>
+      </c>
+      <c r="P123" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 07:05 AM</t>
+        </is>
+      </c>
+      <c r="Q123" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0230</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="inlineStr">
+        <is>
+          <t>Praveen Ganapathi</t>
+        </is>
+      </c>
+      <c r="D124" s="17" t="inlineStr">
+        <is>
+          <t>8919532610</t>
+        </is>
+      </c>
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t>1994-06-06</t>
+        </is>
+      </c>
+      <c r="F124" s="18" t="inlineStr">
+        <is>
+          <t>Rayachoty</t>
+        </is>
+      </c>
+      <c r="G124" s="17" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H124" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I124" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J124" s="18" t="inlineStr">
+        <is>
+          <t>Rayachoty primary league runner-up team member</t>
+        </is>
+      </c>
+      <c r="K124" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L124" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M124" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0122</t>
+        </is>
+      </c>
+      <c r="N124" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O124" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 08:59 AM</t>
+        </is>
+      </c>
+      <c r="P124" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 08:58 AM</t>
+        </is>
+      </c>
+      <c r="Q124" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="13" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0231</t>
+        </is>
+      </c>
+      <c r="C125" s="21" t="inlineStr">
+        <is>
+          <t>E. Krishna Prasad</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>7997080030</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>1988-06-12</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="inlineStr">
+        <is>
+          <t>Kadapa, రామచంద్రపురం</t>
+        </is>
+      </c>
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J125" s="21" t="inlineStr">
+        <is>
+          <t>Rcp క్రికెట్ club</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L125" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M125" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0123</t>
+        </is>
+      </c>
+      <c r="N125" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O125" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:06 AM</t>
+        </is>
+      </c>
+      <c r="P125" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:05 AM</t>
+        </is>
+      </c>
+      <c r="Q125" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0232</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>Thota Jaswanth</t>
+        </is>
+      </c>
+      <c r="D126" s="17" t="inlineStr">
+        <is>
+          <t>9347692650</t>
+        </is>
+      </c>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
+          <t>2007-06-17</t>
+        </is>
+      </c>
+      <c r="F126" s="18" t="inlineStr">
+        <is>
+          <t>Galiveedu near Gottiveedu</t>
+        </is>
+      </c>
+      <c r="G126" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H126" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J126" s="18" t="inlineStr">
+        <is>
+          <t>Jaruguvandla palli near Madhavaram</t>
+        </is>
+      </c>
+      <c r="K126" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L126" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M126" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0124</t>
+        </is>
+      </c>
+      <c r="N126" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O126" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:17 AM</t>
+        </is>
+      </c>
+      <c r="P126" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:16 AM</t>
+        </is>
+      </c>
+      <c r="Q126" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="13" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0234</t>
+        </is>
+      </c>
+      <c r="C127" s="21" t="inlineStr">
+        <is>
+          <t>VALLEPU GANESH</t>
+        </is>
+      </c>
+      <c r="D127" s="13" t="inlineStr">
+        <is>
+          <t>9908853576</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>2004-10-23</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G127" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H127" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J127" s="21" t="inlineStr">
+        <is>
+          <t>South zone 2026</t>
+        </is>
+      </c>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L127" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M127" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0125</t>
+        </is>
+      </c>
+      <c r="N127" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O127" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:52 AM</t>
+        </is>
+      </c>
+      <c r="P127" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:51 AM</t>
+        </is>
+      </c>
+      <c r="Q127" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="17" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0235</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="inlineStr">
+        <is>
+          <t>Sudeer</t>
+        </is>
+      </c>
+      <c r="D128" s="17" t="inlineStr">
+        <is>
+          <t>8217086217</t>
+        </is>
+      </c>
+      <c r="E128" s="17" t="inlineStr">
+        <is>
+          <t>1992-05-06</t>
+        </is>
+      </c>
+      <c r="F128" s="18" t="inlineStr">
+        <is>
+          <t>Vempalli</t>
+        </is>
+      </c>
+      <c r="G128" s="17" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H128" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I128" s="17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J128" s="18" t="inlineStr"/>
+      <c r="K128" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L128" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M128" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0126</t>
+        </is>
+      </c>
+      <c r="N128" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O128" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:06 AM</t>
+        </is>
+      </c>
+      <c r="P128" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:05 AM</t>
+        </is>
+      </c>
+      <c r="Q128" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0236</t>
+        </is>
+      </c>
+      <c r="C129" s="21" t="inlineStr">
+        <is>
+          <t>Vennapusa Lakshmi Reddy</t>
+        </is>
+      </c>
+      <c r="D129" s="13" t="inlineStr">
+        <is>
+          <t>8074883035</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t>2000-07-08</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="inlineStr">
+        <is>
+          <t>Pendlimarri mandal, Kadapa</t>
+        </is>
+      </c>
+      <c r="G129" s="13" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H129" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J129" s="21" t="inlineStr"/>
+      <c r="K129" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L129" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M129" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0127</t>
+        </is>
+      </c>
+      <c r="N129" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O129" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:15 AM</t>
+        </is>
+      </c>
+      <c r="P129" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:13 AM</t>
+        </is>
+      </c>
+      <c r="Q129" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="17" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0237</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="inlineStr">
+        <is>
+          <t>RAHAMATHULLA   MANI</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t>9701035323</t>
+        </is>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>1998-08-24</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>Chakibanda</t>
+        </is>
+      </c>
+      <c r="G130" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H130" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J130" s="18" t="inlineStr">
+        <is>
+          <t>PLAYING KER ACADEMY IN Raya choty</t>
+        </is>
+      </c>
+      <c r="K130" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L130" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M130" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0128</t>
+        </is>
+      </c>
+      <c r="N130" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O130" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:40 AM</t>
+        </is>
+      </c>
+      <c r="P130" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:38 AM</t>
+        </is>
+      </c>
+      <c r="Q130" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0238</t>
+        </is>
+      </c>
+      <c r="C131" s="21" t="inlineStr">
+        <is>
+          <t>Robin</t>
+        </is>
+      </c>
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>8688562626</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>1998-06-22</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t>Ontimitta,kadapa</t>
+        </is>
+      </c>
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H131" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J131" s="21" t="inlineStr"/>
+      <c r="K131" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L131" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M131" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0129</t>
+        </is>
+      </c>
+      <c r="N131" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O131" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="P131" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:58 AM</t>
+        </is>
+      </c>
+      <c r="Q131" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0239</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>Ganga Mahesh</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t>6305134304</t>
+        </is>
+      </c>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t>2003-05-17</t>
+        </is>
+      </c>
+      <c r="F132" s="18" t="inlineStr">
+        <is>
+          <t>Yerraguntla</t>
+        </is>
+      </c>
+      <c r="G132" s="17" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H132" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I132" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J132" s="18" t="inlineStr">
+        <is>
+          <t>Playing local tournaments</t>
+        </is>
+      </c>
+      <c r="K132" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L132" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M132" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0131</t>
+        </is>
+      </c>
+      <c r="N132" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O132" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:18 AM</t>
+        </is>
+      </c>
+      <c r="P132" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:17 AM</t>
+        </is>
+      </c>
+      <c r="Q132" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="13" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0240</t>
+        </is>
+      </c>
+      <c r="C133" s="21" t="inlineStr">
+        <is>
+          <t>Abdul Salam 07</t>
+        </is>
+      </c>
+      <c r="D133" s="13" t="inlineStr">
+        <is>
+          <t>7997686064</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="inlineStr">
+        <is>
+          <t>2004-12-14</t>
+        </is>
+      </c>
+      <c r="F133" s="21" t="inlineStr">
+        <is>
+          <t>Rajampeta</t>
+        </is>
+      </c>
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J133" s="21" t="inlineStr">
+        <is>
+          <t>Local Tournaments</t>
+        </is>
+      </c>
+      <c r="K133" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L133" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M133" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0133</t>
+        </is>
+      </c>
+      <c r="N133" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O133" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 12:59 PM</t>
+        </is>
+      </c>
+      <c r="P133" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:22 AM</t>
+        </is>
+      </c>
+      <c r="Q133" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="17" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0241</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>C . Lokeswar</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr">
+        <is>
+          <t>9550815737</t>
+        </is>
+      </c>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>1996-03-28</t>
+        </is>
+      </c>
+      <c r="F134" s="18" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G134" s="17" t="inlineStr">
+        <is>
+          <t>Wicketkeeper</t>
+        </is>
+      </c>
+      <c r="H134" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J134" s="18" t="inlineStr">
+        <is>
+          <t>Pulivendula tournments thimammapalli tournament all years continue pertispate</t>
+        </is>
+      </c>
+      <c r="K134" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L134" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M134" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0132</t>
+        </is>
+      </c>
+      <c r="N134" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O134" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:46 AM</t>
+        </is>
+      </c>
+      <c r="P134" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:45 AM</t>
+        </is>
+      </c>
+      <c r="Q134" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q110"/>
+  <autoFilter ref="A1:Q134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10040,7 +12040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10487,32 +12487,32 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0158</t>
+          <t>TKPL-2026-0164</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>Shaikbabaji</t>
+          <t>Bhanu prakash</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>9885626641</t>
+          <t>9100859612</t>
         </is>
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>1996-01-17</t>
+          <t>2008-09-21</t>
         </is>
       </c>
       <c r="F6" s="18" t="inlineStr">
         <is>
-          <t>Nagulaguttapalli</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Wicketkeeper</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
@@ -10527,7 +12527,7 @@
       </c>
       <c r="J6" s="18" t="inlineStr">
         <is>
-          <t>I have  local tournaments  experience</t>
+          <t>Renadu titians and pai viecory tirupati</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
@@ -10557,7 +12557,7 @@
       </c>
       <c r="P6" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 01:19 PM</t>
+          <t>30-10-2026 01:49 PM</t>
         </is>
       </c>
       <c r="Q6" s="18" t="inlineStr">
@@ -10572,27 +12572,27 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0164</t>
+          <t>TKPL-2026-0212</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>Bhanu prakash</t>
+          <t>Rachamallu Mallikarjuna Reddy</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>9100859612</t>
+          <t>9652490435</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>2008-09-21</t>
+          <t>1990-07-06</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t>Kadapa</t>
+          <t>Vempalli</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -10610,11 +12610,7 @@
           <t>Right-arm Pace</t>
         </is>
       </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>Renadu titians and pai viecory tirupati</t>
-        </is>
-      </c>
+      <c r="J7" s="21" t="inlineStr"/>
       <c r="K7" s="13" t="inlineStr">
         <is>
           <t>Submitted</t>
@@ -10642,7 +12638,7 @@
       </c>
       <c r="P7" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 01:49 PM</t>
+          <t>30-10-2026 07:32 PM</t>
         </is>
       </c>
       <c r="Q7" s="21" t="inlineStr">
@@ -10657,32 +12653,32 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>TKPL-2026-0202</t>
+          <t>TKPL-2026-0223</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>R shahabuddin</t>
+          <t>Sonu akthar</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>8639460531</t>
+          <t>6309928386</t>
         </is>
       </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>2009-08-20</t>
+          <t>2000-04-28</t>
         </is>
       </c>
       <c r="F8" s="18" t="inlineStr">
         <is>
-          <t>Khajipeta</t>
+          <t>Kadapa</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>All-Rounder</t>
+          <t>Bowler</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
@@ -10692,10 +12688,14 @@
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>Right-arm Pace</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr"/>
+          <t>Right-arm Spin</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>All.i played in ipl</t>
+        </is>
+      </c>
       <c r="K8" s="17" t="inlineStr">
         <is>
           <t>Submitted</t>
@@ -10723,7 +12723,7 @@
       </c>
       <c r="P8" s="17" t="inlineStr">
         <is>
-          <t>30-10-2026 05:16 PM</t>
+          <t>31-10-2026 01:23 AM</t>
         </is>
       </c>
       <c r="Q8" s="18" t="inlineStr">
@@ -10738,32 +12738,32 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>TKPL-2026-0212</t>
+          <t>TKPL-2026-0233</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
-          <t>Rachamallu Mallikarjuna Reddy</t>
+          <t>Shaik Mohammad</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>9652490435</t>
+          <t>7842625468</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>1990-07-06</t>
+          <t>2006-12-15</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t>Vempalli</t>
+          <t>Kadapa district Vempalli</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Wicketkeeper</t>
+          <t>All-Rounder</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -10804,7 +12804,7 @@
       </c>
       <c r="P9" s="13" t="inlineStr">
         <is>
-          <t>30-10-2026 07:32 PM</t>
+          <t>31-10-2026 09:20 AM</t>
         </is>
       </c>
       <c r="Q9" s="21" t="inlineStr">
@@ -10813,8 +12813,170 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0242</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Gandepoornanandha</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>9014177870</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>2010-03-03</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Rayachoti</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="inlineStr"/>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P10" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 12:25 PM</t>
+        </is>
+      </c>
+      <c r="Q10" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0243</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>Shaik abdul aslam</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>9347817220</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>2006-08-13</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>Kadapa</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Wicketkeeper</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr"/>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P11" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="Q11" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q9"/>
+  <autoFilter ref="A1:Q11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10825,7 +12987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q118"/>
+  <dimension ref="A1:Q144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15743,17 +17905,17 @@
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L59" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L59" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TKPL-RCPT-2026-0130</t>
         </is>
       </c>
       <c r="N59" s="22" t="inlineStr">
@@ -15763,7 +17925,7 @@
       </c>
       <c r="O59" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31-10-2026 11:12 AM</t>
         </is>
       </c>
       <c r="P59" s="13" t="inlineStr">
@@ -15773,7 +17935,7 @@
       </c>
       <c r="Q59" s="21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -19417,17 +21579,17 @@
       <c r="J103" s="21" t="inlineStr"/>
       <c r="K103" s="13" t="inlineStr">
         <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="L103" s="26" t="inlineStr">
-        <is>
-          <t>Pending</t>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L103" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
       <c r="M103" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TKPL-RCPT-2026-0112</t>
         </is>
       </c>
       <c r="N103" s="22" t="inlineStr">
@@ -19437,7 +21599,7 @@
       </c>
       <c r="O103" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30-10-2026 10:17 PM</t>
         </is>
       </c>
       <c r="P103" s="13" t="inlineStr">
@@ -19447,7 +21609,7 @@
       </c>
       <c r="Q103" s="21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
         </is>
       </c>
     </row>
@@ -20682,8 +22844,2170 @@
         </is>
       </c>
     </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="13" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0218</t>
+        </is>
+      </c>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>D SUBHAN</t>
+        </is>
+      </c>
+      <c r="D119" s="13" t="inlineStr">
+        <is>
+          <t>7659847184</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="inlineStr">
+        <is>
+          <t>1996-05-15</t>
+        </is>
+      </c>
+      <c r="F119" s="21" t="inlineStr">
+        <is>
+          <t>GUDIPADU</t>
+        </is>
+      </c>
+      <c r="G119" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H119" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J119" s="21" t="inlineStr"/>
+      <c r="K119" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L119" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M119" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0110</t>
+        </is>
+      </c>
+      <c r="N119" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O119" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:09 PM</t>
+        </is>
+      </c>
+      <c r="P119" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:08 PM</t>
+        </is>
+      </c>
+      <c r="Q119" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="17" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0219</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>R SIRAJUDDIN</t>
+        </is>
+      </c>
+      <c r="D120" s="17" t="inlineStr">
+        <is>
+          <t>8341772788</t>
+        </is>
+      </c>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t>1995-06-05</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>KHAJIPETA</t>
+        </is>
+      </c>
+      <c r="G120" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H120" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J120" s="18" t="inlineStr">
+        <is>
+          <t>Recent jan 2025 -NATIONAL CHAMPIONSHIP</t>
+        </is>
+      </c>
+      <c r="K120" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L120" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M120" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0111</t>
+        </is>
+      </c>
+      <c r="N120" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O120" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:13 PM</t>
+        </is>
+      </c>
+      <c r="P120" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:13 PM</t>
+        </is>
+      </c>
+      <c r="Q120" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0220</t>
+        </is>
+      </c>
+      <c r="C121" s="21" t="inlineStr">
+        <is>
+          <t>P.Manikanta</t>
+        </is>
+      </c>
+      <c r="D121" s="13" t="inlineStr">
+        <is>
+          <t>9381010023</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="inlineStr">
+        <is>
+          <t>1995-06-16</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="inlineStr">
+        <is>
+          <t>Lakkireddy palli (m) ,Rayachoty</t>
+        </is>
+      </c>
+      <c r="G121" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H121" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J121" s="21" t="inlineStr">
+        <is>
+          <t>Ysr premier league, Dudekala palli cricket league</t>
+        </is>
+      </c>
+      <c r="K121" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L121" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M121" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0113</t>
+        </is>
+      </c>
+      <c r="N121" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O121" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:46 PM</t>
+        </is>
+      </c>
+      <c r="P121" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 10:45 PM</t>
+        </is>
+      </c>
+      <c r="Q121" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="17" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0221</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>G.Nagendra</t>
+        </is>
+      </c>
+      <c r="D122" s="17" t="inlineStr">
+        <is>
+          <t>9849873443</t>
+        </is>
+      </c>
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t>1995-06-02</t>
+        </is>
+      </c>
+      <c r="F122" s="18" t="inlineStr">
+        <is>
+          <t>Lakkireddy palli</t>
+        </is>
+      </c>
+      <c r="G122" s="17" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H122" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J122" s="18" t="inlineStr">
+        <is>
+          <t>RPL premier league, Ysr cricket league</t>
+        </is>
+      </c>
+      <c r="K122" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L122" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M122" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0114</t>
+        </is>
+      </c>
+      <c r="N122" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O122" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 11:01 PM</t>
+        </is>
+      </c>
+      <c r="P122" s="17" t="inlineStr">
+        <is>
+          <t>30-10-2026 11:00 PM</t>
+        </is>
+      </c>
+      <c r="Q122" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="13" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0222</t>
+        </is>
+      </c>
+      <c r="C123" s="21" t="inlineStr">
+        <is>
+          <t>penchalaiah chepuri</t>
+        </is>
+      </c>
+      <c r="D123" s="13" t="inlineStr">
+        <is>
+          <t>6360920486</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>1990-06-20</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="inlineStr">
+        <is>
+          <t>S K R nagar  madhavaram 1 , sidhout mandal, kadapa</t>
+        </is>
+      </c>
+      <c r="G123" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H123" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J123" s="21" t="inlineStr"/>
+      <c r="K123" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L123" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M123" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0115</t>
+        </is>
+      </c>
+      <c r="N123" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O123" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 11:39 PM</t>
+        </is>
+      </c>
+      <c r="P123" s="13" t="inlineStr">
+        <is>
+          <t>30-10-2026 11:38 PM</t>
+        </is>
+      </c>
+      <c r="Q123" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0223</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="inlineStr">
+        <is>
+          <t>Sonu akthar</t>
+        </is>
+      </c>
+      <c r="D124" s="17" t="inlineStr">
+        <is>
+          <t>6309928386</t>
+        </is>
+      </c>
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t>2000-04-28</t>
+        </is>
+      </c>
+      <c r="F124" s="18" t="inlineStr">
+        <is>
+          <t>Kadapa</t>
+        </is>
+      </c>
+      <c r="G124" s="17" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H124" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I124" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Spin</t>
+        </is>
+      </c>
+      <c r="J124" s="18" t="inlineStr">
+        <is>
+          <t>All.i played in ipl</t>
+        </is>
+      </c>
+      <c r="K124" s="17" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="L124" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M124" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O124" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P124" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 01:23 AM</t>
+        </is>
+      </c>
+      <c r="Q124" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="13" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0224</t>
+        </is>
+      </c>
+      <c r="C125" s="21" t="inlineStr">
+        <is>
+          <t>Sreekrishna .P</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>9642237511</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>1994-02-20</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="inlineStr">
+        <is>
+          <t>Devaragutta palli</t>
+        </is>
+      </c>
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J125" s="21" t="inlineStr"/>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L125" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M125" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0116</t>
+        </is>
+      </c>
+      <c r="N125" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O125" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:34 AM</t>
+        </is>
+      </c>
+      <c r="P125" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:33 AM</t>
+        </is>
+      </c>
+      <c r="Q125" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0225</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>Duggineni Ramaiah</t>
+        </is>
+      </c>
+      <c r="D126" s="17" t="inlineStr">
+        <is>
+          <t>6300723321</t>
+        </is>
+      </c>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
+          <t>2001-06-04</t>
+        </is>
+      </c>
+      <c r="F126" s="18" t="inlineStr">
+        <is>
+          <t>Badvel</t>
+        </is>
+      </c>
+      <c r="G126" s="17" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H126" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I126" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J126" s="18" t="inlineStr"/>
+      <c r="K126" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L126" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M126" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0117</t>
+        </is>
+      </c>
+      <c r="N126" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O126" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:36 AM</t>
+        </is>
+      </c>
+      <c r="P126" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:35 AM</t>
+        </is>
+      </c>
+      <c r="Q126" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="13" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0226</t>
+        </is>
+      </c>
+      <c r="C127" s="21" t="inlineStr">
+        <is>
+          <t>Suneel K</t>
+        </is>
+      </c>
+      <c r="D127" s="13" t="inlineStr">
+        <is>
+          <t>8008353200</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>1991-07-17</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="inlineStr">
+        <is>
+          <t>Proddatur</t>
+        </is>
+      </c>
+      <c r="G127" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H127" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J127" s="21" t="inlineStr"/>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L127" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M127" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0118</t>
+        </is>
+      </c>
+      <c r="N127" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O127" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:40 AM</t>
+        </is>
+      </c>
+      <c r="P127" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:39 AM</t>
+        </is>
+      </c>
+      <c r="Q127" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="17" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0227</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="inlineStr">
+        <is>
+          <t>Komma sai karthik reddy</t>
+        </is>
+      </c>
+      <c r="D128" s="17" t="inlineStr">
+        <is>
+          <t>6281530172</t>
+        </is>
+      </c>
+      <c r="E128" s="17" t="inlineStr">
+        <is>
+          <t>2007-07-04</t>
+        </is>
+      </c>
+      <c r="F128" s="18" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G128" s="17" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H128" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I128" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J128" s="18" t="inlineStr">
+        <is>
+          <t>Yes sir</t>
+        </is>
+      </c>
+      <c r="K128" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L128" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M128" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0119</t>
+        </is>
+      </c>
+      <c r="N128" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O128" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:41 AM</t>
+        </is>
+      </c>
+      <c r="P128" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:40 AM</t>
+        </is>
+      </c>
+      <c r="Q128" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0228</t>
+        </is>
+      </c>
+      <c r="C129" s="21" t="inlineStr">
+        <is>
+          <t>Nagendra yadav</t>
+        </is>
+      </c>
+      <c r="D129" s="13" t="inlineStr">
+        <is>
+          <t>6305023573</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t>2000-10-03</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="inlineStr">
+        <is>
+          <t>Badvel</t>
+        </is>
+      </c>
+      <c r="G129" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H129" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J129" s="21" t="inlineStr"/>
+      <c r="K129" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L129" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M129" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0120</t>
+        </is>
+      </c>
+      <c r="N129" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O129" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:54 AM</t>
+        </is>
+      </c>
+      <c r="P129" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 06:53 AM</t>
+        </is>
+      </c>
+      <c r="Q129" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="17" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0229</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="inlineStr">
+        <is>
+          <t>Dinesh Vulli</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t>8919184201</t>
+        </is>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>1990-07-10</t>
+        </is>
+      </c>
+      <c r="F130" s="18" t="inlineStr">
+        <is>
+          <t>Proddatur</t>
+        </is>
+      </c>
+      <c r="G130" s="17" t="inlineStr">
+        <is>
+          <t>Wicketkeeper</t>
+        </is>
+      </c>
+      <c r="H130" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J130" s="18" t="inlineStr">
+        <is>
+          <t>All local tourments played</t>
+        </is>
+      </c>
+      <c r="K130" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L130" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M130" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0121</t>
+        </is>
+      </c>
+      <c r="N130" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O130" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 07:06 AM</t>
+        </is>
+      </c>
+      <c r="P130" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 07:05 AM</t>
+        </is>
+      </c>
+      <c r="Q130" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0230</t>
+        </is>
+      </c>
+      <c r="C131" s="21" t="inlineStr">
+        <is>
+          <t>Praveen Ganapathi</t>
+        </is>
+      </c>
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>8919532610</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>1994-06-06</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t>Rayachoty</t>
+        </is>
+      </c>
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H131" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J131" s="21" t="inlineStr">
+        <is>
+          <t>Rayachoty primary league runner-up team member</t>
+        </is>
+      </c>
+      <c r="K131" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L131" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M131" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0122</t>
+        </is>
+      </c>
+      <c r="N131" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O131" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 08:59 AM</t>
+        </is>
+      </c>
+      <c r="P131" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 08:58 AM</t>
+        </is>
+      </c>
+      <c r="Q131" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0231</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>E. Krishna Prasad</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t>7997080030</t>
+        </is>
+      </c>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t>1988-06-12</t>
+        </is>
+      </c>
+      <c r="F132" s="18" t="inlineStr">
+        <is>
+          <t>Kadapa, రామచంద్రపురం</t>
+        </is>
+      </c>
+      <c r="G132" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H132" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I132" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J132" s="18" t="inlineStr">
+        <is>
+          <t>Rcp క్రికెట్ club</t>
+        </is>
+      </c>
+      <c r="K132" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L132" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M132" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0123</t>
+        </is>
+      </c>
+      <c r="N132" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O132" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:06 AM</t>
+        </is>
+      </c>
+      <c r="P132" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:05 AM</t>
+        </is>
+      </c>
+      <c r="Q132" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="13" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0232</t>
+        </is>
+      </c>
+      <c r="C133" s="21" t="inlineStr">
+        <is>
+          <t>Thota Jaswanth</t>
+        </is>
+      </c>
+      <c r="D133" s="13" t="inlineStr">
+        <is>
+          <t>9347692650</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="inlineStr">
+        <is>
+          <t>2007-06-17</t>
+        </is>
+      </c>
+      <c r="F133" s="21" t="inlineStr">
+        <is>
+          <t>Galiveedu near Gottiveedu</t>
+        </is>
+      </c>
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J133" s="21" t="inlineStr">
+        <is>
+          <t>Jaruguvandla palli near Madhavaram</t>
+        </is>
+      </c>
+      <c r="K133" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L133" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M133" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0124</t>
+        </is>
+      </c>
+      <c r="N133" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O133" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:17 AM</t>
+        </is>
+      </c>
+      <c r="P133" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:16 AM</t>
+        </is>
+      </c>
+      <c r="Q133" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="17" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0233</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>Shaik Mohammad</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr">
+        <is>
+          <t>7842625468</t>
+        </is>
+      </c>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>2006-12-15</t>
+        </is>
+      </c>
+      <c r="F134" s="18" t="inlineStr">
+        <is>
+          <t>Kadapa district Vempalli</t>
+        </is>
+      </c>
+      <c r="G134" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H134" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J134" s="18" t="inlineStr"/>
+      <c r="K134" s="17" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="L134" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M134" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O134" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P134" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:20 AM</t>
+        </is>
+      </c>
+      <c r="Q134" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0234</t>
+        </is>
+      </c>
+      <c r="C135" s="21" t="inlineStr">
+        <is>
+          <t>VALLEPU GANESH</t>
+        </is>
+      </c>
+      <c r="D135" s="13" t="inlineStr">
+        <is>
+          <t>9908853576</t>
+        </is>
+      </c>
+      <c r="E135" s="13" t="inlineStr">
+        <is>
+          <t>2004-10-23</t>
+        </is>
+      </c>
+      <c r="F135" s="21" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G135" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H135" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J135" s="21" t="inlineStr">
+        <is>
+          <t>South zone 2026</t>
+        </is>
+      </c>
+      <c r="K135" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L135" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M135" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0125</t>
+        </is>
+      </c>
+      <c r="N135" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O135" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:52 AM</t>
+        </is>
+      </c>
+      <c r="P135" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 09:51 AM</t>
+        </is>
+      </c>
+      <c r="Q135" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="17" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0235</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="inlineStr">
+        <is>
+          <t>Sudeer</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t>8217086217</t>
+        </is>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>1992-05-06</t>
+        </is>
+      </c>
+      <c r="F136" s="18" t="inlineStr">
+        <is>
+          <t>Vempalli</t>
+        </is>
+      </c>
+      <c r="G136" s="17" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H136" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I136" s="17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J136" s="18" t="inlineStr"/>
+      <c r="K136" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L136" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M136" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0126</t>
+        </is>
+      </c>
+      <c r="N136" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O136" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:06 AM</t>
+        </is>
+      </c>
+      <c r="P136" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:05 AM</t>
+        </is>
+      </c>
+      <c r="Q136" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="13" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0236</t>
+        </is>
+      </c>
+      <c r="C137" s="21" t="inlineStr">
+        <is>
+          <t>Vennapusa Lakshmi Reddy</t>
+        </is>
+      </c>
+      <c r="D137" s="13" t="inlineStr">
+        <is>
+          <t>8074883035</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>2000-07-08</t>
+        </is>
+      </c>
+      <c r="F137" s="21" t="inlineStr">
+        <is>
+          <t>Pendlimarri mandal, Kadapa</t>
+        </is>
+      </c>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>Batter</t>
+        </is>
+      </c>
+      <c r="H137" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J137" s="21" t="inlineStr"/>
+      <c r="K137" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L137" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M137" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0127</t>
+        </is>
+      </c>
+      <c r="N137" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O137" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:15 AM</t>
+        </is>
+      </c>
+      <c r="P137" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:13 AM</t>
+        </is>
+      </c>
+      <c r="Q137" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="17" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0237</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>RAHAMATHULLA   MANI</t>
+        </is>
+      </c>
+      <c r="D138" s="17" t="inlineStr">
+        <is>
+          <t>9701035323</t>
+        </is>
+      </c>
+      <c r="E138" s="17" t="inlineStr">
+        <is>
+          <t>1998-08-24</t>
+        </is>
+      </c>
+      <c r="F138" s="18" t="inlineStr">
+        <is>
+          <t>Chakibanda</t>
+        </is>
+      </c>
+      <c r="G138" s="17" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H138" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I138" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J138" s="18" t="inlineStr">
+        <is>
+          <t>PLAYING KER ACADEMY IN Raya choty</t>
+        </is>
+      </c>
+      <c r="K138" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L138" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M138" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0128</t>
+        </is>
+      </c>
+      <c r="N138" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O138" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:40 AM</t>
+        </is>
+      </c>
+      <c r="P138" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:38 AM</t>
+        </is>
+      </c>
+      <c r="Q138" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="13" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0238</t>
+        </is>
+      </c>
+      <c r="C139" s="21" t="inlineStr">
+        <is>
+          <t>Robin</t>
+        </is>
+      </c>
+      <c r="D139" s="13" t="inlineStr">
+        <is>
+          <t>8688562626</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>1998-06-22</t>
+        </is>
+      </c>
+      <c r="F139" s="21" t="inlineStr">
+        <is>
+          <t>Ontimitta,kadapa</t>
+        </is>
+      </c>
+      <c r="G139" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H139" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J139" s="21" t="inlineStr"/>
+      <c r="K139" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L139" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M139" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0129</t>
+        </is>
+      </c>
+      <c r="N139" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O139" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="P139" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 10:58 AM</t>
+        </is>
+      </c>
+      <c r="Q139" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="17" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0239</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="inlineStr">
+        <is>
+          <t>Ganga Mahesh</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>6305134304</t>
+        </is>
+      </c>
+      <c r="E140" s="17" t="inlineStr">
+        <is>
+          <t>2003-05-17</t>
+        </is>
+      </c>
+      <c r="F140" s="18" t="inlineStr">
+        <is>
+          <t>Yerraguntla</t>
+        </is>
+      </c>
+      <c r="G140" s="17" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H140" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J140" s="18" t="inlineStr">
+        <is>
+          <t>Playing local tournaments</t>
+        </is>
+      </c>
+      <c r="K140" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L140" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M140" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0131</t>
+        </is>
+      </c>
+      <c r="N140" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O140" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:18 AM</t>
+        </is>
+      </c>
+      <c r="P140" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:17 AM</t>
+        </is>
+      </c>
+      <c r="Q140" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="13" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0240</t>
+        </is>
+      </c>
+      <c r="C141" s="21" t="inlineStr">
+        <is>
+          <t>Abdul Salam 07</t>
+        </is>
+      </c>
+      <c r="D141" s="13" t="inlineStr">
+        <is>
+          <t>7997686064</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>2004-12-14</t>
+        </is>
+      </c>
+      <c r="F141" s="21" t="inlineStr">
+        <is>
+          <t>Rajampeta</t>
+        </is>
+      </c>
+      <c r="G141" s="13" t="inlineStr">
+        <is>
+          <t>All-Rounder</t>
+        </is>
+      </c>
+      <c r="H141" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J141" s="21" t="inlineStr">
+        <is>
+          <t>Local Tournaments</t>
+        </is>
+      </c>
+      <c r="K141" s="13" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L141" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M141" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0133</t>
+        </is>
+      </c>
+      <c r="N141" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O141" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 12:59 PM</t>
+        </is>
+      </c>
+      <c r="P141" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:22 AM</t>
+        </is>
+      </c>
+      <c r="Q141" s="21" t="inlineStr">
+        <is>
+          <t>Registration confirmed upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="17" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0241</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>C . Lokeswar</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
+        <is>
+          <t>9550815737</t>
+        </is>
+      </c>
+      <c r="E142" s="17" t="inlineStr">
+        <is>
+          <t>1996-03-28</t>
+        </is>
+      </c>
+      <c r="F142" s="18" t="inlineStr">
+        <is>
+          <t>Pulivendula</t>
+        </is>
+      </c>
+      <c r="G142" s="17" t="inlineStr">
+        <is>
+          <t>Wicketkeeper</t>
+        </is>
+      </c>
+      <c r="H142" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J142" s="18" t="inlineStr">
+        <is>
+          <t>Pulivendula tournments thimammapalli tournament all years continue pertispate</t>
+        </is>
+      </c>
+      <c r="K142" s="17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="L142" s="19" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="M142" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-RCPT-2026-0132</t>
+        </is>
+      </c>
+      <c r="N142" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O142" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:46 AM</t>
+        </is>
+      </c>
+      <c r="P142" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 11:45 AM</t>
+        </is>
+      </c>
+      <c r="Q142" s="18" t="inlineStr">
+        <is>
+          <t>Registration confirmed automatically upon verified Razorpay payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="13" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="13" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0242</t>
+        </is>
+      </c>
+      <c r="C143" s="21" t="inlineStr">
+        <is>
+          <t>Gandepoornanandha</t>
+        </is>
+      </c>
+      <c r="D143" s="13" t="inlineStr">
+        <is>
+          <t>9014177870</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>2010-03-03</t>
+        </is>
+      </c>
+      <c r="F143" s="21" t="inlineStr">
+        <is>
+          <t>Rayachoti</t>
+        </is>
+      </c>
+      <c r="G143" s="13" t="inlineStr">
+        <is>
+          <t>Bowler</t>
+        </is>
+      </c>
+      <c r="H143" s="13" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>Right-arm Pace</t>
+        </is>
+      </c>
+      <c r="J143" s="21" t="inlineStr"/>
+      <c r="K143" s="13" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="L143" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M143" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="22" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O143" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P143" s="13" t="inlineStr">
+        <is>
+          <t>31-10-2026 12:25 PM</t>
+        </is>
+      </c>
+      <c r="Q143" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="17" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="17" t="inlineStr">
+        <is>
+          <t>TKPL-2026-0243</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>Shaik abdul aslam</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>9347817220</t>
+        </is>
+      </c>
+      <c r="E144" s="17" t="inlineStr">
+        <is>
+          <t>2006-08-13</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>Kadapa</t>
+        </is>
+      </c>
+      <c r="G144" s="17" t="inlineStr">
+        <is>
+          <t>Wicketkeeper</t>
+        </is>
+      </c>
+      <c r="H144" s="17" t="inlineStr">
+        <is>
+          <t>Right Hand</t>
+        </is>
+      </c>
+      <c r="I144" s="17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J144" s="18" t="inlineStr"/>
+      <c r="K144" s="17" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="L144" s="26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="M144" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="20" t="inlineStr">
+        <is>
+          <t>₹399</t>
+        </is>
+      </c>
+      <c r="O144" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P144" s="17" t="inlineStr">
+        <is>
+          <t>31-10-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="Q144" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q118"/>
+  <autoFilter ref="A1:Q144"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>